--- a/fake data/Doctor Schedule Calendar.xlsx
+++ b/fake data/Doctor Schedule Calendar.xlsx
@@ -2,129 +2,129 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doctor Directory" sheetId="1" r:id="R597677e7247344ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D001" sheetId="2" r:id="Reddc96d27bc84a54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D002" sheetId="3" r:id="R4b65a6cb7fdb4be0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D003" sheetId="4" r:id="Re576dfed82844d72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D004" sheetId="5" r:id="Re2af229fff55450a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D005" sheetId="6" r:id="Rdacc78de83ef444a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D006" sheetId="7" r:id="R825644c973954087"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D007" sheetId="8" r:id="R79000e1590d2441d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D008" sheetId="9" r:id="R70c41314b47d4585"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D009" sheetId="10" r:id="R2af86d5ba4614b64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D010" sheetId="11" r:id="R5e1945dbd65a42e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D011" sheetId="12" r:id="R967af360717a4793"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D012" sheetId="13" r:id="R74cd0048882c49bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D013" sheetId="14" r:id="R3dd002cbdd464646"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D014" sheetId="15" r:id="Rf87d82782dc047e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D015" sheetId="16" r:id="Rd4ab113c744b48c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D016" sheetId="17" r:id="R9ce1eda702a842d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D017" sheetId="18" r:id="Re5f6bd8c9d344425"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D018" sheetId="19" r:id="R593f2a0af08b4f61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D019" sheetId="20" r:id="Rd5b661c067d3443d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D020" sheetId="21" r:id="R5b93ee0c17b34cef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D021" sheetId="22" r:id="R7294b8070d184cc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D022" sheetId="23" r:id="R013e49e2008844c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D023" sheetId="24" r:id="R3e6edeb2cc1b46f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D024" sheetId="25" r:id="R3954d7c7b78d4c4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D025" sheetId="26" r:id="R748a664976cf4706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D026" sheetId="27" r:id="Rff85ad374a624081"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D027" sheetId="28" r:id="R03909e4e14d34508"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D028" sheetId="29" r:id="Rff83ec5f1cac48c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D029" sheetId="30" r:id="R8464c5753f724d69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D030" sheetId="31" r:id="Rd6ec486f0e944c8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D031" sheetId="32" r:id="R797b89de36c84744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D032" sheetId="33" r:id="Rc86be68a6bfa4cc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D033" sheetId="34" r:id="R1f341dd5353a4273"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D034" sheetId="35" r:id="Rec8a9b9f765d4b0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D035" sheetId="36" r:id="R27b86ac4b470482c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D036" sheetId="37" r:id="Reab223a0ebe745a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D037" sheetId="38" r:id="Re3e8eeca51c0462a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D038" sheetId="39" r:id="R42695a0b082c4144"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D039" sheetId="40" r:id="R38508143820e4de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D040" sheetId="41" r:id="R212fdeb6f92140e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D041" sheetId="42" r:id="R636a13d4e0fd4f9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D042" sheetId="43" r:id="R6224ac04eba8497a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D043" sheetId="44" r:id="R0bf9968f192d48e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D044" sheetId="45" r:id="R3ae1121be6f1486d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D045" sheetId="46" r:id="R57948b217e81445c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D046" sheetId="47" r:id="Rb17ef0bde0544d41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D047" sheetId="48" r:id="R9e91e8ad0a194232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D048" sheetId="49" r:id="R6b034d4d0ade4582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D049" sheetId="50" r:id="Rc0b79440f3394237"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D050" sheetId="51" r:id="Rf00ee27a46494e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D051" sheetId="52" r:id="R33c8029223f94d4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D052" sheetId="53" r:id="R980b30882d684ff6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D053" sheetId="54" r:id="R90e180ffbf2c4c69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D054" sheetId="55" r:id="R66023baaf3bf4003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D055" sheetId="56" r:id="R11ffdd7aa8994374"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D056" sheetId="57" r:id="Rb8e7be69f46a4bb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D057" sheetId="58" r:id="R09006abff6044b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D058" sheetId="59" r:id="Rc73f892c42b74d15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D059" sheetId="60" r:id="R194c3537d2fc4484"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D060" sheetId="61" r:id="Rc3edd0c8dfd5451a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D061" sheetId="62" r:id="R65c9437628754b95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D062" sheetId="63" r:id="R9b7282e755c44ea6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D063" sheetId="64" r:id="Re8f8d2217e204354"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D064" sheetId="65" r:id="R7c6216f755874cc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D065" sheetId="66" r:id="Rf770e2df75e448d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D066" sheetId="67" r:id="R8036b7a9ba3949f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D067" sheetId="68" r:id="R7e5cc352777a495e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D068" sheetId="69" r:id="Rde9e9422ec2b4528"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D069" sheetId="70" r:id="R21bb402dc4894ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D070" sheetId="71" r:id="Rc348020475a04cfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D071" sheetId="72" r:id="R4f87a5e0288d4b27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D072" sheetId="73" r:id="Re9c1cf6efd354529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D073" sheetId="74" r:id="R0a0309601aa74a95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D074" sheetId="75" r:id="R4264f343a6e6481a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D075" sheetId="76" r:id="R492eff0d860c46e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D076" sheetId="77" r:id="Reb79a3f0fd5a4a8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D077" sheetId="78" r:id="Ra08d366a8607481f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D078" sheetId="79" r:id="Rf7e21924186d45ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D079" sheetId="80" r:id="R8837a1a7e3374af0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D080" sheetId="81" r:id="R39012b78406f4c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D081" sheetId="82" r:id="R9ccc92ce41e646b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D082" sheetId="83" r:id="Ra0726d12293a4e01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D083" sheetId="84" r:id="R6e70ff652a854f48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D084" sheetId="85" r:id="R5eaa38dd2e8b4712"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D085" sheetId="86" r:id="R05ac5f7a0d6d4f6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D086" sheetId="87" r:id="Rc80bd064ba74471f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D087" sheetId="88" r:id="Rce099faf475e48d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D088" sheetId="89" r:id="R3fe6796f0f834fa4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D089" sheetId="90" r:id="R1ef212bd2eb04be5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D090" sheetId="91" r:id="R8271c0f5befe4a6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D091" sheetId="92" r:id="Rc305b9533195440d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D092" sheetId="93" r:id="Ra135d18231774f94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D093" sheetId="94" r:id="Rdb473b7ea92546d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D094" sheetId="95" r:id="R5c73d7c2147b49c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D095" sheetId="96" r:id="R0f5d4f8bc2e0483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D096" sheetId="97" r:id="Rc5b40b6b19984cbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D097" sheetId="98" r:id="R7833392e67f84c61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D098" sheetId="99" r:id="R954893c652bd41c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D099" sheetId="100" r:id="R92b338d61d9c41a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D100" sheetId="101" r:id="Re9a0114bf10f4c64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D101" sheetId="102" r:id="Rd39a00f8c804465f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D102" sheetId="103" r:id="R6575ba9b24ab45b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D103" sheetId="104" r:id="R99910ce433c84fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D104" sheetId="105" r:id="Rb943ba6bfeb2455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D105" sheetId="106" r:id="R6fe52137d96b49b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D106" sheetId="107" r:id="Rf3f1edfa84424b73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D107" sheetId="108" r:id="R0b35506e453a4375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D108" sheetId="109" r:id="Rb21162c408ac4804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D109" sheetId="110" r:id="R28d988c38dad4d0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D110" sheetId="111" r:id="Ra92360aca0814195"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D111" sheetId="112" r:id="R82ba6bbb77b74d71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D112" sheetId="113" r:id="Rdd2ab04161bf4acc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D113" sheetId="114" r:id="R38fddb9ba5c84ec9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D114" sheetId="115" r:id="Rea928933299645e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D115" sheetId="116" r:id="R04d2923338484ec4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D116" sheetId="117" r:id="Rf7cbd64a0e754f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D117" sheetId="118" r:id="Rafe0afa3672b4612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D118" sheetId="119" r:id="R3fd5870c38f94817"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D119" sheetId="120" r:id="R526fa1333fc440b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D120" sheetId="121" r:id="Reebc5136286b4169"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D121" sheetId="122" r:id="R5ec72943eb6d410a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D122" sheetId="123" r:id="Ra9d1557bc90848f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doctor Directory" sheetId="1" r:id="R5ec392f1ffcf40d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D001" sheetId="2" r:id="R3fb23f85761c45f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D002" sheetId="3" r:id="R683cad98308043a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D003" sheetId="4" r:id="Rd16c3e707ab1488a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D004" sheetId="5" r:id="R1120713ef47d4181"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D005" sheetId="6" r:id="Rcf24e805ebb9487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D006" sheetId="7" r:id="R4278363331794219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D007" sheetId="8" r:id="Rac0220519f1846b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D008" sheetId="9" r:id="R2bf7c08a6cdc427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D009" sheetId="10" r:id="R37e5a3028be64b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D010" sheetId="11" r:id="R881deccf7a824f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D011" sheetId="12" r:id="Rca73fb7749344f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D012" sheetId="13" r:id="R9718b23cdbf444f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D013" sheetId="14" r:id="R294ef4e477f44151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D014" sheetId="15" r:id="Reb598a1ee9b54798"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D015" sheetId="16" r:id="R45e766e368584b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D016" sheetId="17" r:id="Re0f95e7c85dc4b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D017" sheetId="18" r:id="R81a25eda691e447f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D018" sheetId="19" r:id="R3c765f2297494768"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D019" sheetId="20" r:id="R14316e8a277a4ce9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D020" sheetId="21" r:id="R6c2a0066a0a649ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D021" sheetId="22" r:id="R844ff0d273b84648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D022" sheetId="23" r:id="R56412824841f4762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D023" sheetId="24" r:id="R3e63715eae484a47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D024" sheetId="25" r:id="Rfac8ac1213544be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D025" sheetId="26" r:id="R37132d90559c4600"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D026" sheetId="27" r:id="Ra8ca2e98cdf84c11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D027" sheetId="28" r:id="R9bcd3883553548e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D028" sheetId="29" r:id="R8dbc3b341f434d62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D029" sheetId="30" r:id="R37752431c958477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D030" sheetId="31" r:id="R1113346bf67f46b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D031" sheetId="32" r:id="Re9bba3596dab4618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D032" sheetId="33" r:id="R8422300ffc04410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D033" sheetId="34" r:id="Red4543e740584a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D034" sheetId="35" r:id="Ra9536ef674f34b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D035" sheetId="36" r:id="R6deac1449fdc460f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D036" sheetId="37" r:id="R48c31de770ff45f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D037" sheetId="38" r:id="R71c2c664acf64716"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D038" sheetId="39" r:id="R1a8b0bbbf00b4e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D039" sheetId="40" r:id="Re7d73a0fc0b14ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D040" sheetId="41" r:id="R664b7fa9cffb4dca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D041" sheetId="42" r:id="R4fe2a8adf5bf44f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D042" sheetId="43" r:id="R930041c2542c47ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D043" sheetId="44" r:id="R8c453cca56a44e05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D044" sheetId="45" r:id="R838801d7ced44e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D045" sheetId="46" r:id="R375a13db08e54529"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D046" sheetId="47" r:id="R7c8888fc93514522"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D047" sheetId="48" r:id="R6efc43eb5f9c4f92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D048" sheetId="49" r:id="Rd1a241edca9f44c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D049" sheetId="50" r:id="Rbe8595059ac54348"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D050" sheetId="51" r:id="R8c254c632cb24773"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D051" sheetId="52" r:id="Rc4d5804118b14541"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D052" sheetId="53" r:id="R4d8276f041ee42a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D053" sheetId="54" r:id="Rb519933e9b1042c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D054" sheetId="55" r:id="R90a4a525081b4f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D055" sheetId="56" r:id="R4f34c371c5924718"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D056" sheetId="57" r:id="R1efd4c76de10412c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D057" sheetId="58" r:id="Rad4bbef5afe743eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D058" sheetId="59" r:id="R43d3125093ab45f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D059" sheetId="60" r:id="Rafcb25455aaf4ea7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D060" sheetId="61" r:id="R2e5f8025c1df4457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D061" sheetId="62" r:id="R6c02a8bfbd7e4408"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D062" sheetId="63" r:id="R2be3fa3b8b9840c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D063" sheetId="64" r:id="R080f0bf3849f49ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D064" sheetId="65" r:id="R3392ba9fb4064c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D065" sheetId="66" r:id="R6807d1c88e0044b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D066" sheetId="67" r:id="R6cb301630cae47d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D067" sheetId="68" r:id="Rf154cc8cdd5f49f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D068" sheetId="69" r:id="R03d92d6daaa04b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D069" sheetId="70" r:id="Rce0207ecda714e4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D070" sheetId="71" r:id="R2dc385c1463f4105"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D071" sheetId="72" r:id="R705b32e16db9496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D072" sheetId="73" r:id="Rf9ae9f323fef4d9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D073" sheetId="74" r:id="Re35e7a64aa784bd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D074" sheetId="75" r:id="Rcdd2a534f4bd48ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D075" sheetId="76" r:id="Ra816fa3f0e07457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D076" sheetId="77" r:id="R85612db9f94c4ad4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D077" sheetId="78" r:id="R83d5a8bbf9ae4a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D078" sheetId="79" r:id="R3e190b93e7ec4d57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D079" sheetId="80" r:id="R25c48d5e837b4d1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D080" sheetId="81" r:id="Rbe821520af464bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D081" sheetId="82" r:id="R1f6cb9e8c26b4474"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D082" sheetId="83" r:id="Rebd9d1b1f20e445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D083" sheetId="84" r:id="R46cdee44271945c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D084" sheetId="85" r:id="Rdb256a5402d54e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D085" sheetId="86" r:id="Rce372b5e95974152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D086" sheetId="87" r:id="Ra6b1a551c76841b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D087" sheetId="88" r:id="R607d85aa08b842a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D088" sheetId="89" r:id="R9f9c154a343e444b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D089" sheetId="90" r:id="R6e3c092831a24df5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D090" sheetId="91" r:id="Re14a9ad779304f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D091" sheetId="92" r:id="Rd5ee5ee68e6041b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D092" sheetId="93" r:id="R43046adbbac541ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D093" sheetId="94" r:id="Rd86ed4551d6342fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D094" sheetId="95" r:id="R883c2c4e7f6d423b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D095" sheetId="96" r:id="Rd7144d4145394337"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D096" sheetId="97" r:id="R7dc3f08adce64c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D097" sheetId="98" r:id="R712578a26d7942dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D098" sheetId="99" r:id="R0205915349b34abd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D099" sheetId="100" r:id="Rc007210648824bdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D100" sheetId="101" r:id="R91c6299e294f44c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D101" sheetId="102" r:id="R7e4f929a90b14e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D102" sheetId="103" r:id="Ra3545d29b10a4458"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D103" sheetId="104" r:id="Rafb65c5f6ed74583"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D104" sheetId="105" r:id="R2c3249aae32849cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D105" sheetId="106" r:id="R72c52a56988b44fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D106" sheetId="107" r:id="R28a8d746b7b54e24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D107" sheetId="108" r:id="R3c4f7706fde9478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D108" sheetId="109" r:id="R975fb9d251314c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D109" sheetId="110" r:id="R03244d343d814cb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D110" sheetId="111" r:id="Re97603e82e5d45d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D111" sheetId="112" r:id="R4d0e9982ac814d12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D112" sheetId="113" r:id="R7cd6c11335eb49da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D113" sheetId="114" r:id="R0c9a8966e59345da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D114" sheetId="115" r:id="Ra90c6abc798f4deb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D115" sheetId="116" r:id="R0eded2b6c6e44f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D116" sheetId="117" r:id="Ra0edc109b6e545f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D117" sheetId="118" r:id="R363d2605117e4986"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D118" sheetId="119" r:id="R9e6b0b3e0567413b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D119" sheetId="120" r:id="Rfc0a5059911d425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D120" sheetId="121" r:id="R74deb71e522b493c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D121" sheetId="122" r:id="R91ca88de4ece4967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D122" sheetId="123" r:id="R02cdeb6b24de4b75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -693,7 +693,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8e2536b126b40ae"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2b6eaeca064047b4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3510,7 +3510,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>One weekly calendar tab per doctor, based on lecture assignments in the General Schedule. Tutorials and labs remain assigned to teaching assistants.</x:v>
+        <x:v>One weekly calendar per doctor, based on shared or major-specific lectures. Tutorials and labs are TA-led, single-major, and never shared across majors.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -6822,9 +6822,9 @@
     <x:mergeCell ref="A2:P2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7d380489bbf4a3a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85cb08e230504ea6"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b608825a6874dcd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb831abebc6524758"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7097,7 +7097,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MD-Y1-G01; MD-Y1-G02; MD-Y1-G03; MD-Y1-G04; MD-Y1-G05</x:v>
+        <x:v>MD-Y1-T01; MD-Y1-T02; MD-Y1-T03; MD-Y1-T04; MD-Y1-T05</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>104</x:v>
@@ -7122,7 +7122,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b43733f75164cf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1732290716b64eba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7399,7 +7399,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>LLS-Y5-G01; LLS-Y5-G02; LLS-Y5-G03</x:v>
+        <x:v>LLS-Y5-T01; LLS-Y5-T02; LLS-Y5-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>56</x:v>
@@ -7440,7 +7440,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>PHR-Y5-G01; PHR-Y5-G02; PHR-Y5-G03; PHR-Y5-G04; BIO-Y5-G01; BIO-Y5-G02; BIO-Y5-G03; CPH-Y5-G01; CPH-Y5-G02; CPH-Y5-G03</x:v>
+        <x:v>PHR-Y5-T01; PHR-Y5-T02; PHR-Y5-T03; PHR-Y5-T04; BIO-Y5-T01; BIO-Y5-T02; BIO-Y5-T03; CPH-Y5-T01; CPH-Y5-T02; CPH-Y5-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>193</x:v>
@@ -7465,7 +7465,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R681c925f534243a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R172314ef3479467d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7742,7 +7742,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>ARC-Y5-G09</x:v>
+        <x:v>ARC-Y5-T09</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>24</x:v>
@@ -7783,7 +7783,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ARC-Y5-G01; ARC-Y5-G02; ARC-Y5-G03; ARC-Y5-G04; ARC-Y5-G05; ARC-Y5-G06; ARC-Y5-G07; ARC-Y5-G08</x:v>
+        <x:v>ARC-Y5-T01; ARC-Y5-T02; ARC-Y5-T03; ARC-Y5-T04; ARC-Y5-T05; ARC-Y5-T06; ARC-Y5-T07; ARC-Y5-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>199</x:v>
@@ -7808,7 +7808,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0b903cacc284c5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60d4235e47814f43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8085,7 +8085,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>TBM-Y3-G04</x:v>
+        <x:v>TBM-Y3-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>21</x:v>
@@ -8126,7 +8126,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>GM-Y3-G01; GM-Y3-G02; BI-Y3-G01; BI-Y3-G02; BI-Y3-G03; BI-Y3-G04; TBM-Y3-G01; TBM-Y3-G02; TBM-Y3-G03</x:v>
+        <x:v>GM-Y3-T01; GM-Y3-T02; BI-Y3-T01; BI-Y3-T02; BI-Y3-T03; BI-Y3-T04; TBM-Y3-T01; TBM-Y3-T02; TBM-Y3-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>192</x:v>
@@ -8151,7 +8151,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R955f83b400cc40f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00eb62f7ff7f4b02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8432,7 +8432,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CSE-Y4-G09; CSE-Y4-G10</x:v>
+        <x:v>CSE-Y4-T09; CSE-Y4-T10</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>48</x:v>
@@ -8473,7 +8473,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CSE-Y4-G01; CSE-Y4-G02; CSE-Y4-G03; CSE-Y4-G04; CSE-Y4-G05; CSE-Y4-G06; CSE-Y4-G07; CSE-Y4-G08</x:v>
+        <x:v>CSE-Y4-T01; CSE-Y4-T02; CSE-Y4-T03; CSE-Y4-T04; CSE-Y4-T05; CSE-Y4-T06; CSE-Y4-T07; CSE-Y4-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>195</x:v>
@@ -8514,7 +8514,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CPH-Y5-G01; CPH-Y5-G02; CPH-Y5-G03</x:v>
+        <x:v>CPH-Y5-T01; CPH-Y5-T02; CPH-Y5-T03</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>66</x:v>
@@ -8539,7 +8539,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22a2e1a173b943e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R698270383c04435a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8816,7 +8816,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>BI-Y2-G01; BI-Y2-G02; BI-Y2-G03; BI-Y2-G04</x:v>
+        <x:v>BI-Y2-T01; BI-Y2-T02; BI-Y2-T03; BI-Y2-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>90</x:v>
@@ -8857,7 +8857,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>BIO-Y3-G01; BIO-Y3-G02; BIO-Y3-G03</x:v>
+        <x:v>BIO-Y3-T01; BIO-Y3-T02; BIO-Y3-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>55</x:v>
@@ -8882,7 +8882,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb67c654c67bc4440"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d2aa278147401b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9163,7 +9163,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CSE-Y1-G01; CSE-Y1-G02; CSE-Y1-G03; CSE-Y1-G04; CSE-Y1-G05; CSE-Y1-G06; CSE-Y1-G07; CSE-Y1-G08</x:v>
+        <x:v>CSE-Y1-T01; CSE-Y1-T02; CSE-Y1-T03; CSE-Y1-T04; CSE-Y1-T05; CSE-Y1-T06; CSE-Y1-T07; CSE-Y1-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>190</x:v>
@@ -9204,7 +9204,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DMET-Y1-G05; DMET-Y1-G06; DMET-Y1-G07; DMET-Y1-G08; DMET-Y1-G09; DMET-Y1-G10; DMET-Y1-G11</x:v>
+        <x:v>DMET-Y1-T05; DMET-Y1-T06; DMET-Y1-T07; DMET-Y1-T08; DMET-Y1-T09; DMET-Y1-T10; DMET-Y1-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>174</x:v>
@@ -9245,7 +9245,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CSE-Y1-G09; CSE-Y1-G10; CSE-Y1-G11; CSE-Y1-G12; DMET-Y1-G01; DMET-Y1-G02; DMET-Y1-G03; DMET-Y1-G04</x:v>
+        <x:v>CSE-Y1-T09; CSE-Y1-T10; CSE-Y1-T11; CSE-Y1-T12; DMET-Y1-T01; DMET-Y1-T02; DMET-Y1-T03; DMET-Y1-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>192</x:v>
@@ -9270,7 +9270,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd4006b1a776453c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b46ab14ae4d46d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9555,7 +9555,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CIV-Y5-G01; CIV-Y5-G02; CIV-Y5-G03; CIV-Y5-G04; CIV-Y5-G05; CIV-Y5-G06; CIV-Y5-G07; CIV-Y5-G08</x:v>
+        <x:v>CIV-Y5-T01; CIV-Y5-T02; CIV-Y5-T03; CIV-Y5-T04; CIV-Y5-T05; CIV-Y5-T06; CIV-Y5-T07; CIV-Y5-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>194</x:v>
@@ -9596,7 +9596,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DMET-Y2-G09; DMET-Y2-G10; DMET-Y2-G11</x:v>
+        <x:v>DMET-Y2-T09; DMET-Y2-T10; DMET-Y2-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>71</x:v>
@@ -9637,7 +9637,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DMET-Y2-G01; DMET-Y2-G02; DMET-Y2-G03; DMET-Y2-G04; DMET-Y2-G05; DMET-Y2-G06; DMET-Y2-G07; DMET-Y2-G08</x:v>
+        <x:v>DMET-Y2-T01; DMET-Y2-T02; DMET-Y2-T03; DMET-Y2-T04; DMET-Y2-T05; DMET-Y2-T06; DMET-Y2-T07; DMET-Y2-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>192</x:v>
@@ -9678,7 +9678,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>CIV-Y5-G09; CIV-Y5-G10</x:v>
+        <x:v>CIV-Y5-T09; CIV-Y5-T10</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>48</x:v>
@@ -9703,7 +9703,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43c814c1cb00416d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42afcc11824d4786"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9976,7 +9976,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CPH-Y2-G01; CPH-Y2-G02; CPH-Y2-G03; CPH-Y2-G04</x:v>
+        <x:v>CPH-Y2-T01; CPH-Y2-T02; CPH-Y2-T03; CPH-Y2-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>76</x:v>
@@ -10001,7 +10001,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94b7d9d4db684982"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R043a2de97dd34c18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10282,7 +10282,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PGD-Y4-G01; PGD-Y4-G02; PGD-Y4-G03</x:v>
+        <x:v>PGD-Y4-T01; PGD-Y4-T02; PGD-Y4-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>53</x:v>
@@ -10323,7 +10323,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DEN-Y5-G01; DEN-Y5-G02</x:v>
+        <x:v>DEN-Y5-T01; DEN-Y5-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>37</x:v>
@@ -10364,7 +10364,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MD-Y4-G01; MD-Y4-G02; MD-Y4-G03; MD-Y4-G04</x:v>
+        <x:v>MD-Y4-T01; MD-Y4-T02; MD-Y4-T03; MD-Y4-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>89</x:v>
@@ -10389,7 +10389,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R298f84166b614fc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56aeb6faba2c4326"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10686,7 +10686,7 @@
         <x:v>L06</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CIV-Y3-G08; CIV-Y3-G09; CIV-Y3-G10; CIV-Y3-G11; ARC-Y3-G01; ARC-Y3-G02; ARC-Y3-G03; ARC-Y3-G04</x:v>
+        <x:v>CIV-Y3-T08; CIV-Y3-T09; CIV-Y3-T10; CIV-Y3-T11; ARC-Y3-T01; ARC-Y3-T02; ARC-Y3-T03; ARC-Y3-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>196</x:v>
@@ -10727,7 +10727,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MAT-Y3-G09; MAT-Y3-G10; MAT-Y3-G11; DPE-Y3-G01; DPE-Y3-G02; DPE-Y3-G03; DPE-Y3-G04; DPE-Y3-G05</x:v>
+        <x:v>MAT-Y3-T09; MAT-Y3-T10; MAT-Y3-T11; DPE-Y3-T01; DPE-Y3-T02; DPE-Y3-T03; DPE-Y3-T04; DPE-Y3-T05</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>196</x:v>
@@ -10768,7 +10768,7 @@
         <x:v>L07</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>ARC-Y3-G05; ARC-Y3-G06; ARC-Y3-G07; ARC-Y3-G08; ARC-Y3-G09; ARC-Y3-G10</x:v>
+        <x:v>ARC-Y3-T05; ARC-Y3-T06; ARC-Y3-T07; ARC-Y3-T08; ARC-Y3-T09; ARC-Y3-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>146</x:v>
@@ -10809,7 +10809,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>DPE-Y3-G06; DPE-Y3-G07; DPE-Y3-G08; DPE-Y3-G09; DPE-Y3-G10; DPE-Y3-G11; MCT-Y3-G01; MCT-Y3-G02</x:v>
+        <x:v>DPE-Y3-T06; DPE-Y3-T07; DPE-Y3-T08; DPE-Y3-T09; DPE-Y3-T10; DPE-Y3-T11; MCT-Y3-T01; MCT-Y3-T02</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>192</x:v>
@@ -10850,7 +10850,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>MCT-Y3-G03; MCT-Y3-G04; MCT-Y3-G05; MCT-Y3-G06; MCT-Y3-G07; MCT-Y3-G08; MCT-Y3-G09; MCT-Y3-G10</x:v>
+        <x:v>MCT-Y3-T03; MCT-Y3-T04; MCT-Y3-T05; MCT-Y3-T06; MCT-Y3-T07; MCT-Y3-T08; MCT-Y3-T09; MCT-Y3-T10</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>192</x:v>
@@ -10891,7 +10891,7 @@
         <x:v>L05</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>MCT-Y3-G11; CIV-Y3-G01; CIV-Y3-G02; CIV-Y3-G03; CIV-Y3-G04; CIV-Y3-G05; CIV-Y3-G06; CIV-Y3-G07</x:v>
+        <x:v>MCT-Y3-T11; CIV-Y3-T01; CIV-Y3-T02; CIV-Y3-T03; CIV-Y3-T04; CIV-Y3-T05; CIV-Y3-T06; CIV-Y3-T07</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>195</x:v>
@@ -10932,7 +10932,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>MAT-Y3-G01; MAT-Y3-G02; MAT-Y3-G03; MAT-Y3-G04; MAT-Y3-G05; MAT-Y3-G06; MAT-Y3-G07; MAT-Y3-G08</x:v>
+        <x:v>MAT-Y3-T01; MAT-Y3-T02; MAT-Y3-T03; MAT-Y3-T04; MAT-Y3-T05; MAT-Y3-T06; MAT-Y3-T07; MAT-Y3-T08</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>192</x:v>
@@ -10957,7 +10957,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73e5a97d704c4b39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1ba9bbf353c452b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11234,7 +11234,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PD-Y4-G01; PD-Y4-G02; PD-Y4-G03; PD-Y4-G04</x:v>
+        <x:v>PD-Y4-T01; PD-Y4-T02; PD-Y4-T03; PD-Y4-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>93</x:v>
@@ -11275,7 +11275,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>GM-Y5-G01; GM-Y5-G02; BI-Y5-G01; BI-Y5-G02; BI-Y5-G03; BI-Y5-G04; TBM-Y5-G01; TBM-Y5-G02; TBM-Y5-G03; TBM-Y5-G04</x:v>
+        <x:v>GM-Y5-T01; GM-Y5-T02; BI-Y5-T01; BI-Y5-T02; BI-Y5-T03; BI-Y5-T04; TBM-Y5-T01; TBM-Y5-T02; TBM-Y5-T03; TBM-Y5-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>193</x:v>
@@ -11300,7 +11300,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra774a7b13f194097"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf4bdda12b054d60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11573,7 +11573,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PGD-Y4-G01; PGD-Y4-G02; PGD-Y4-G03; MSC-Y4-G01; MSC-Y4-G02; PHD-Y4-G01; PHD-Y4-G02; PHD-Y4-G03; PHD-Y4-G04</x:v>
+        <x:v>PGD-Y4-T01; PGD-Y4-T02; PGD-Y4-T03; MSC-Y4-T01; MSC-Y4-T02; PHD-Y4-T01; PHD-Y4-T02; PHD-Y4-T03; PHD-Y4-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>187</x:v>
@@ -11598,7 +11598,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67ca41aeba8644ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66f4829be07e4125"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11887,7 +11887,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CSE-Y5-G09; CSE-Y5-G10</x:v>
+        <x:v>CSE-Y5-T09; CSE-Y5-T10</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>46</x:v>
@@ -11928,7 +11928,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DMET-Y1-G09; DMET-Y1-G10; DMET-Y1-G11</x:v>
+        <x:v>DMET-Y1-T09; DMET-Y1-T10; DMET-Y1-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>74</x:v>
@@ -11969,7 +11969,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>GD-Y1-G01; GD-Y1-G02</x:v>
+        <x:v>GD-Y1-T01; GD-Y1-T02</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>48</x:v>
@@ -12010,7 +12010,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>DMET-Y1-G01; DMET-Y1-G02; DMET-Y1-G03; DMET-Y1-G04; DMET-Y1-G05; DMET-Y1-G06; DMET-Y1-G07; DMET-Y1-G08</x:v>
+        <x:v>DMET-Y1-T01; DMET-Y1-T02; DMET-Y1-T03; DMET-Y1-T04; DMET-Y1-T05; DMET-Y1-T06; DMET-Y1-T07; DMET-Y1-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>200</x:v>
@@ -12051,7 +12051,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>CSE-Y5-G01; CSE-Y5-G02; CSE-Y5-G03; CSE-Y5-G04; CSE-Y5-G05; CSE-Y5-G06; CSE-Y5-G07; CSE-Y5-G08</x:v>
+        <x:v>CSE-Y5-T01; CSE-Y5-T02; CSE-Y5-T03; CSE-Y5-T04; CSE-Y5-T05; CSE-Y5-T06; CSE-Y5-T07; CSE-Y5-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>185</x:v>
@@ -12076,7 +12076,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fe8661794a34bda"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0113d3f5f1aa427e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12349,7 +12349,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MSC-Y3-G01; MSC-Y3-G02</x:v>
+        <x:v>MSC-Y3-T01; MSC-Y3-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>48</x:v>
@@ -12374,7 +12374,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca37b403bb04102"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9d4f4db54da43a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12663,7 +12663,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DMET-Y1-G09; DMET-Y1-G10; DMET-Y1-G11</x:v>
+        <x:v>DMET-Y1-T09; DMET-Y1-T10; DMET-Y1-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>74</x:v>
@@ -12704,7 +12704,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>GD-Y1-G01; GD-Y1-G02</x:v>
+        <x:v>GD-Y1-T01; GD-Y1-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>48</x:v>
@@ -12745,7 +12745,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CSE-Y5-G01; CSE-Y5-G02; CSE-Y5-G03; CSE-Y5-G04; CSE-Y5-G05; CSE-Y5-G06; CSE-Y5-G07; CSE-Y5-G08</x:v>
+        <x:v>CSE-Y5-T01; CSE-Y5-T02; CSE-Y5-T03; CSE-Y5-T04; CSE-Y5-T05; CSE-Y5-T06; CSE-Y5-T07; CSE-Y5-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>185</x:v>
@@ -12786,7 +12786,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>CSE-Y5-G09; CSE-Y5-G10</x:v>
+        <x:v>CSE-Y5-T09; CSE-Y5-T10</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>46</x:v>
@@ -12827,7 +12827,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>DMET-Y1-G01; DMET-Y1-G02; DMET-Y1-G03; DMET-Y1-G04; DMET-Y1-G05; DMET-Y1-G06; DMET-Y1-G07; DMET-Y1-G08</x:v>
+        <x:v>DMET-Y1-T01; DMET-Y1-T02; DMET-Y1-T03; DMET-Y1-T04; DMET-Y1-T05; DMET-Y1-T06; DMET-Y1-T07; DMET-Y1-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>200</x:v>
@@ -12852,7 +12852,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3569f6c3ff2d43be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46fd8041e2ae42b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13125,7 +13125,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>TBM-Y5-G01; TBM-Y5-G02; TBM-Y5-G03; TBM-Y5-G04</x:v>
+        <x:v>TBM-Y5-T01; TBM-Y5-T02; TBM-Y5-T03; TBM-Y5-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>80</x:v>
@@ -13150,7 +13150,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R858a4293457c4e67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1984690fcdc64167"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13447,7 +13447,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>ELX-Y2-G09; ELX-Y2-G10; ELX-Y2-G11</x:v>
+        <x:v>ELX-Y2-T09; ELX-Y2-T10; ELX-Y2-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>71</x:v>
@@ -13488,7 +13488,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CSE-Y1-G09; CSE-Y1-G10; CSE-Y1-G11; CSE-Y1-G12</x:v>
+        <x:v>CSE-Y1-T09; CSE-Y1-T10; CSE-Y1-T11; CSE-Y1-T12</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>92</x:v>
@@ -13529,7 +13529,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>ELX-Y2-G01; ELX-Y2-G02; ELX-Y2-G03; ELX-Y2-G04; ELX-Y2-G05; ELX-Y2-G06; ELX-Y2-G07; ELX-Y2-G08</x:v>
+        <x:v>ELX-Y2-T01; ELX-Y2-T02; ELX-Y2-T03; ELX-Y2-T04; ELX-Y2-T05; ELX-Y2-T06; ELX-Y2-T07; ELX-Y2-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>192</x:v>
@@ -13570,7 +13570,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>PD-Y3-G01; PD-Y3-G02; PD-Y3-G03; PD-Y3-G04</x:v>
+        <x:v>PD-Y3-T01; PD-Y3-T02; PD-Y3-T03; PD-Y3-T04</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>98</x:v>
@@ -13611,7 +13611,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>DPE-Y2-G09; DPE-Y2-G10; DPE-Y2-G11; DPE-Y2-G12</x:v>
+        <x:v>DPE-Y2-T09; DPE-Y2-T10; DPE-Y2-T11; DPE-Y2-T12</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>92</x:v>
@@ -13652,7 +13652,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>CSE-Y1-G01; CSE-Y1-G02; CSE-Y1-G03; CSE-Y1-G04; CSE-Y1-G05; CSE-Y1-G06; CSE-Y1-G07; CSE-Y1-G08</x:v>
+        <x:v>CSE-Y1-T01; CSE-Y1-T02; CSE-Y1-T03; CSE-Y1-T04; CSE-Y1-T05; CSE-Y1-T06; CSE-Y1-T07; CSE-Y1-T08</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>190</x:v>
@@ -13693,7 +13693,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>DPE-Y2-G01; DPE-Y2-G02; DPE-Y2-G03; DPE-Y2-G04; DPE-Y2-G05; DPE-Y2-G06; DPE-Y2-G07; DPE-Y2-G08</x:v>
+        <x:v>DPE-Y2-T01; DPE-Y2-T02; DPE-Y2-T03; DPE-Y2-T04; DPE-Y2-T05; DPE-Y2-T06; DPE-Y2-T07; DPE-Y2-T08</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>190</x:v>
@@ -13718,7 +13718,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R420a5f622bd746c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd764ce7676f48a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14019,7 +14019,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PHR-Y4-G01; PHR-Y4-G02; PHR-Y4-G03; PHR-Y4-G04</x:v>
+        <x:v>PHR-Y4-T01; PHR-Y4-T02; PHR-Y4-T03; PHR-Y4-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>79</x:v>
@@ -14060,7 +14060,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DPE-Y1-G01; DPE-Y1-G02; DPE-Y1-G03; DPE-Y1-G04; DPE-Y1-G05; DPE-Y1-G06; DPE-Y1-G07; DPE-Y1-G08</x:v>
+        <x:v>DPE-Y1-T01; DPE-Y1-T02; DPE-Y1-T03; DPE-Y1-T04; DPE-Y1-T05; DPE-Y1-T06; DPE-Y1-T07; DPE-Y1-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>200</x:v>
@@ -14101,7 +14101,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>ELX-Y1-G09; ELX-Y1-G10; ELX-Y1-G11</x:v>
+        <x:v>ELX-Y1-T09; ELX-Y1-T10; ELX-Y1-T11</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>74</x:v>
@@ -14142,7 +14142,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>ELX-Y1-G01; ELX-Y1-G02; ELX-Y1-G03; ELX-Y1-G04; ELX-Y1-G05; ELX-Y1-G06; ELX-Y1-G07; ELX-Y1-G08</x:v>
+        <x:v>ELX-Y1-T01; ELX-Y1-T02; ELX-Y1-T03; ELX-Y1-T04; ELX-Y1-T05; ELX-Y1-T06; ELX-Y1-T07; ELX-Y1-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>200</x:v>
@@ -14183,7 +14183,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>NET-Y5-G09; NET-Y5-G10</x:v>
+        <x:v>NET-Y5-T09; NET-Y5-T10</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>46</x:v>
@@ -14224,7 +14224,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>DPE-Y1-G09; DPE-Y1-G10; DPE-Y1-G11; DPE-Y1-G12</x:v>
+        <x:v>DPE-Y1-T09; DPE-Y1-T10; DPE-Y1-T11; DPE-Y1-T12</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>96</x:v>
@@ -14265,7 +14265,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>GD-Y2-G01; GD-Y2-G02</x:v>
+        <x:v>GD-Y2-T01; GD-Y2-T02</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>46</x:v>
@@ -14306,7 +14306,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>NET-Y5-G01; NET-Y5-G02; NET-Y5-G03; NET-Y5-G04; NET-Y5-G05; NET-Y5-G06; NET-Y5-G07; NET-Y5-G08</x:v>
+        <x:v>NET-Y5-T01; NET-Y5-T02; NET-Y5-T03; NET-Y5-T04; NET-Y5-T05; NET-Y5-T06; NET-Y5-T07; NET-Y5-T08</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>187</x:v>
@@ -14331,7 +14331,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42bc47b7e40e4c27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R160c18dd65de45b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14628,7 +14628,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MD-Y5-G01; MD-Y5-G02; MD-Y5-G03; MD-Y5-G04</x:v>
+        <x:v>MD-Y5-T01; MD-Y5-T02; MD-Y5-T03; MD-Y5-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>84</x:v>
@@ -14669,7 +14669,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DEN-Y5-G01; DEN-Y5-G02</x:v>
+        <x:v>DEN-Y5-T01; DEN-Y5-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>37</x:v>
@@ -14710,7 +14710,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>NET-Y4-G09; NET-Y4-G10</x:v>
+        <x:v>NET-Y4-T09; NET-Y4-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>48</x:v>
@@ -14751,7 +14751,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>TBM-Y2-G01; TBM-Y2-G02; TBM-Y2-G03; TBM-Y2-G04</x:v>
+        <x:v>TBM-Y2-T01; TBM-Y2-T02; TBM-Y2-T03; TBM-Y2-T04</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>92</x:v>
@@ -14792,7 +14792,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>PGD-Y5-G01; PGD-Y5-G02; PGD-Y5-G03</x:v>
+        <x:v>PGD-Y5-T01; PGD-Y5-T02; PGD-Y5-T03</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>51</x:v>
@@ -14833,7 +14833,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>GM-Y1-G01; GM-Y1-G02</x:v>
+        <x:v>GM-Y1-T01; GM-Y1-T02</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>45</x:v>
@@ -14874,7 +14874,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>NET-Y4-G01; NET-Y4-G02; NET-Y4-G03; NET-Y4-G04; NET-Y4-G05; NET-Y4-G06; NET-Y4-G07; NET-Y4-G08</x:v>
+        <x:v>NET-Y4-T01; NET-Y4-T02; NET-Y4-T03; NET-Y4-T04; NET-Y4-T05; NET-Y4-T06; NET-Y4-T07; NET-Y4-T08</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>199</x:v>
@@ -14899,7 +14899,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racd296ca11914fc5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40cad56e1df646d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15204,7 +15204,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>NET-Y1-G01; NET-Y1-G02; NET-Y1-G03; NET-Y1-G04; NET-Y1-G05; NET-Y1-G06; NET-Y1-G07; NET-Y1-G08</x:v>
+        <x:v>NET-Y1-T01; NET-Y1-T02; NET-Y1-T03; NET-Y1-T04; NET-Y1-T05; NET-Y1-T06; NET-Y1-T07; NET-Y1-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>192</x:v>
@@ -15245,7 +15245,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ARC-Y2-G01; ARC-Y2-G02; ARC-Y2-G03; ARC-Y2-G04; ARC-Y2-G05; ARC-Y2-G06; ARC-Y2-G07; ARC-Y2-G08</x:v>
+        <x:v>ARC-Y2-T01; ARC-Y2-T02; ARC-Y2-T03; ARC-Y2-T04; ARC-Y2-T05; ARC-Y2-T06; ARC-Y2-T07; ARC-Y2-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>190</x:v>
@@ -15286,7 +15286,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>GD-Y5-G01; GD-Y5-G02; MD-Y5-G01; MD-Y5-G02; MD-Y5-G03; MD-Y5-G04; PD-Y5-G01; PD-Y5-G02; PD-Y5-G03</x:v>
+        <x:v>GD-Y5-T01; GD-Y5-T02; MD-Y5-T01; MD-Y5-T02; MD-Y5-T03; MD-Y5-T04; PD-Y5-T01; PD-Y5-T02; PD-Y5-T03</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>190</x:v>
@@ -15327,7 +15327,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>BIO-Y1-G01; BIO-Y1-G02; BIO-Y1-G03</x:v>
+        <x:v>BIO-Y1-T01; BIO-Y1-T02; BIO-Y1-T03</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>62</x:v>
@@ -15368,7 +15368,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>NET-Y1-G09; NET-Y1-G10; NET-Y1-G11; NET-Y1-G12</x:v>
+        <x:v>NET-Y1-T09; NET-Y1-T10; NET-Y1-T11; NET-Y1-T12</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>93</x:v>
@@ -15409,7 +15409,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>PD-Y1-G01; PD-Y1-G02; PD-Y1-G03; PD-Y1-G04; PD-Y1-G05</x:v>
+        <x:v>PD-Y1-T01; PD-Y1-T02; PD-Y1-T03; PD-Y1-T04; PD-Y1-T05</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>106</x:v>
@@ -15450,7 +15450,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>PD-Y5-G04</x:v>
+        <x:v>PD-Y5-T04</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>21</x:v>
@@ -15491,7 +15491,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>ARC-Y2-G09; ARC-Y2-G10; ARC-Y2-G11</x:v>
+        <x:v>ARC-Y2-T09; ARC-Y2-T10; ARC-Y2-T11</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>69</x:v>
@@ -15532,7 +15532,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K24" s="51" t="str">
-        <x:v>LLS-Y2-G01; LLS-Y2-G02; LLS-Y2-G03</x:v>
+        <x:v>LLS-Y2-T01; LLS-Y2-T02; LLS-Y2-T03</x:v>
       </x:c>
       <x:c r="L24" s="51" t="n">
         <x:v>66</x:v>
@@ -15557,7 +15557,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re81d0c1c06e243e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R013a25ca85514a9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15830,7 +15830,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>GM-Y5-G01; GM-Y5-G02</x:v>
+        <x:v>GM-Y5-T01; GM-Y5-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>37</x:v>
@@ -15855,7 +15855,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d00db2ad43740d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10b3730704d648b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16136,7 +16136,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PGD-Y3-G01; PGD-Y3-G02; PGD-Y3-G03; MSC-Y3-G01; MSC-Y3-G02; PHD-Y3-G01; PHD-Y3-G02; PHD-Y3-G03; PHD-Y3-G04</x:v>
+        <x:v>PGD-Y3-T01; PGD-Y3-T02; PGD-Y3-T03; MSC-Y3-T01; MSC-Y3-T02; PHD-Y3-T01; PHD-Y3-T02; PHD-Y3-T03; PHD-Y3-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>197</x:v>
@@ -16177,7 +16177,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MCT-Y1-G01; MCT-Y1-G02; MCT-Y1-G03; MCT-Y1-G04; MCT-Y1-G05; MCT-Y1-G06; MCT-Y1-G07; MCT-Y1-G08</x:v>
+        <x:v>MCT-Y1-T01; MCT-Y1-T02; MCT-Y1-T03; MCT-Y1-T04; MCT-Y1-T05; MCT-Y1-T06; MCT-Y1-T07; MCT-Y1-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>192</x:v>
@@ -16218,7 +16218,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MCT-Y1-G09; MCT-Y1-G10; MCT-Y1-G11; MCT-Y1-G12</x:v>
+        <x:v>MCT-Y1-T09; MCT-Y1-T10; MCT-Y1-T11; MCT-Y1-T12</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>96</x:v>
@@ -16243,7 +16243,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf786c042c6fe4ecd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4589a4e690f74e84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16528,7 +16528,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MSC-Y4-G01; MSC-Y4-G02</x:v>
+        <x:v>MSC-Y4-T01; MSC-Y4-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>46</x:v>
@@ -16569,7 +16569,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DMET-Y4-G01; DMET-Y4-G02; DMET-Y4-G03; DMET-Y4-G04; DMET-Y4-G05; DMET-Y4-G06; DMET-Y4-G07; DMET-Y4-G08</x:v>
+        <x:v>DMET-Y4-T01; DMET-Y4-T02; DMET-Y4-T03; DMET-Y4-T04; DMET-Y4-T05; DMET-Y4-T06; DMET-Y4-T07; DMET-Y4-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>192</x:v>
@@ -16610,7 +16610,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DMET-Y4-G09; DMET-Y4-G10</x:v>
+        <x:v>DMET-Y4-T09; DMET-Y4-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>46</x:v>
@@ -16651,7 +16651,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>GM-Y2-G01; GM-Y2-G02</x:v>
+        <x:v>GM-Y2-T01; GM-Y2-T02</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>43</x:v>
@@ -16676,7 +16676,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R916937094a0646c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6060abf4e1d04ac8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16957,7 +16957,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DEN-Y4-G01; DEN-Y4-G02</x:v>
+        <x:v>DEN-Y4-T01; DEN-Y4-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>41</x:v>
@@ -16998,7 +16998,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CPH-Y3-G03</x:v>
+        <x:v>CPH-Y3-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>24</x:v>
@@ -17039,7 +17039,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PHR-Y3-G01; PHR-Y3-G02; PHR-Y3-G03; PHR-Y3-G04; BIO-Y3-G01; BIO-Y3-G02; BIO-Y3-G03; CPH-Y3-G01; CPH-Y3-G02</x:v>
+        <x:v>PHR-Y3-T01; PHR-Y3-T02; PHR-Y3-T03; PHR-Y3-T04; BIO-Y3-T01; BIO-Y3-T02; BIO-Y3-T03; CPH-Y3-T01; CPH-Y3-T02</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>189</x:v>
@@ -17064,7 +17064,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43c54371298b4548"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19e45fe99d944f3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17345,7 +17345,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>LLS-Y1-G01; LLS-Y1-G02; LLS-Y1-G03</x:v>
+        <x:v>LLS-Y1-T01; LLS-Y1-T02; LLS-Y1-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>69</x:v>
@@ -17386,7 +17386,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CPH-Y4-G01; CPH-Y4-G02; CPH-Y4-G03</x:v>
+        <x:v>CPH-Y4-T01; CPH-Y4-T02; CPH-Y4-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>70</x:v>
@@ -17427,7 +17427,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PHR-Y3-G01; PHR-Y3-G02; PHR-Y3-G03; PHR-Y3-G04</x:v>
+        <x:v>PHR-Y3-T01; PHR-Y3-T02; PHR-Y3-T03; PHR-Y3-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>84</x:v>
@@ -17452,7 +17452,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9fbce0bfb9143e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fe593ff2cfb4d0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17729,7 +17729,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MAT-Y5-G09; MAT-Y5-G10</x:v>
+        <x:v>MAT-Y5-T09; MAT-Y5-T10</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>46</x:v>
@@ -17770,7 +17770,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MAT-Y5-G01; MAT-Y5-G02; MAT-Y5-G03; MAT-Y5-G04; MAT-Y5-G05; MAT-Y5-G06; MAT-Y5-G07; MAT-Y5-G08</x:v>
+        <x:v>MAT-Y5-T01; MAT-Y5-T02; MAT-Y5-T03; MAT-Y5-T04; MAT-Y5-T05; MAT-Y5-T06; MAT-Y5-T07; MAT-Y5-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>191</x:v>
@@ -17795,7 +17795,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b8e22eea6284468"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R691846fa15374b3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18092,7 +18092,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CSE-Y1-G01; CSE-Y1-G02; CSE-Y1-G03; CSE-Y1-G04; CSE-Y1-G05; CSE-Y1-G06; CSE-Y1-G07; CSE-Y1-G08</x:v>
+        <x:v>CSE-Y1-T01; CSE-Y1-T02; CSE-Y1-T03; CSE-Y1-T04; CSE-Y1-T05; CSE-Y1-T06; CSE-Y1-T07; CSE-Y1-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>190</x:v>
@@ -18133,7 +18133,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DPE-Y2-G01; DPE-Y2-G02; DPE-Y2-G03; DPE-Y2-G04; DPE-Y2-G05; DPE-Y2-G06; DPE-Y2-G07; DPE-Y2-G08</x:v>
+        <x:v>DPE-Y2-T01; DPE-Y2-T02; DPE-Y2-T03; DPE-Y2-T04; DPE-Y2-T05; DPE-Y2-T06; DPE-Y2-T07; DPE-Y2-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>190</x:v>
@@ -18174,7 +18174,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PD-Y3-G01; PD-Y3-G02; PD-Y3-G03; PD-Y3-G04</x:v>
+        <x:v>PD-Y3-T01; PD-Y3-T02; PD-Y3-T03; PD-Y3-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>98</x:v>
@@ -18215,7 +18215,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>DPE-Y2-G09; DPE-Y2-G10; DPE-Y2-G11; DPE-Y2-G12</x:v>
+        <x:v>DPE-Y2-T09; DPE-Y2-T10; DPE-Y2-T11; DPE-Y2-T12</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>92</x:v>
@@ -18256,7 +18256,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>ELX-Y2-G09; ELX-Y2-G10; ELX-Y2-G11</x:v>
+        <x:v>ELX-Y2-T09; ELX-Y2-T10; ELX-Y2-T11</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>71</x:v>
@@ -18297,7 +18297,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>CSE-Y1-G09; CSE-Y1-G10; CSE-Y1-G11; CSE-Y1-G12</x:v>
+        <x:v>CSE-Y1-T09; CSE-Y1-T10; CSE-Y1-T11; CSE-Y1-T12</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>92</x:v>
@@ -18338,7 +18338,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>ELX-Y2-G01; ELX-Y2-G02; ELX-Y2-G03; ELX-Y2-G04; ELX-Y2-G05; ELX-Y2-G06; ELX-Y2-G07; ELX-Y2-G08</x:v>
+        <x:v>ELX-Y2-T01; ELX-Y2-T02; ELX-Y2-T03; ELX-Y2-T04; ELX-Y2-T05; ELX-Y2-T06; ELX-Y2-T07; ELX-Y2-T08</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>192</x:v>
@@ -18363,7 +18363,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reff870a199a24042"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28f75034922f4f42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18660,7 +18660,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>LLS-Y4-G01; LLS-Y4-G02; LLS-Y4-G03</x:v>
+        <x:v>LLS-Y4-T01; LLS-Y4-T02; LLS-Y4-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>59</x:v>
@@ -18701,7 +18701,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CIV-Y3-G09; CIV-Y3-G10; CIV-Y3-G11</x:v>
+        <x:v>CIV-Y3-T09; CIV-Y3-T10; CIV-Y3-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>72</x:v>
@@ -18742,7 +18742,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PD-Y3-G03; PD-Y3-G04</x:v>
+        <x:v>PD-Y3-T03; PD-Y3-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>48</x:v>
@@ -18783,7 +18783,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>MCT-Y4-G01; MCT-Y4-G02; MCT-Y4-G03; MCT-Y4-G04; MCT-Y4-G05; MCT-Y4-G06; MCT-Y4-G07; MCT-Y4-G08</x:v>
+        <x:v>MCT-Y4-T01; MCT-Y4-T02; MCT-Y4-T03; MCT-Y4-T04; MCT-Y4-T05; MCT-Y4-T06; MCT-Y4-T07; MCT-Y4-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>200</x:v>
@@ -18824,7 +18824,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>CIV-Y3-G01; CIV-Y3-G02; CIV-Y3-G03; CIV-Y3-G04; CIV-Y3-G05; CIV-Y3-G06; CIV-Y3-G07; CIV-Y3-G08</x:v>
+        <x:v>CIV-Y3-T01; CIV-Y3-T02; CIV-Y3-T03; CIV-Y3-T04; CIV-Y3-T05; CIV-Y3-T06; CIV-Y3-T07; CIV-Y3-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>196</x:v>
@@ -18865,7 +18865,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>MCT-Y4-G09; MCT-Y4-G10</x:v>
+        <x:v>MCT-Y4-T09; MCT-Y4-T10</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>50</x:v>
@@ -18906,7 +18906,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>GD-Y3-G01; GD-Y3-G02; MD-Y3-G01; MD-Y3-G02; MD-Y3-G03; MD-Y3-G04; PD-Y3-G01; PD-Y3-G02</x:v>
+        <x:v>GD-Y3-T01; GD-Y3-T02; MD-Y3-T01; MD-Y3-T02; MD-Y3-T03; MD-Y3-T04; PD-Y3-T01; PD-Y3-T02</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>189</x:v>
@@ -18931,7 +18931,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad15edf9fcfc46ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb4c853ab96b48b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19236,7 +19236,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>ARC-Y2-G01; ARC-Y2-G02; ARC-Y2-G03; ARC-Y2-G04; ARC-Y2-G05; ARC-Y2-G06; ARC-Y2-G07; ARC-Y2-G08</x:v>
+        <x:v>ARC-Y2-T01; ARC-Y2-T02; ARC-Y2-T03; ARC-Y2-T04; ARC-Y2-T05; ARC-Y2-T06; ARC-Y2-T07; ARC-Y2-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>190</x:v>
@@ -19277,7 +19277,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>BIO-Y1-G01; BIO-Y1-G02; BIO-Y1-G03</x:v>
+        <x:v>BIO-Y1-T01; BIO-Y1-T02; BIO-Y1-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>62</x:v>
@@ -19318,7 +19318,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>NET-Y1-G01; NET-Y1-G02; NET-Y1-G03; NET-Y1-G04; NET-Y1-G05; NET-Y1-G06; NET-Y1-G07; NET-Y1-G08</x:v>
+        <x:v>NET-Y1-T01; NET-Y1-T02; NET-Y1-T03; NET-Y1-T04; NET-Y1-T05; NET-Y1-T06; NET-Y1-T07; NET-Y1-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>192</x:v>
@@ -19359,7 +19359,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>PD-Y1-G01; PD-Y1-G02; PD-Y1-G03; PD-Y1-G04; PD-Y1-G05</x:v>
+        <x:v>PD-Y1-T01; PD-Y1-T02; PD-Y1-T03; PD-Y1-T04; PD-Y1-T05</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>106</x:v>
@@ -19400,7 +19400,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>NET-Y1-G09; NET-Y1-G10; NET-Y1-G11; NET-Y1-G12</x:v>
+        <x:v>NET-Y1-T09; NET-Y1-T10; NET-Y1-T11; NET-Y1-T12</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>93</x:v>
@@ -19441,7 +19441,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>CSE-Y5-G09; CSE-Y5-G10; DMET-Y5-G01; DMET-Y5-G02; DMET-Y5-G03; DMET-Y5-G04; DMET-Y5-G05; DMET-Y5-G06</x:v>
+        <x:v>CSE-Y5-T09; CSE-Y5-T10; DMET-Y5-T01; DMET-Y5-T02; DMET-Y5-T03; DMET-Y5-T04; DMET-Y5-T05; DMET-Y5-T06</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>196</x:v>
@@ -19482,7 +19482,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>DMET-Y5-G07; DMET-Y5-G08; DMET-Y5-G09</x:v>
+        <x:v>DMET-Y5-T07; DMET-Y5-T08; DMET-Y5-T09</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>74</x:v>
@@ -19523,7 +19523,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>CSE-Y5-G01; CSE-Y5-G02; CSE-Y5-G03; CSE-Y5-G04; CSE-Y5-G05; CSE-Y5-G06; CSE-Y5-G07; CSE-Y5-G08</x:v>
+        <x:v>CSE-Y5-T01; CSE-Y5-T02; CSE-Y5-T03; CSE-Y5-T04; CSE-Y5-T05; CSE-Y5-T06; CSE-Y5-T07; CSE-Y5-T08</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>185</x:v>
@@ -19564,7 +19564,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K24" s="51" t="str">
-        <x:v>ARC-Y2-G09; ARC-Y2-G10; ARC-Y2-G11</x:v>
+        <x:v>ARC-Y2-T09; ARC-Y2-T10; ARC-Y2-T11</x:v>
       </x:c>
       <x:c r="L24" s="51" t="n">
         <x:v>69</x:v>
@@ -19589,7 +19589,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R539a51bcd521480e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31fc621472ac4d27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19862,7 +19862,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>GM-Y5-G01; GM-Y5-G02</x:v>
+        <x:v>GM-Y5-T01; GM-Y5-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>37</x:v>
@@ -19887,7 +19887,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb630cc2fcd3c4151"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3417eeefdd344980"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20172,7 +20172,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>BI-Y4-G01; BI-Y4-G02; BI-Y4-G03; BI-Y4-G04</x:v>
+        <x:v>BI-Y4-T01; BI-Y4-T02; BI-Y4-T03; BI-Y4-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>80</x:v>
@@ -20213,7 +20213,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MAT-Y4-G01; MAT-Y4-G02; MAT-Y4-G03; MAT-Y4-G04; MAT-Y4-G05; MAT-Y4-G06; MAT-Y4-G07; MAT-Y4-G08</x:v>
+        <x:v>MAT-Y4-T01; MAT-Y4-T02; MAT-Y4-T03; MAT-Y4-T04; MAT-Y4-T05; MAT-Y4-T06; MAT-Y4-T07; MAT-Y4-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>184</x:v>
@@ -20254,7 +20254,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MAT-Y4-G09; MAT-Y4-G10; MAT-Y4-G11</x:v>
+        <x:v>MAT-Y4-T09; MAT-Y4-T10; MAT-Y4-T11</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>67</x:v>
@@ -20295,7 +20295,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>BIO-Y5-G01; BIO-Y5-G02; BIO-Y5-G03</x:v>
+        <x:v>BIO-Y5-T01; BIO-Y5-T02; BIO-Y5-T03</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>51</x:v>
@@ -20320,7 +20320,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b0e9bd770a84c02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0746d0fac70b4ca7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20597,7 +20597,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PHD-Y2-G01; PHD-Y2-G02; PHD-Y2-G03; PHD-Y2-G04</x:v>
+        <x:v>PHD-Y2-T01; PHD-Y2-T02; PHD-Y2-T03; PHD-Y2-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>97</x:v>
@@ -20638,7 +20638,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>LLS-Y2-G01; LLS-Y2-G02; LLS-Y2-G03</x:v>
+        <x:v>LLS-Y2-T01; LLS-Y2-T02; LLS-Y2-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>66</x:v>
@@ -20663,7 +20663,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6989891f88224bc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1547484ab24a4239"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20940,7 +20940,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PHD-Y4-G01; PHD-Y4-G02; PHD-Y4-G03; PHD-Y4-G04</x:v>
+        <x:v>PHD-Y4-T01; PHD-Y4-T02; PHD-Y4-T03; PHD-Y4-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>88</x:v>
@@ -20981,7 +20981,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DEN-Y2-G01; DEN-Y2-G02</x:v>
+        <x:v>DEN-Y2-T01; DEN-Y2-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>44</x:v>
@@ -21006,7 +21006,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd6f8ba9b2814d73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a42784b79c2480c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21291,7 +21291,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MCT-Y5-G01; MCT-Y5-G02; MCT-Y5-G03; MCT-Y5-G04; MCT-Y5-G05; MCT-Y5-G06; MCT-Y5-G07; MCT-Y5-G08</x:v>
+        <x:v>MCT-Y5-T01; MCT-Y5-T02; MCT-Y5-T03; MCT-Y5-T04; MCT-Y5-T05; MCT-Y5-T06; MCT-Y5-T07; MCT-Y5-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>190</x:v>
@@ -21332,7 +21332,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MCT-Y5-G09; MCT-Y5-G10</x:v>
+        <x:v>MCT-Y5-T09; MCT-Y5-T10</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>46</x:v>
@@ -21373,7 +21373,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>NET-Y3-G01; NET-Y3-G02; NET-Y3-G03; NET-Y3-G04; NET-Y3-G05; NET-Y3-G06; NET-Y3-G07; NET-Y3-G08</x:v>
+        <x:v>NET-Y3-T01; NET-Y3-T02; NET-Y3-T03; NET-Y3-T04; NET-Y3-T05; NET-Y3-T06; NET-Y3-T07; NET-Y3-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>190</x:v>
@@ -21414,7 +21414,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>NET-Y3-G09; NET-Y3-G10; NET-Y3-G11</x:v>
+        <x:v>NET-Y3-T09; NET-Y3-T10; NET-Y3-T11</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>69</x:v>
@@ -21439,7 +21439,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fbde53e583047ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc32067495e7a4143"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21724,7 +21724,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MAT-Y5-G09; MAT-Y5-G10</x:v>
+        <x:v>MAT-Y5-T09; MAT-Y5-T10</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>46</x:v>
@@ -21765,7 +21765,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>TBM-Y4-G04</x:v>
+        <x:v>TBM-Y4-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>21</x:v>
@@ -21806,7 +21806,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MAT-Y5-G01; MAT-Y5-G02; MAT-Y5-G03; MAT-Y5-G04; MAT-Y5-G05; MAT-Y5-G06; MAT-Y5-G07; MAT-Y5-G08</x:v>
+        <x:v>MAT-Y5-T01; MAT-Y5-T02; MAT-Y5-T03; MAT-Y5-T04; MAT-Y5-T05; MAT-Y5-T06; MAT-Y5-T07; MAT-Y5-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>191</x:v>
@@ -21847,7 +21847,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>GM-Y4-G01; GM-Y4-G02; BI-Y4-G01; BI-Y4-G02; BI-Y4-G03; BI-Y4-G04; TBM-Y4-G01; TBM-Y4-G02; TBM-Y4-G03</x:v>
+        <x:v>GM-Y4-T01; GM-Y4-T02; BI-Y4-T01; BI-Y4-T02; BI-Y4-T03; BI-Y4-T04; TBM-Y4-T01; TBM-Y4-T02; TBM-Y4-T03</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>182</x:v>
@@ -21872,7 +21872,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0bbbe8ac1394e93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd776377fd6a44425"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22153,7 +22153,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>BI-Y3-G01; BI-Y3-G02; BI-Y3-G03; BI-Y3-G04</x:v>
+        <x:v>BI-Y3-T01; BI-Y3-T02; BI-Y3-T03; BI-Y3-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>86</x:v>
@@ -22194,7 +22194,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>BIO-Y2-G01; BIO-Y2-G02; BIO-Y2-G03</x:v>
+        <x:v>BIO-Y2-T01; BIO-Y2-T02; BIO-Y2-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>58</x:v>
@@ -22235,7 +22235,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PHD-Y5-G01; PHD-Y5-G02; PHD-Y5-G03; PHD-Y5-G04</x:v>
+        <x:v>PHD-Y5-T01; PHD-Y5-T02; PHD-Y5-T03; PHD-Y5-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>82</x:v>
@@ -22260,7 +22260,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaca8e40ea204a32"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd81b728d05254df5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22541,7 +22541,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>TBM-Y1-G03; TBM-Y1-G04</x:v>
+        <x:v>TBM-Y1-T03; TBM-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>48</x:v>
@@ -22582,7 +22582,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>GM-Y1-G01; GM-Y1-G02; BI-Y1-G01; BI-Y1-G02; BI-Y1-G03; BI-Y1-G04; TBM-Y1-G01; TBM-Y1-G02</x:v>
+        <x:v>GM-Y1-T01; GM-Y1-T02; BI-Y1-T01; BI-Y1-T02; BI-Y1-T03; BI-Y1-T04; TBM-Y1-T01; TBM-Y1-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>187</x:v>
@@ -22623,7 +22623,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MD-Y1-G01; MD-Y1-G02; MD-Y1-G03; MD-Y1-G04; MD-Y1-G05</x:v>
+        <x:v>MD-Y1-T01; MD-Y1-T02; MD-Y1-T03; MD-Y1-T04; MD-Y1-T05</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>104</x:v>
@@ -22648,7 +22648,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c58f3129cba41a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb334b3456e94737"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22945,7 +22945,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>ARC-Y1-G01; ARC-Y1-G02; ARC-Y1-G03; ARC-Y1-G04; ARC-Y1-G05; ARC-Y1-G06; ARC-Y1-G07; ARC-Y1-G08</x:v>
+        <x:v>ARC-Y1-T01; ARC-Y1-T02; ARC-Y1-T03; ARC-Y1-T04; ARC-Y1-T05; ARC-Y1-T06; ARC-Y1-T07; ARC-Y1-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>199</x:v>
@@ -22986,7 +22986,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>PHD-Y2-G04</x:v>
+        <x:v>PHD-Y2-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>24</x:v>
@@ -23027,7 +23027,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MSC-Y1-G01; MSC-Y1-G02; MSC-Y1-G03</x:v>
+        <x:v>MSC-Y1-T01; MSC-Y1-T02; MSC-Y1-T03</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>54</x:v>
@@ -23068,7 +23068,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>PGD-Y2-G01; PGD-Y2-G02; PGD-Y2-G03; MSC-Y2-G01; MSC-Y2-G02; PHD-Y2-G01; PHD-Y2-G02; PHD-Y2-G03</x:v>
+        <x:v>PGD-Y2-T01; PGD-Y2-T02; PGD-Y2-T03; MSC-Y2-T01; MSC-Y2-T02; PHD-Y2-T01; PHD-Y2-T02; PHD-Y2-T03</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>183</x:v>
@@ -23109,7 +23109,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>NET-Y2-G09; NET-Y2-G10; NET-Y2-G11</x:v>
+        <x:v>NET-Y2-T09; NET-Y2-T10; NET-Y2-T11</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>72</x:v>
@@ -23150,7 +23150,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>ARC-Y1-G09; ARC-Y1-G10; ARC-Y1-G11</x:v>
+        <x:v>ARC-Y1-T09; ARC-Y1-T10; ARC-Y1-T11</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>72</x:v>
@@ -23191,7 +23191,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>NET-Y2-G01; NET-Y2-G02; NET-Y2-G03; NET-Y2-G04; NET-Y2-G05; NET-Y2-G06; NET-Y2-G07; NET-Y2-G08</x:v>
+        <x:v>NET-Y2-T01; NET-Y2-T02; NET-Y2-T03; NET-Y2-T04; NET-Y2-T05; NET-Y2-T06; NET-Y2-T07; NET-Y2-T08</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>200</x:v>
@@ -23216,7 +23216,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99d3d02f493d4913"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba7305c89d8f4e0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23489,7 +23489,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>TBM-Y1-G01; TBM-Y1-G02; TBM-Y1-G03; TBM-Y1-G04</x:v>
+        <x:v>TBM-Y1-T01; TBM-Y1-T02; TBM-Y1-T03; TBM-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>96</x:v>
@@ -23514,7 +23514,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab917dd5ceae4a97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0bc501f2c5b4a3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23799,7 +23799,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CIV-Y1-G09; CIV-Y1-G10; CIV-Y1-G11; CIV-Y1-G12</x:v>
+        <x:v>CIV-Y1-T09; CIV-Y1-T10; CIV-Y1-T11; CIV-Y1-T12</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>96</x:v>
@@ -23840,7 +23840,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CSE-Y3-G01; CSE-Y3-G02; CSE-Y3-G03; CSE-Y3-G04; CSE-Y3-G05; CSE-Y3-G06; CSE-Y3-G07; CSE-Y3-G08</x:v>
+        <x:v>CSE-Y3-T01; CSE-Y3-T02; CSE-Y3-T03; CSE-Y3-T04; CSE-Y3-T05; CSE-Y3-T06; CSE-Y3-T07; CSE-Y3-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>186</x:v>
@@ -23881,7 +23881,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CSE-Y3-G09; CSE-Y3-G10; CSE-Y3-G11</x:v>
+        <x:v>CSE-Y3-T09; CSE-Y3-T10; CSE-Y3-T11</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>69</x:v>
@@ -23922,7 +23922,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>CIV-Y1-G01; CIV-Y1-G02; CIV-Y1-G03; CIV-Y1-G04; CIV-Y1-G05; CIV-Y1-G06; CIV-Y1-G07; CIV-Y1-G08</x:v>
+        <x:v>CIV-Y1-T01; CIV-Y1-T02; CIV-Y1-T03; CIV-Y1-T04; CIV-Y1-T05; CIV-Y1-T06; CIV-Y1-T07; CIV-Y1-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>199</x:v>
@@ -23947,7 +23947,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6accdeacec064854"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca19d60623054758"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24220,7 +24220,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DEN-Y1-G01; DEN-Y1-G02</x:v>
+        <x:v>DEN-Y1-T01; DEN-Y1-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>46</x:v>
@@ -24245,7 +24245,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0732e8e2ab684db6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R908b26e0b69541a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24530,7 +24530,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PD-Y1-G03; PD-Y1-G04; PD-Y1-G05</x:v>
+        <x:v>PD-Y1-T03; PD-Y1-T04; PD-Y1-T05</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>63</x:v>
@@ -24571,7 +24571,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>PHR-Y2-G01; PHR-Y2-G02; PHR-Y2-G03; PHR-Y2-G04; BIO-Y2-G01; BIO-Y2-G02; BIO-Y2-G03; CPH-Y2-G01; CPH-Y2-G02</x:v>
+        <x:v>PHR-Y2-T01; PHR-Y2-T02; PHR-Y2-T03; PHR-Y2-T04; BIO-Y2-T01; BIO-Y2-T02; BIO-Y2-T03; CPH-Y2-T01; CPH-Y2-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>184</x:v>
@@ -24612,7 +24612,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CPH-Y2-G03; CPH-Y2-G04</x:v>
+        <x:v>CPH-Y2-T03; CPH-Y2-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>38</x:v>
@@ -24653,7 +24653,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>GD-Y1-G01; GD-Y1-G02; MD-Y1-G01; MD-Y1-G02; MD-Y1-G03; MD-Y1-G04; MD-Y1-G05; PD-Y1-G01; PD-Y1-G02</x:v>
+        <x:v>GD-Y1-T01; GD-Y1-T02; MD-Y1-T01; MD-Y1-T02; MD-Y1-T03; MD-Y1-T04; MD-Y1-T05; PD-Y1-T01; PD-Y1-T02</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>195</x:v>
@@ -24678,7 +24678,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d4d1aacf3824f4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f440626a34d48a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24967,7 +24967,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MSC-Y5-G01; MSC-Y5-G02</x:v>
+        <x:v>MSC-Y5-T01; MSC-Y5-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>44</x:v>
@@ -25008,7 +25008,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>COM-Y4-G09; COM-Y4-G10</x:v>
+        <x:v>COM-Y4-T09; COM-Y4-T10</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>46</x:v>
@@ -25049,7 +25049,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DMET-Y5-G01; DMET-Y5-G02; DMET-Y5-G03; DMET-Y5-G04; DMET-Y5-G05; DMET-Y5-G06; DMET-Y5-G07; DMET-Y5-G08</x:v>
+        <x:v>DMET-Y5-T01; DMET-Y5-T02; DMET-Y5-T03; DMET-Y5-T04; DMET-Y5-T05; DMET-Y5-T06; DMET-Y5-T07; DMET-Y5-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>200</x:v>
@@ -25090,7 +25090,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>COM-Y4-G01; COM-Y4-G02; COM-Y4-G03; COM-Y4-G04; COM-Y4-G05; COM-Y4-G06; COM-Y4-G07; COM-Y4-G08</x:v>
+        <x:v>COM-Y4-T01; COM-Y4-T02; COM-Y4-T03; COM-Y4-T04; COM-Y4-T05; COM-Y4-T06; COM-Y4-T07; COM-Y4-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>187</x:v>
@@ -25131,7 +25131,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>DMET-Y5-G09</x:v>
+        <x:v>DMET-Y5-T09</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>24</x:v>
@@ -25156,7 +25156,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref77d27449594304"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra716569f552b4d18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25433,7 +25433,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DEN-Y1-G01; DEN-Y1-G02</x:v>
+        <x:v>DEN-Y1-T01; DEN-Y1-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>46</x:v>
@@ -25474,7 +25474,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CPH-Y3-G01; CPH-Y3-G02; CPH-Y3-G03</x:v>
+        <x:v>CPH-Y3-T01; CPH-Y3-T02; CPH-Y3-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>74</x:v>
@@ -25499,7 +25499,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76dbe8b68615431c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb275d1e0e8c4aec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25784,7 +25784,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CIV-Y3-G09; CIV-Y3-G10; CIV-Y3-G11</x:v>
+        <x:v>CIV-Y3-T09; CIV-Y3-T10; CIV-Y3-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>72</x:v>
@@ -25825,7 +25825,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CIV-Y3-G01; CIV-Y3-G02; CIV-Y3-G03; CIV-Y3-G04; CIV-Y3-G05; CIV-Y3-G06; CIV-Y3-G07; CIV-Y3-G08</x:v>
+        <x:v>CIV-Y3-T01; CIV-Y3-T02; CIV-Y3-T03; CIV-Y3-T04; CIV-Y3-T05; CIV-Y3-T06; CIV-Y3-T07; CIV-Y3-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>196</x:v>
@@ -25866,7 +25866,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MCT-Y4-G09; MCT-Y4-G10</x:v>
+        <x:v>MCT-Y4-T09; MCT-Y4-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>50</x:v>
@@ -25907,7 +25907,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>MCT-Y4-G01; MCT-Y4-G02; MCT-Y4-G03; MCT-Y4-G04; MCT-Y4-G05; MCT-Y4-G06; MCT-Y4-G07; MCT-Y4-G08</x:v>
+        <x:v>MCT-Y4-T01; MCT-Y4-T02; MCT-Y4-T03; MCT-Y4-T04; MCT-Y4-T05; MCT-Y4-T06; MCT-Y4-T07; MCT-Y4-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>200</x:v>
@@ -25932,7 +25932,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86f2815d83e147be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebae08a910eb4139"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26213,7 +26213,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CIV-Y2-G01; CIV-Y2-G02; CIV-Y2-G03; CIV-Y2-G04; CIV-Y2-G05; CIV-Y2-G06; CIV-Y2-G07; CIV-Y2-G08</x:v>
+        <x:v>CIV-Y2-T01; CIV-Y2-T02; CIV-Y2-T03; CIV-Y2-T04; CIV-Y2-T05; CIV-Y2-T06; CIV-Y2-T07; CIV-Y2-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>190</x:v>
@@ -26254,7 +26254,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>PHR-Y2-G01; PHR-Y2-G02; PHR-Y2-G03; PHR-Y2-G04</x:v>
+        <x:v>PHR-Y2-T01; PHR-Y2-T02; PHR-Y2-T03; PHR-Y2-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>88</x:v>
@@ -26295,7 +26295,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CIV-Y2-G09; CIV-Y2-G10; CIV-Y2-G11; CIV-Y2-G12</x:v>
+        <x:v>CIV-Y2-T09; CIV-Y2-T10; CIV-Y2-T11; CIV-Y2-T12</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>92</x:v>
@@ -26320,7 +26320,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cb39bf43e2b46a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf187b4980184907"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26605,7 +26605,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DPE-Y5-G01; DPE-Y5-G02; DPE-Y5-G03; DPE-Y5-G04; DPE-Y5-G05; DPE-Y5-G06; DPE-Y5-G07; DPE-Y5-G08</x:v>
+        <x:v>DPE-Y5-T01; DPE-Y5-T02; DPE-Y5-T03; DPE-Y5-T04; DPE-Y5-T05; DPE-Y5-T06; DPE-Y5-T07; DPE-Y5-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>194</x:v>
@@ -26646,7 +26646,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ELX-Y5-G01; ELX-Y5-G02; ELX-Y5-G03; ELX-Y5-G04; ELX-Y5-G05; ELX-Y5-G06; ELX-Y5-G07; ELX-Y5-G08</x:v>
+        <x:v>ELX-Y5-T01; ELX-Y5-T02; ELX-Y5-T03; ELX-Y5-T04; ELX-Y5-T05; ELX-Y5-T06; ELX-Y5-T07; ELX-Y5-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>200</x:v>
@@ -26687,7 +26687,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DPE-Y5-G09; DPE-Y5-G10</x:v>
+        <x:v>DPE-Y5-T09; DPE-Y5-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>48</x:v>
@@ -26728,7 +26728,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>ELX-Y5-G09</x:v>
+        <x:v>ELX-Y5-T09</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>24</x:v>
@@ -26753,7 +26753,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9968a36a675463e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02b76b32b1624093"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27034,7 +27034,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CIV-Y2-G01; CIV-Y2-G02; CIV-Y2-G03; CIV-Y2-G04; CIV-Y2-G05; CIV-Y2-G06; CIV-Y2-G07; CIV-Y2-G08</x:v>
+        <x:v>CIV-Y2-T01; CIV-Y2-T02; CIV-Y2-T03; CIV-Y2-T04; CIV-Y2-T05; CIV-Y2-T06; CIV-Y2-T07; CIV-Y2-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>190</x:v>
@@ -27075,7 +27075,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CIV-Y2-G09; CIV-Y2-G10; CIV-Y2-G11; CIV-Y2-G12</x:v>
+        <x:v>CIV-Y2-T09; CIV-Y2-T10; CIV-Y2-T11; CIV-Y2-T12</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>92</x:v>
@@ -27116,7 +27116,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PHR-Y2-G01; PHR-Y2-G02; PHR-Y2-G03; PHR-Y2-G04</x:v>
+        <x:v>PHR-Y2-T01; PHR-Y2-T02; PHR-Y2-T03; PHR-Y2-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>88</x:v>
@@ -27141,7 +27141,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d7a0cdeddcd48bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a73a6c836de426f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27422,7 +27422,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MAT-Y2-G01; MAT-Y2-G02; MAT-Y2-G03; MAT-Y2-G04; MAT-Y2-G05; MAT-Y2-G06; MAT-Y2-G07; MAT-Y2-G08</x:v>
+        <x:v>MAT-Y2-T01; MAT-Y2-T02; MAT-Y2-T03; MAT-Y2-T04; MAT-Y2-T05; MAT-Y2-T06; MAT-Y2-T07; MAT-Y2-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>184</x:v>
@@ -27463,7 +27463,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>TBM-Y4-G01; TBM-Y4-G02; TBM-Y4-G03; TBM-Y4-G04</x:v>
+        <x:v>TBM-Y4-T01; TBM-Y4-T02; TBM-Y4-T03; TBM-Y4-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>84</x:v>
@@ -27504,7 +27504,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MAT-Y2-G09; MAT-Y2-G10; MAT-Y2-G11; MAT-Y2-G12</x:v>
+        <x:v>MAT-Y2-T09; MAT-Y2-T10; MAT-Y2-T11; MAT-Y2-T12</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>92</x:v>
@@ -27529,7 +27529,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab302629060d4f50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R882286db21ab4eb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27818,7 +27818,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PGD-Y3-G01; PGD-Y3-G02; PGD-Y3-G03</x:v>
+        <x:v>PGD-Y3-T01; PGD-Y3-T02; PGD-Y3-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>57</x:v>
@@ -27859,7 +27859,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ELX-Y3-G01; ELX-Y3-G02; ELX-Y3-G03; ELX-Y3-G04; ELX-Y3-G05; ELX-Y3-G06; ELX-Y3-G07; ELX-Y3-G08</x:v>
+        <x:v>ELX-Y3-T01; ELX-Y3-T02; ELX-Y3-T03; ELX-Y3-T04; ELX-Y3-T05; ELX-Y3-T06; ELX-Y3-T07; ELX-Y3-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>200</x:v>
@@ -27900,7 +27900,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DEN-Y3-G01; DEN-Y3-G02</x:v>
+        <x:v>DEN-Y3-T01; DEN-Y3-T02</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>43</x:v>
@@ -27941,7 +27941,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>MD-Y3-G01; MD-Y3-G02; MD-Y3-G03; MD-Y3-G04</x:v>
+        <x:v>MD-Y3-T01; MD-Y3-T02; MD-Y3-T03; MD-Y3-T04</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>94</x:v>
@@ -27982,7 +27982,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>ELX-Y3-G09; ELX-Y3-G10</x:v>
+        <x:v>ELX-Y3-T09; ELX-Y3-T10</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>50</x:v>
@@ -28007,7 +28007,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf12023adefad47cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd59a898484446d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28324,7 +28324,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DPE-Y4-G09; DPE-Y4-G10; DPE-Y4-G11</x:v>
+        <x:v>DPE-Y4-T09; DPE-Y4-T10; DPE-Y4-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>69</x:v>
@@ -28365,7 +28365,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>NET-Y5-G09; NET-Y5-G10; COM-Y5-G01; COM-Y5-G02; COM-Y5-G03; COM-Y5-G04; COM-Y5-G05; COM-Y5-G06</x:v>
+        <x:v>NET-Y5-T09; NET-Y5-T10; COM-Y5-T01; COM-Y5-T02; COM-Y5-T03; COM-Y5-T04; COM-Y5-T05; COM-Y5-T06</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>194</x:v>
@@ -28406,7 +28406,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>ELX-Y5-G06; ELX-Y5-G07; ELX-Y5-G08; ELX-Y5-G09</x:v>
+        <x:v>ELX-Y5-T06; ELX-Y5-T07; ELX-Y5-T08; ELX-Y5-T09</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>99</x:v>
@@ -28447,7 +28447,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>NET-Y5-G01; NET-Y5-G02; NET-Y5-G03; NET-Y5-G04; NET-Y5-G05; NET-Y5-G06; NET-Y5-G07; NET-Y5-G08</x:v>
+        <x:v>NET-Y5-T01; NET-Y5-T02; NET-Y5-T03; NET-Y5-T04; NET-Y5-T05; NET-Y5-T06; NET-Y5-T07; NET-Y5-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>187</x:v>
@@ -28488,7 +28488,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>DPE-Y4-G01; DPE-Y4-G02; DPE-Y4-G03; DPE-Y4-G04; DPE-Y4-G05; DPE-Y4-G06; DPE-Y4-G07; DPE-Y4-G08</x:v>
+        <x:v>DPE-Y4-T01; DPE-Y4-T02; DPE-Y4-T03; DPE-Y4-T04; DPE-Y4-T05; DPE-Y4-T06; DPE-Y4-T07; DPE-Y4-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>186</x:v>
@@ -28529,7 +28529,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>ELX-Y4-G01; ELX-Y4-G02; ELX-Y4-G03; ELX-Y4-G04; ELX-Y4-G05; ELX-Y4-G06; ELX-Y4-G07; ELX-Y4-G08</x:v>
+        <x:v>ELX-Y4-T01; ELX-Y4-T02; ELX-Y4-T03; ELX-Y4-T04; ELX-Y4-T05; ELX-Y4-T06; ELX-Y4-T07; ELX-Y4-T08</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>191</x:v>
@@ -28570,7 +28570,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>ARC-Y3-G09; ARC-Y3-G10</x:v>
+        <x:v>ARC-Y3-T09; ARC-Y3-T10</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>48</x:v>
@@ -28611,7 +28611,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>PHR-Y1-G01; PHR-Y1-G02; PHR-Y1-G03; PHR-Y1-G04</x:v>
+        <x:v>PHR-Y1-T01; PHR-Y1-T02; PHR-Y1-T03; PHR-Y1-T04</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>93</x:v>
@@ -28652,7 +28652,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K24" s="51" t="str">
-        <x:v>ELX-Y4-G09; ELX-Y4-G10</x:v>
+        <x:v>ELX-Y4-T09; ELX-Y4-T10</x:v>
       </x:c>
       <x:c r="L24" s="51" t="n">
         <x:v>46</x:v>
@@ -28693,7 +28693,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K25" s="51" t="str">
-        <x:v>ARC-Y3-G01; ARC-Y3-G02; ARC-Y3-G03; ARC-Y3-G04; ARC-Y3-G05; ARC-Y3-G06; ARC-Y3-G07; ARC-Y3-G08</x:v>
+        <x:v>ARC-Y3-T01; ARC-Y3-T02; ARC-Y3-T03; ARC-Y3-T04; ARC-Y3-T05; ARC-Y3-T06; ARC-Y3-T07; ARC-Y3-T08</x:v>
       </x:c>
       <x:c r="L25" s="51" t="n">
         <x:v>198</x:v>
@@ -28734,7 +28734,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K26" s="51" t="str">
-        <x:v>PD-Y5-G01; PD-Y5-G02; PD-Y5-G03; PD-Y5-G04</x:v>
+        <x:v>PD-Y5-T01; PD-Y5-T02; PD-Y5-T03; PD-Y5-T04</x:v>
       </x:c>
       <x:c r="L26" s="51" t="n">
         <x:v>87</x:v>
@@ -28775,7 +28775,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K27" s="51" t="str">
-        <x:v>COM-Y5-G07; COM-Y5-G08; COM-Y5-G09; ELX-Y5-G01; ELX-Y5-G02; ELX-Y5-G03; ELX-Y5-G04; ELX-Y5-G05</x:v>
+        <x:v>COM-Y5-T07; COM-Y5-T08; COM-Y5-T09; ELX-Y5-T01; ELX-Y5-T02; ELX-Y5-T03; ELX-Y5-T04; ELX-Y5-T05</x:v>
       </x:c>
       <x:c r="L27" s="51" t="n">
         <x:v>197</x:v>
@@ -28800,7 +28800,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R077f009e638e4a5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47fab535fc7a47de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29077,7 +29077,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MCT-Y3-G01; MCT-Y3-G02; MCT-Y3-G03; MCT-Y3-G04; MCT-Y3-G05; MCT-Y3-G06; MCT-Y3-G07; MCT-Y3-G08</x:v>
+        <x:v>MCT-Y3-T01; MCT-Y3-T02; MCT-Y3-T03; MCT-Y3-T04; MCT-Y3-T05; MCT-Y3-T06; MCT-Y3-T07; MCT-Y3-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>192</x:v>
@@ -29118,7 +29118,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MCT-Y3-G09; MCT-Y3-G10; MCT-Y3-G11</x:v>
+        <x:v>MCT-Y3-T09; MCT-Y3-T10; MCT-Y3-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>71</x:v>
@@ -29143,7 +29143,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c2de2c805a04670"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde175c1b010b41d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29428,7 +29428,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>TBM-Y3-G01; TBM-Y3-G02; TBM-Y3-G03; TBM-Y3-G04</x:v>
+        <x:v>TBM-Y3-T01; TBM-Y3-T02; TBM-Y3-T03; TBM-Y3-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>87</x:v>
@@ -29469,7 +29469,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MSC-Y2-G01; MSC-Y2-G02</x:v>
+        <x:v>MSC-Y2-T01; MSC-Y2-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>50</x:v>
@@ -29510,7 +29510,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CIV-Y4-G01; CIV-Y4-G02; CIV-Y4-G03; CIV-Y4-G04; CIV-Y4-G05; CIV-Y4-G06; CIV-Y4-G07; CIV-Y4-G08</x:v>
+        <x:v>CIV-Y4-T01; CIV-Y4-T02; CIV-Y4-T03; CIV-Y4-T04; CIV-Y4-T05; CIV-Y4-T06; CIV-Y4-T07; CIV-Y4-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>187</x:v>
@@ -29551,7 +29551,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>CIV-Y4-G09; CIV-Y4-G10; CIV-Y4-G11</x:v>
+        <x:v>CIV-Y4-T09; CIV-Y4-T10; CIV-Y4-T11</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>69</x:v>
@@ -29576,7 +29576,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0d3f8f13f4747ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34f3edcdf1f54dd8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29849,7 +29849,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>LLS-Y5-G01; LLS-Y5-G02; LLS-Y5-G03</x:v>
+        <x:v>LLS-Y5-T01; LLS-Y5-T02; LLS-Y5-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>56</x:v>
@@ -29874,7 +29874,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4ef00eabfce4a13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2343bf3da4c42f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30147,7 +30147,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>LLS-Y1-G01; LLS-Y1-G02; LLS-Y1-G03</x:v>
+        <x:v>LLS-Y1-T01; LLS-Y1-T02; LLS-Y1-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>69</x:v>
@@ -30172,7 +30172,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6236886b01294f01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a8742b41794bb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30453,7 +30453,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CPH-Y1-G01; CPH-Y1-G02; CPH-Y1-G03; CPH-Y1-G04</x:v>
+        <x:v>CPH-Y1-T01; CPH-Y1-T02; CPH-Y1-T03; CPH-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>80</x:v>
@@ -30494,7 +30494,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>COM-Y5-G01; COM-Y5-G02; COM-Y5-G03; COM-Y5-G04; COM-Y5-G05; COM-Y5-G06; COM-Y5-G07; COM-Y5-G08</x:v>
+        <x:v>COM-Y5-T01; COM-Y5-T02; COM-Y5-T03; COM-Y5-T04; COM-Y5-T05; COM-Y5-T06; COM-Y5-T07; COM-Y5-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>196</x:v>
@@ -30535,7 +30535,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>COM-Y5-G09</x:v>
+        <x:v>COM-Y5-T09</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>24</x:v>
@@ -30560,7 +30560,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R216c080ce68b47b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc375ca1edaec473f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30845,7 +30845,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MCT-Y5-G01; MCT-Y5-G02; MCT-Y5-G03; MCT-Y5-G04; MCT-Y5-G05; MCT-Y5-G06; MCT-Y5-G07; MCT-Y5-G08</x:v>
+        <x:v>MCT-Y5-T01; MCT-Y5-T02; MCT-Y5-T03; MCT-Y5-T04; MCT-Y5-T05; MCT-Y5-T06; MCT-Y5-T07; MCT-Y5-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>190</x:v>
@@ -30886,7 +30886,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>NET-Y3-G09; NET-Y3-G10; NET-Y3-G11</x:v>
+        <x:v>NET-Y3-T09; NET-Y3-T10; NET-Y3-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>69</x:v>
@@ -30927,7 +30927,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>NET-Y3-G01; NET-Y3-G02; NET-Y3-G03; NET-Y3-G04; NET-Y3-G05; NET-Y3-G06; NET-Y3-G07; NET-Y3-G08</x:v>
+        <x:v>NET-Y3-T01; NET-Y3-T02; NET-Y3-T03; NET-Y3-T04; NET-Y3-T05; NET-Y3-T06; NET-Y3-T07; NET-Y3-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>190</x:v>
@@ -30968,7 +30968,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>MCT-Y5-G09; MCT-Y5-G10</x:v>
+        <x:v>MCT-Y5-T09; MCT-Y5-T10</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>46</x:v>
@@ -30993,7 +30993,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d673e5ef27e4dcf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bea11fe02eb41d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31282,7 +31282,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PHD-Y5-G01; PHD-Y5-G02; PHD-Y5-G03; PHD-Y5-G04</x:v>
+        <x:v>PHD-Y5-T01; PHD-Y5-T02; PHD-Y5-T03; PHD-Y5-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>82</x:v>
@@ -31323,7 +31323,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>PHR-Y4-G01; PHR-Y4-G02; PHR-Y4-G03; PHR-Y4-G04; BIO-Y4-G01; BIO-Y4-G02; BIO-Y4-G03; CPH-Y4-G01; CPH-Y4-G02</x:v>
+        <x:v>PHR-Y4-T01; PHR-Y4-T02; PHR-Y4-T03; PHR-Y4-T04; BIO-Y4-T01; BIO-Y4-T02; BIO-Y4-T03; CPH-Y4-T01; CPH-Y4-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>178</x:v>
@@ -31364,7 +31364,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>BIO-Y2-G01; BIO-Y2-G02; BIO-Y2-G03</x:v>
+        <x:v>BIO-Y2-T01; BIO-Y2-T02; BIO-Y2-T03</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>58</x:v>
@@ -31405,7 +31405,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>BI-Y3-G01; BI-Y3-G02; BI-Y3-G03; BI-Y3-G04</x:v>
+        <x:v>BI-Y3-T01; BI-Y3-T02; BI-Y3-T03; BI-Y3-T04</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>86</x:v>
@@ -31446,7 +31446,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>CPH-Y4-G03</x:v>
+        <x:v>CPH-Y4-T03</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>23</x:v>
@@ -31471,7 +31471,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16272452ef31497d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1324d7c555c94802"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31760,7 +31760,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>NET-Y2-G09; NET-Y2-G10; NET-Y2-G11</x:v>
+        <x:v>NET-Y2-T09; NET-Y2-T10; NET-Y2-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>72</x:v>
@@ -31801,7 +31801,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MSC-Y1-G01; MSC-Y1-G02; MSC-Y1-G03</x:v>
+        <x:v>MSC-Y1-T01; MSC-Y1-T02; MSC-Y1-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>54</x:v>
@@ -31842,7 +31842,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>ARC-Y1-G01; ARC-Y1-G02; ARC-Y1-G03; ARC-Y1-G04; ARC-Y1-G05; ARC-Y1-G06; ARC-Y1-G07; ARC-Y1-G08</x:v>
+        <x:v>ARC-Y1-T01; ARC-Y1-T02; ARC-Y1-T03; ARC-Y1-T04; ARC-Y1-T05; ARC-Y1-T06; ARC-Y1-T07; ARC-Y1-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>199</x:v>
@@ -31883,7 +31883,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>NET-Y2-G01; NET-Y2-G02; NET-Y2-G03; NET-Y2-G04; NET-Y2-G05; NET-Y2-G06; NET-Y2-G07; NET-Y2-G08</x:v>
+        <x:v>NET-Y2-T01; NET-Y2-T02; NET-Y2-T03; NET-Y2-T04; NET-Y2-T05; NET-Y2-T06; NET-Y2-T07; NET-Y2-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>200</x:v>
@@ -31924,7 +31924,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>ARC-Y1-G09; ARC-Y1-G10; ARC-Y1-G11</x:v>
+        <x:v>ARC-Y1-T09; ARC-Y1-T10; ARC-Y1-T11</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>72</x:v>
@@ -31949,7 +31949,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11de9dab3cc34e52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd896c4fb32c54237"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32230,7 +32230,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>BIO-Y4-G01; BIO-Y4-G02; BIO-Y4-G03</x:v>
+        <x:v>BIO-Y4-T01; BIO-Y4-T02; BIO-Y4-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>52</x:v>
@@ -32271,7 +32271,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>BI-Y5-G01; BI-Y5-G02; BI-Y5-G03; BI-Y5-G04</x:v>
+        <x:v>BI-Y5-T01; BI-Y5-T02; BI-Y5-T03; BI-Y5-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>76</x:v>
@@ -32312,7 +32312,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PHR-Y5-G01; PHR-Y5-G02; PHR-Y5-G03; PHR-Y5-G04</x:v>
+        <x:v>PHR-Y5-T01; PHR-Y5-T02; PHR-Y5-T03; PHR-Y5-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>76</x:v>
@@ -32337,7 +32337,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re06f800147a34ce5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18c42caedcfa48fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32622,7 +32622,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MCT-Y2-G01; MCT-Y2-G02; MCT-Y2-G03; MCT-Y2-G04; MCT-Y2-G05; MCT-Y2-G06; MCT-Y2-G07; MCT-Y2-G08</x:v>
+        <x:v>MCT-Y2-T01; MCT-Y2-T02; MCT-Y2-T03; MCT-Y2-T04; MCT-Y2-T05; MCT-Y2-T06; MCT-Y2-T07; MCT-Y2-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>200</x:v>
@@ -32663,7 +32663,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DMET-Y3-G09; DMET-Y3-G10</x:v>
+        <x:v>DMET-Y3-T09; DMET-Y3-T10</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>50</x:v>
@@ -32704,7 +32704,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MCT-Y2-G09; MCT-Y2-G10; MCT-Y2-G11</x:v>
+        <x:v>MCT-Y2-T09; MCT-Y2-T10; MCT-Y2-T11</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>75</x:v>
@@ -32745,7 +32745,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>DMET-Y3-G01; DMET-Y3-G02; DMET-Y3-G03; DMET-Y3-G04; DMET-Y3-G05; DMET-Y3-G06; DMET-Y3-G07; DMET-Y3-G08</x:v>
+        <x:v>DMET-Y3-T01; DMET-Y3-T02; DMET-Y3-T03; DMET-Y3-T04; DMET-Y3-T05; DMET-Y3-T06; DMET-Y3-T07; DMET-Y3-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>200</x:v>
@@ -32770,7 +32770,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R219921adf70447cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcaea04f78454c13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33087,7 +33087,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MAT-Y1-G09; MAT-Y1-G10; MAT-Y1-G11; MAT-Y1-G12; DPE-Y1-G01; DPE-Y1-G02; DPE-Y1-G03; DPE-Y1-G04</x:v>
+        <x:v>MAT-Y1-T09; MAT-Y1-T10; MAT-Y1-T11; MAT-Y1-T12; DPE-Y1-T01; DPE-Y1-T02; DPE-Y1-T03; DPE-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>196</x:v>
@@ -33128,7 +33128,7 @@
         <x:v>L06</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CIV-Y1-G05; CIV-Y1-G06; CIV-Y1-G07; CIV-Y1-G08; CIV-Y1-G09; CIV-Y1-G10; CIV-Y1-G11; CIV-Y1-G12</x:v>
+        <x:v>CIV-Y1-T05; CIV-Y1-T06; CIV-Y1-T07; CIV-Y1-T08; CIV-Y1-T09; CIV-Y1-T10; CIV-Y1-T11; CIV-Y1-T12</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>195</x:v>
@@ -33169,7 +33169,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CIV-Y1-G09; CIV-Y1-G10; CIV-Y1-G11; CIV-Y1-G12</x:v>
+        <x:v>CIV-Y1-T09; CIV-Y1-T10; CIV-Y1-T11; CIV-Y1-T12</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>96</x:v>
@@ -33210,7 +33210,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>DPE-Y1-G05; DPE-Y1-G06; DPE-Y1-G07; DPE-Y1-G08; DPE-Y1-G09; DPE-Y1-G10; DPE-Y1-G11; DPE-Y1-G12</x:v>
+        <x:v>DPE-Y1-T05; DPE-Y1-T06; DPE-Y1-T07; DPE-Y1-T08; DPE-Y1-T09; DPE-Y1-T10; DPE-Y1-T11; DPE-Y1-T12</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>196</x:v>
@@ -33251,7 +33251,7 @@
         <x:v>L07</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>ARC-Y1-G01; ARC-Y1-G02; ARC-Y1-G03; ARC-Y1-G04; ARC-Y1-G05; ARC-Y1-G06; ARC-Y1-G07; ARC-Y1-G08</x:v>
+        <x:v>ARC-Y1-T01; ARC-Y1-T02; ARC-Y1-T03; ARC-Y1-T04; ARC-Y1-T05; ARC-Y1-T06; ARC-Y1-T07; ARC-Y1-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>199</x:v>
@@ -33292,7 +33292,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>CIV-Y1-G01; CIV-Y1-G02; CIV-Y1-G03; CIV-Y1-G04; CIV-Y1-G05; CIV-Y1-G06; CIV-Y1-G07; CIV-Y1-G08</x:v>
+        <x:v>CIV-Y1-T01; CIV-Y1-T02; CIV-Y1-T03; CIV-Y1-T04; CIV-Y1-T05; CIV-Y1-T06; CIV-Y1-T07; CIV-Y1-T08</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>199</x:v>
@@ -33333,7 +33333,7 @@
         <x:v>L08</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>ARC-Y1-G09; ARC-Y1-G10; ARC-Y1-G11</x:v>
+        <x:v>ARC-Y1-T09; ARC-Y1-T10; ARC-Y1-T11</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>72</x:v>
@@ -33374,7 +33374,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>CSE-Y3-G01; CSE-Y3-G02; CSE-Y3-G03; CSE-Y3-G04; CSE-Y3-G05; CSE-Y3-G06; CSE-Y3-G07; CSE-Y3-G08</x:v>
+        <x:v>CSE-Y3-T01; CSE-Y3-T02; CSE-Y3-T03; CSE-Y3-T04; CSE-Y3-T05; CSE-Y3-T06; CSE-Y3-T07; CSE-Y3-T08</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>186</x:v>
@@ -33415,7 +33415,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K24" s="51" t="str">
-        <x:v>MAT-Y1-G01; MAT-Y1-G02; MAT-Y1-G03; MAT-Y1-G04; MAT-Y1-G05; MAT-Y1-G06; MAT-Y1-G07; MAT-Y1-G08</x:v>
+        <x:v>MAT-Y1-T01; MAT-Y1-T02; MAT-Y1-T03; MAT-Y1-T04; MAT-Y1-T05; MAT-Y1-T06; MAT-Y1-T07; MAT-Y1-T08</x:v>
       </x:c>
       <x:c r="L24" s="51" t="n">
         <x:v>193</x:v>
@@ -33456,7 +33456,7 @@
         <x:v>L05</x:v>
       </x:c>
       <x:c r="K25" s="51" t="str">
-        <x:v>MCT-Y1-G09; MCT-Y1-G10; MCT-Y1-G11; MCT-Y1-G12; CIV-Y1-G01; CIV-Y1-G02; CIV-Y1-G03; CIV-Y1-G04</x:v>
+        <x:v>MCT-Y1-T09; MCT-Y1-T10; MCT-Y1-T11; MCT-Y1-T12; CIV-Y1-T01; CIV-Y1-T02; CIV-Y1-T03; CIV-Y1-T04</x:v>
       </x:c>
       <x:c r="L25" s="51" t="n">
         <x:v>196</x:v>
@@ -33497,7 +33497,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K26" s="51" t="str">
-        <x:v>MCT-Y1-G01; MCT-Y1-G02; MCT-Y1-G03; MCT-Y1-G04; MCT-Y1-G05; MCT-Y1-G06; MCT-Y1-G07; MCT-Y1-G08</x:v>
+        <x:v>MCT-Y1-T01; MCT-Y1-T02; MCT-Y1-T03; MCT-Y1-T04; MCT-Y1-T05; MCT-Y1-T06; MCT-Y1-T07; MCT-Y1-T08</x:v>
       </x:c>
       <x:c r="L26" s="51" t="n">
         <x:v>192</x:v>
@@ -33538,7 +33538,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K27" s="51" t="str">
-        <x:v>CSE-Y3-G09; CSE-Y3-G10; CSE-Y3-G11</x:v>
+        <x:v>CSE-Y3-T09; CSE-Y3-T10; CSE-Y3-T11</x:v>
       </x:c>
       <x:c r="L27" s="51" t="n">
         <x:v>69</x:v>
@@ -33563,7 +33563,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ea999e6382e4e02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7e8c2149b934ded"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33844,7 +33844,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CSE-Y4-G01; CSE-Y4-G02; CSE-Y4-G03; CSE-Y4-G04; CSE-Y4-G05; CSE-Y4-G06; CSE-Y4-G07; CSE-Y4-G08</x:v>
+        <x:v>CSE-Y4-T01; CSE-Y4-T02; CSE-Y4-T03; CSE-Y4-T04; CSE-Y4-T05; CSE-Y4-T06; CSE-Y4-T07; CSE-Y4-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>195</x:v>
@@ -33885,7 +33885,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DMET-Y4-G07; DMET-Y4-G08; DMET-Y4-G09; DMET-Y4-G10</x:v>
+        <x:v>DMET-Y4-T07; DMET-Y4-T08; DMET-Y4-T09; DMET-Y4-T10</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>94</x:v>
@@ -33926,7 +33926,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CSE-Y4-G09; CSE-Y4-G10; DMET-Y4-G01; DMET-Y4-G02; DMET-Y4-G03; DMET-Y4-G04; DMET-Y4-G05; DMET-Y4-G06</x:v>
+        <x:v>CSE-Y4-T09; CSE-Y4-T10; DMET-Y4-T01; DMET-Y4-T02; DMET-Y4-T03; DMET-Y4-T04; DMET-Y4-T05; DMET-Y4-T06</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>192</x:v>
@@ -33951,7 +33951,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ed10f3e4a8e44dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1902a961e0014fd6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34240,7 +34240,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DMET-Y5-G01; DMET-Y5-G02; DMET-Y5-G03; DMET-Y5-G04; DMET-Y5-G05; DMET-Y5-G06; DMET-Y5-G07; DMET-Y5-G08</x:v>
+        <x:v>DMET-Y5-T01; DMET-Y5-T02; DMET-Y5-T03; DMET-Y5-T04; DMET-Y5-T05; DMET-Y5-T06; DMET-Y5-T07; DMET-Y5-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>200</x:v>
@@ -34281,7 +34281,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>COM-Y4-G09; COM-Y4-G10</x:v>
+        <x:v>COM-Y4-T09; COM-Y4-T10</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>46</x:v>
@@ -34322,7 +34322,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MSC-Y5-G01; MSC-Y5-G02</x:v>
+        <x:v>MSC-Y5-T01; MSC-Y5-T02</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>44</x:v>
@@ -34363,7 +34363,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>DMET-Y5-G09</x:v>
+        <x:v>DMET-Y5-T09</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>24</x:v>
@@ -34404,7 +34404,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>COM-Y4-G01; COM-Y4-G02; COM-Y4-G03; COM-Y4-G04; COM-Y4-G05; COM-Y4-G06; COM-Y4-G07; COM-Y4-G08</x:v>
+        <x:v>COM-Y4-T01; COM-Y4-T02; COM-Y4-T03; COM-Y4-T04; COM-Y4-T05; COM-Y4-T06; COM-Y4-T07; COM-Y4-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>187</x:v>
@@ -34429,7 +34429,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9da1b162e9d44b6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad31a7b30c3e4799"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34702,7 +34702,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>LLS-Y4-G01; LLS-Y4-G02; LLS-Y4-G03</x:v>
+        <x:v>LLS-Y4-T01; LLS-Y4-T02; LLS-Y4-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>59</x:v>
@@ -34727,7 +34727,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdce2ec2882a4cb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14531110f1db4791"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35020,7 +35020,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>GD-Y3-G01; GD-Y3-G02</x:v>
+        <x:v>GD-Y3-T01; GD-Y3-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>45</x:v>
@@ -35061,7 +35061,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>PD-Y4-G03; PD-Y4-G04</x:v>
+        <x:v>PD-Y4-T03; PD-Y4-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>46</x:v>
@@ -35102,7 +35102,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CSE-Y2-G09; CSE-Y2-G10; CSE-Y2-G11</x:v>
+        <x:v>CSE-Y2-T09; CSE-Y2-T10; CSE-Y2-T11</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>72</x:v>
@@ -35143,7 +35143,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>GD-Y4-G01; GD-Y4-G02; MD-Y4-G01; MD-Y4-G02; MD-Y4-G03; MD-Y4-G04; PD-Y4-G01; PD-Y4-G02</x:v>
+        <x:v>GD-Y4-T01; GD-Y4-T02; MD-Y4-T01; MD-Y4-T02; MD-Y4-T03; MD-Y4-T04; PD-Y4-T01; PD-Y4-T02</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>179</x:v>
@@ -35184,7 +35184,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>LLS-Y3-G01; LLS-Y3-G02; LLS-Y3-G03</x:v>
+        <x:v>LLS-Y3-T01; LLS-Y3-T02; LLS-Y3-T03</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>62</x:v>
@@ -35225,7 +35225,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>CSE-Y2-G01; CSE-Y2-G02; CSE-Y2-G03; CSE-Y2-G04; CSE-Y2-G05; CSE-Y2-G06; CSE-Y2-G07; CSE-Y2-G08</x:v>
+        <x:v>CSE-Y2-T01; CSE-Y2-T02; CSE-Y2-T03; CSE-Y2-T04; CSE-Y2-T05; CSE-Y2-T06; CSE-Y2-T07; CSE-Y2-T08</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>196</x:v>
@@ -35250,7 +35250,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e9ce60e5e044cab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7535701f098346e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35535,7 +35535,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>BI-Y4-G01; BI-Y4-G02; BI-Y4-G03; BI-Y4-G04</x:v>
+        <x:v>BI-Y4-T01; BI-Y4-T02; BI-Y4-T03; BI-Y4-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>80</x:v>
@@ -35576,7 +35576,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MAT-Y4-G09; MAT-Y4-G10; MAT-Y4-G11</x:v>
+        <x:v>MAT-Y4-T09; MAT-Y4-T10; MAT-Y4-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>67</x:v>
@@ -35617,7 +35617,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MAT-Y4-G01; MAT-Y4-G02; MAT-Y4-G03; MAT-Y4-G04; MAT-Y4-G05; MAT-Y4-G06; MAT-Y4-G07; MAT-Y4-G08</x:v>
+        <x:v>MAT-Y4-T01; MAT-Y4-T02; MAT-Y4-T03; MAT-Y4-T04; MAT-Y4-T05; MAT-Y4-T06; MAT-Y4-T07; MAT-Y4-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>184</x:v>
@@ -35658,7 +35658,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>BIO-Y5-G01; BIO-Y5-G02; BIO-Y5-G03</x:v>
+        <x:v>BIO-Y5-T01; BIO-Y5-T02; BIO-Y5-T03</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>51</x:v>
@@ -35683,7 +35683,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a8241840ed948e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R548d3ecfc7714d3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35976,7 +35976,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DPE-Y3-G01; DPE-Y3-G02; DPE-Y3-G03; DPE-Y3-G04; DPE-Y3-G05; DPE-Y3-G06; DPE-Y3-G07; DPE-Y3-G08</x:v>
+        <x:v>DPE-Y3-T01; DPE-Y3-T02; DPE-Y3-T03; DPE-Y3-T04; DPE-Y3-T05; DPE-Y3-T06; DPE-Y3-T07; DPE-Y3-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>196</x:v>
@@ -36017,7 +36017,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ELX-Y3-G09; ELX-Y3-G10</x:v>
+        <x:v>ELX-Y3-T09; ELX-Y3-T10</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>50</x:v>
@@ -36058,7 +36058,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>ARC-Y4-G09; ARC-Y4-G10</x:v>
+        <x:v>ARC-Y4-T09; ARC-Y4-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>46</x:v>
@@ -36099,7 +36099,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>ELX-Y3-G01; ELX-Y3-G02; ELX-Y3-G03; ELX-Y3-G04; ELX-Y3-G05; ELX-Y3-G06; ELX-Y3-G07; ELX-Y3-G08</x:v>
+        <x:v>ELX-Y3-T01; ELX-Y3-T02; ELX-Y3-T03; ELX-Y3-T04; ELX-Y3-T05; ELX-Y3-T06; ELX-Y3-T07; ELX-Y3-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>200</x:v>
@@ -36140,7 +36140,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>ARC-Y4-G01; ARC-Y4-G02; ARC-Y4-G03; ARC-Y4-G04; ARC-Y4-G05; ARC-Y4-G06; ARC-Y4-G07; ARC-Y4-G08</x:v>
+        <x:v>ARC-Y4-T01; ARC-Y4-T02; ARC-Y4-T03; ARC-Y4-T04; ARC-Y4-T05; ARC-Y4-T06; ARC-Y4-T07; ARC-Y4-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>189</x:v>
@@ -36181,7 +36181,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>DPE-Y3-G09; DPE-Y3-G10; DPE-Y3-G11</x:v>
+        <x:v>DPE-Y3-T09; DPE-Y3-T10; DPE-Y3-T11</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>72</x:v>
@@ -36206,7 +36206,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd66bdb7def464a11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf14c7838d0cc46c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36499,7 +36499,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CPH-Y3-G01; CPH-Y3-G02; CPH-Y3-G03</x:v>
+        <x:v>CPH-Y3-T01; CPH-Y3-T02; CPH-Y3-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>74</x:v>
@@ -36540,7 +36540,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DEN-Y1-G01; DEN-Y1-G02</x:v>
+        <x:v>DEN-Y1-T01; DEN-Y1-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>46</x:v>
@@ -36581,7 +36581,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>COM-Y4-G07; COM-Y4-G08; COM-Y4-G09; COM-Y4-G10; ELX-Y4-G01; ELX-Y4-G02; ELX-Y4-G03; ELX-Y4-G04</x:v>
+        <x:v>COM-Y4-T07; COM-Y4-T08; COM-Y4-T09; COM-Y4-T10; ELX-Y4-T01; ELX-Y4-T02; ELX-Y4-T03; ELX-Y4-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>188</x:v>
@@ -36622,7 +36622,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>NET-Y4-G09; NET-Y4-G10; COM-Y4-G01; COM-Y4-G02; COM-Y4-G03; COM-Y4-G04; COM-Y4-G05; COM-Y4-G06</x:v>
+        <x:v>NET-Y4-T09; NET-Y4-T10; COM-Y4-T01; COM-Y4-T02; COM-Y4-T03; COM-Y4-T04; COM-Y4-T05; COM-Y4-T06</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>189</x:v>
@@ -36663,7 +36663,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>NET-Y4-G01; NET-Y4-G02; NET-Y4-G03; NET-Y4-G04; NET-Y4-G05; NET-Y4-G06; NET-Y4-G07; NET-Y4-G08</x:v>
+        <x:v>NET-Y4-T01; NET-Y4-T02; NET-Y4-T03; NET-Y4-T04; NET-Y4-T05; NET-Y4-T06; NET-Y4-T07; NET-Y4-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>199</x:v>
@@ -36704,7 +36704,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>ELX-Y4-G05; ELX-Y4-G06; ELX-Y4-G07; ELX-Y4-G08; ELX-Y4-G09; ELX-Y4-G10</x:v>
+        <x:v>ELX-Y4-T05; ELX-Y4-T06; ELX-Y4-T07; ELX-Y4-T08; ELX-Y4-T09; ELX-Y4-T10</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>141</x:v>
@@ -36729,7 +36729,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6461c3d679d1401e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a013dfd9729429d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37010,7 +37010,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>ARC-Y5-G01; ARC-Y5-G02; ARC-Y5-G03; ARC-Y5-G04; ARC-Y5-G05; ARC-Y5-G06; ARC-Y5-G07; ARC-Y5-G08</x:v>
+        <x:v>ARC-Y5-T01; ARC-Y5-T02; ARC-Y5-T03; ARC-Y5-T04; ARC-Y5-T05; ARC-Y5-T06; ARC-Y5-T07; ARC-Y5-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>199</x:v>
@@ -37051,7 +37051,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ARC-Y5-G09</x:v>
+        <x:v>ARC-Y5-T09</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>24</x:v>
@@ -37092,7 +37092,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DEN-Y3-G01; DEN-Y3-G02</x:v>
+        <x:v>DEN-Y3-T01; DEN-Y3-T02</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>43</x:v>
@@ -37117,7 +37117,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46c7d6e07fcc4e98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51db348d8bb94fb7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37398,7 +37398,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CPH-Y1-G01; CPH-Y1-G02; CPH-Y1-G03; CPH-Y1-G04</x:v>
+        <x:v>CPH-Y1-T01; CPH-Y1-T02; CPH-Y1-T03; CPH-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>80</x:v>
@@ -37439,7 +37439,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>COM-Y5-G01; COM-Y5-G02; COM-Y5-G03; COM-Y5-G04; COM-Y5-G05; COM-Y5-G06; COM-Y5-G07; COM-Y5-G08</x:v>
+        <x:v>COM-Y5-T01; COM-Y5-T02; COM-Y5-T03; COM-Y5-T04; COM-Y5-T05; COM-Y5-T06; COM-Y5-T07; COM-Y5-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>196</x:v>
@@ -37480,7 +37480,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>COM-Y5-G09</x:v>
+        <x:v>COM-Y5-T09</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>24</x:v>
@@ -37505,7 +37505,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R612abc246e114364"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf5d965953974e6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37778,7 +37778,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>TBM-Y5-G01; TBM-Y5-G02; TBM-Y5-G03; TBM-Y5-G04</x:v>
+        <x:v>TBM-Y5-T01; TBM-Y5-T02; TBM-Y5-T03; TBM-Y5-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>80</x:v>
@@ -37803,7 +37803,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d4fb8b315c44a09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ced38c1fcab4374"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38092,7 +38092,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>NET-Y1-G09; NET-Y1-G10; NET-Y1-G11; NET-Y1-G12; COM-Y1-G01; COM-Y1-G02; COM-Y1-G03; COM-Y1-G04</x:v>
+        <x:v>NET-Y1-T09; NET-Y1-T10; NET-Y1-T11; NET-Y1-T12; COM-Y1-T01; COM-Y1-T02; COM-Y1-T03; COM-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>193</x:v>
@@ -38133,7 +38133,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>NET-Y1-G01; NET-Y1-G02; NET-Y1-G03; NET-Y1-G04; NET-Y1-G05; NET-Y1-G06; NET-Y1-G07; NET-Y1-G08</x:v>
+        <x:v>NET-Y1-T01; NET-Y1-T02; NET-Y1-T03; NET-Y1-T04; NET-Y1-T05; NET-Y1-T06; NET-Y1-T07; NET-Y1-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>192</x:v>
@@ -38174,7 +38174,7 @@
         <x:v>L05</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>ELX-Y1-G10; ELX-Y1-G11</x:v>
+        <x:v>ELX-Y1-T10; ELX-Y1-T11</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>49</x:v>
@@ -38215,7 +38215,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>ELX-Y1-G02; ELX-Y1-G03; ELX-Y1-G04; ELX-Y1-G05; ELX-Y1-G06; ELX-Y1-G07; ELX-Y1-G08; ELX-Y1-G09</x:v>
+        <x:v>ELX-Y1-T02; ELX-Y1-T03; ELX-Y1-T04; ELX-Y1-T05; ELX-Y1-T06; ELX-Y1-T07; ELX-Y1-T08; ELX-Y1-T09</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>200</x:v>
@@ -38256,7 +38256,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>COM-Y1-G05; COM-Y1-G06; COM-Y1-G07; COM-Y1-G08; COM-Y1-G09; COM-Y1-G10; COM-Y1-G11; ELX-Y1-G01</x:v>
+        <x:v>COM-Y1-T05; COM-Y1-T06; COM-Y1-T07; COM-Y1-T08; COM-Y1-T09; COM-Y1-T10; COM-Y1-T11; ELX-Y1-T01</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>194</x:v>
@@ -38281,7 +38281,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57f4e16d02f44f56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c31b980a52b41c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38566,7 +38566,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MAT-Y1-G01; MAT-Y1-G02; MAT-Y1-G03; MAT-Y1-G04; MAT-Y1-G05; MAT-Y1-G06; MAT-Y1-G07; MAT-Y1-G08</x:v>
+        <x:v>MAT-Y1-T01; MAT-Y1-T02; MAT-Y1-T03; MAT-Y1-T04; MAT-Y1-T05; MAT-Y1-T06; MAT-Y1-T07; MAT-Y1-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>193</x:v>
@@ -38607,7 +38607,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>PHD-Y3-G01; PHD-Y3-G02; PHD-Y3-G03; PHD-Y3-G04</x:v>
+        <x:v>PHD-Y3-T01; PHD-Y3-T02; PHD-Y3-T03; PHD-Y3-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>92</x:v>
@@ -38648,7 +38648,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PGD-Y1-G01; PGD-Y1-G02; PGD-Y1-G03</x:v>
+        <x:v>PGD-Y1-T01; PGD-Y1-T02; PGD-Y1-T03</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>63</x:v>
@@ -38689,7 +38689,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>MAT-Y1-G09; MAT-Y1-G10; MAT-Y1-G11; MAT-Y1-G12</x:v>
+        <x:v>MAT-Y1-T09; MAT-Y1-T10; MAT-Y1-T11; MAT-Y1-T12</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>96</x:v>
@@ -38714,7 +38714,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb29db32e1e974b5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f78b40677c040e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39015,7 +39015,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DPE-Y1-G09; DPE-Y1-G10; DPE-Y1-G11; DPE-Y1-G12</x:v>
+        <x:v>DPE-Y1-T09; DPE-Y1-T10; DPE-Y1-T11; DPE-Y1-T12</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>96</x:v>
@@ -39056,7 +39056,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ELX-Y1-G09; ELX-Y1-G10; ELX-Y1-G11</x:v>
+        <x:v>ELX-Y1-T09; ELX-Y1-T10; ELX-Y1-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>74</x:v>
@@ -39097,7 +39097,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>NET-Y5-G09; NET-Y5-G10</x:v>
+        <x:v>NET-Y5-T09; NET-Y5-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>46</x:v>
@@ -39138,7 +39138,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>PHR-Y4-G01; PHR-Y4-G02; PHR-Y4-G03; PHR-Y4-G04</x:v>
+        <x:v>PHR-Y4-T01; PHR-Y4-T02; PHR-Y4-T03; PHR-Y4-T04</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>79</x:v>
@@ -39179,7 +39179,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>GD-Y2-G01; GD-Y2-G02</x:v>
+        <x:v>GD-Y2-T01; GD-Y2-T02</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>46</x:v>
@@ -39220,7 +39220,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>NET-Y5-G01; NET-Y5-G02; NET-Y5-G03; NET-Y5-G04; NET-Y5-G05; NET-Y5-G06; NET-Y5-G07; NET-Y5-G08</x:v>
+        <x:v>NET-Y5-T01; NET-Y5-T02; NET-Y5-T03; NET-Y5-T04; NET-Y5-T05; NET-Y5-T06; NET-Y5-T07; NET-Y5-T08</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>187</x:v>
@@ -39261,7 +39261,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>DPE-Y1-G01; DPE-Y1-G02; DPE-Y1-G03; DPE-Y1-G04; DPE-Y1-G05; DPE-Y1-G06; DPE-Y1-G07; DPE-Y1-G08</x:v>
+        <x:v>DPE-Y1-T01; DPE-Y1-T02; DPE-Y1-T03; DPE-Y1-T04; DPE-Y1-T05; DPE-Y1-T06; DPE-Y1-T07; DPE-Y1-T08</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>200</x:v>
@@ -39302,7 +39302,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>ELX-Y1-G01; ELX-Y1-G02; ELX-Y1-G03; ELX-Y1-G04; ELX-Y1-G05; ELX-Y1-G06; ELX-Y1-G07; ELX-Y1-G08</x:v>
+        <x:v>ELX-Y1-T01; ELX-Y1-T02; ELX-Y1-T03; ELX-Y1-T04; ELX-Y1-T05; ELX-Y1-T06; ELX-Y1-T07; ELX-Y1-T08</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>200</x:v>
@@ -39327,7 +39327,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc71ac0fe26d546f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R062f35999d934e88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39632,7 +39632,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PHD-Y1-G04</x:v>
+        <x:v>PHD-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>25</x:v>
@@ -39673,7 +39673,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DEN-Y5-G01; DEN-Y5-G02</x:v>
+        <x:v>DEN-Y5-T01; DEN-Y5-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>37</x:v>
@@ -39714,7 +39714,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PGD-Y1-G01; PGD-Y1-G02; PGD-Y1-G03; MSC-Y1-G01; MSC-Y1-G02; MSC-Y1-G03; PHD-Y1-G01; PHD-Y1-G02; PHD-Y1-G03</x:v>
+        <x:v>PGD-Y1-T01; PGD-Y1-T02; PGD-Y1-T03; MSC-Y1-T01; MSC-Y1-T02; MSC-Y1-T03; PHD-Y1-T01; PHD-Y1-T02; PHD-Y1-T03</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>192</x:v>
@@ -39755,7 +39755,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>PGD-Y5-G01; PGD-Y5-G02; PGD-Y5-G03</x:v>
+        <x:v>PGD-Y5-T01; PGD-Y5-T02; PGD-Y5-T03</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>51</x:v>
@@ -39796,7 +39796,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>NET-Y4-G01; NET-Y4-G02; NET-Y4-G03; NET-Y4-G04; NET-Y4-G05; NET-Y4-G06; NET-Y4-G07; NET-Y4-G08</x:v>
+        <x:v>NET-Y4-T01; NET-Y4-T02; NET-Y4-T03; NET-Y4-T04; NET-Y4-T05; NET-Y4-T06; NET-Y4-T07; NET-Y4-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>199</x:v>
@@ -39837,7 +39837,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>TBM-Y2-G01; TBM-Y2-G02; TBM-Y2-G03; TBM-Y2-G04</x:v>
+        <x:v>TBM-Y2-T01; TBM-Y2-T02; TBM-Y2-T03; TBM-Y2-T04</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>92</x:v>
@@ -39878,7 +39878,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>GM-Y1-G01; GM-Y1-G02</x:v>
+        <x:v>GM-Y1-T01; GM-Y1-T02</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>45</x:v>
@@ -39919,7 +39919,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>NET-Y4-G09; NET-Y4-G10</x:v>
+        <x:v>NET-Y4-T09; NET-Y4-T10</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>48</x:v>
@@ -39960,7 +39960,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K24" s="51" t="str">
-        <x:v>MD-Y5-G01; MD-Y5-G02; MD-Y5-G03; MD-Y5-G04</x:v>
+        <x:v>MD-Y5-T01; MD-Y5-T02; MD-Y5-T03; MD-Y5-T04</x:v>
       </x:c>
       <x:c r="L24" s="51" t="n">
         <x:v>84</x:v>
@@ -39985,7 +39985,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35b6d86d69f54930"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dc83b033e3a4a69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40290,7 +40290,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>NET-Y2-G01; NET-Y2-G02; NET-Y2-G03; NET-Y2-G04; NET-Y2-G05; NET-Y2-G06; NET-Y2-G07; NET-Y2-G08</x:v>
+        <x:v>NET-Y2-T01; NET-Y2-T02; NET-Y2-T03; NET-Y2-T04; NET-Y2-T05; NET-Y2-T06; NET-Y2-T07; NET-Y2-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>200</x:v>
@@ -40331,7 +40331,7 @@
         <x:v>L05</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ELX-Y2-G11</x:v>
+        <x:v>ELX-Y2-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>23</x:v>
@@ -40372,7 +40372,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DMET-Y4-G01; DMET-Y4-G02; DMET-Y4-G03; DMET-Y4-G04; DMET-Y4-G05; DMET-Y4-G06; DMET-Y4-G07; DMET-Y4-G08</x:v>
+        <x:v>DMET-Y4-T01; DMET-Y4-T02; DMET-Y4-T03; DMET-Y4-T04; DMET-Y4-T05; DMET-Y4-T06; DMET-Y4-T07; DMET-Y4-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>192</x:v>
@@ -40413,7 +40413,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>NET-Y2-G09; NET-Y2-G10; NET-Y2-G11; COM-Y2-G01; COM-Y2-G02; COM-Y2-G03; COM-Y2-G04; COM-Y2-G05</x:v>
+        <x:v>NET-Y2-T09; NET-Y2-T10; NET-Y2-T11; COM-Y2-T01; COM-Y2-T02; COM-Y2-T03; COM-Y2-T04; COM-Y2-T05</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>191</x:v>
@@ -40454,7 +40454,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>COM-Y2-G06; COM-Y2-G07; COM-Y2-G08; COM-Y2-G09; COM-Y2-G10; COM-Y2-G11; ELX-Y2-G01; ELX-Y2-G02</x:v>
+        <x:v>COM-Y2-T06; COM-Y2-T07; COM-Y2-T08; COM-Y2-T09; COM-Y2-T10; COM-Y2-T11; ELX-Y2-T01; ELX-Y2-T02</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>186</x:v>
@@ -40495,7 +40495,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>MSC-Y4-G01; MSC-Y4-G02</x:v>
+        <x:v>MSC-Y4-T01; MSC-Y4-T02</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>46</x:v>
@@ -40536,7 +40536,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>DMET-Y4-G09; DMET-Y4-G10</x:v>
+        <x:v>DMET-Y4-T09; DMET-Y4-T10</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>46</x:v>
@@ -40577,7 +40577,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>GM-Y2-G01; GM-Y2-G02</x:v>
+        <x:v>GM-Y2-T01; GM-Y2-T02</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>43</x:v>
@@ -40618,7 +40618,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K24" s="51" t="str">
-        <x:v>ELX-Y2-G03; ELX-Y2-G04; ELX-Y2-G05; ELX-Y2-G06; ELX-Y2-G07; ELX-Y2-G08; ELX-Y2-G09; ELX-Y2-G10</x:v>
+        <x:v>ELX-Y2-T03; ELX-Y2-T04; ELX-Y2-T05; ELX-Y2-T06; ELX-Y2-T07; ELX-Y2-T08; ELX-Y2-T09; ELX-Y2-T10</x:v>
       </x:c>
       <x:c r="L24" s="51" t="n">
         <x:v>192</x:v>
@@ -40643,7 +40643,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb930acf28a24da7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91fcadfb249042d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40920,7 +40920,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>LLS-Y2-G01; LLS-Y2-G02; LLS-Y2-G03</x:v>
+        <x:v>LLS-Y2-T01; LLS-Y2-T02; LLS-Y2-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>66</x:v>
@@ -40961,7 +40961,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>PHD-Y2-G01; PHD-Y2-G02; PHD-Y2-G03; PHD-Y2-G04</x:v>
+        <x:v>PHD-Y2-T01; PHD-Y2-T02; PHD-Y2-T03; PHD-Y2-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>97</x:v>
@@ -40986,7 +40986,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R085deebe187d4e2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28045f296bc340d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41287,7 +41287,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DPE-Y4-G06; DPE-Y4-G07; DPE-Y4-G08; DPE-Y4-G09; DPE-Y4-G10; DPE-Y4-G11; MCT-Y4-G01; MCT-Y4-G02</x:v>
+        <x:v>DPE-Y4-T06; DPE-Y4-T07; DPE-Y4-T08; DPE-Y4-T09; DPE-Y4-T10; DPE-Y4-T11; MCT-Y4-T01; MCT-Y4-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>188</x:v>
@@ -41328,7 +41328,7 @@
         <x:v>L07</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ARC-Y4-G06; ARC-Y4-G07; ARC-Y4-G08; ARC-Y4-G09; ARC-Y4-G10</x:v>
+        <x:v>ARC-Y4-T06; ARC-Y4-T07; ARC-Y4-T08; ARC-Y4-T09; ARC-Y4-T10</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>115</x:v>
@@ -41369,7 +41369,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PD-Y4-G01; PD-Y4-G02; PD-Y4-G03; PD-Y4-G04</x:v>
+        <x:v>PD-Y4-T01; PD-Y4-T02; PD-Y4-T03; PD-Y4-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>93</x:v>
@@ -41410,7 +41410,7 @@
         <x:v>L06</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>CIV-Y4-G09; CIV-Y4-G10; CIV-Y4-G11; ARC-Y4-G01; ARC-Y4-G02; ARC-Y4-G03; ARC-Y4-G04; ARC-Y4-G05</x:v>
+        <x:v>CIV-Y4-T09; CIV-Y4-T10; CIV-Y4-T11; ARC-Y4-T01; ARC-Y4-T02; ARC-Y4-T03; ARC-Y4-T04; ARC-Y4-T05</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>189</x:v>
@@ -41451,7 +41451,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>MAT-Y4-G09; MAT-Y4-G10; MAT-Y4-G11; DPE-Y4-G01; DPE-Y4-G02; DPE-Y4-G03; DPE-Y4-G04; DPE-Y4-G05</x:v>
+        <x:v>MAT-Y4-T09; MAT-Y4-T10; MAT-Y4-T11; DPE-Y4-T01; DPE-Y4-T02; DPE-Y4-T03; DPE-Y4-T04; DPE-Y4-T05</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>184</x:v>
@@ -41492,7 +41492,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>MAT-Y4-G01; MAT-Y4-G02; MAT-Y4-G03; MAT-Y4-G04; MAT-Y4-G05; MAT-Y4-G06; MAT-Y4-G07; MAT-Y4-G08</x:v>
+        <x:v>MAT-Y4-T01; MAT-Y4-T02; MAT-Y4-T03; MAT-Y4-T04; MAT-Y4-T05; MAT-Y4-T06; MAT-Y4-T07; MAT-Y4-T08</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>184</x:v>
@@ -41533,7 +41533,7 @@
         <x:v>L05</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>CIV-Y4-G01; CIV-Y4-G02; CIV-Y4-G03; CIV-Y4-G04; CIV-Y4-G05; CIV-Y4-G06; CIV-Y4-G07; CIV-Y4-G08</x:v>
+        <x:v>CIV-Y4-T01; CIV-Y4-T02; CIV-Y4-T03; CIV-Y4-T04; CIV-Y4-T05; CIV-Y4-T06; CIV-Y4-T07; CIV-Y4-T08</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>187</x:v>
@@ -41574,7 +41574,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>MCT-Y4-G03; MCT-Y4-G04; MCT-Y4-G05; MCT-Y4-G06; MCT-Y4-G07; MCT-Y4-G08; MCT-Y4-G09; MCT-Y4-G10</x:v>
+        <x:v>MCT-Y4-T03; MCT-Y4-T04; MCT-Y4-T05; MCT-Y4-T06; MCT-Y4-T07; MCT-Y4-T08; MCT-Y4-T09; MCT-Y4-T10</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>200</x:v>
@@ -41599,7 +41599,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0a1c619c09442bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e88dd8692f2406d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41880,7 +41880,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PGD-Y2-G01; PGD-Y2-G02; PGD-Y2-G03</x:v>
+        <x:v>PGD-Y2-T01; PGD-Y2-T02; PGD-Y2-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>60</x:v>
@@ -41921,7 +41921,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>GD-Y5-G01; GD-Y5-G02</x:v>
+        <x:v>GD-Y5-T01; GD-Y5-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>40</x:v>
@@ -41962,7 +41962,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MD-Y2-G01; MD-Y2-G02; MD-Y2-G03; MD-Y2-G04</x:v>
+        <x:v>MD-Y2-T01; MD-Y2-T02; MD-Y2-T03; MD-Y2-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>99</x:v>
@@ -41987,7 +41987,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd8fc7ddf84e4b4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bb1d68e32e24167"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42260,7 +42260,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DEN-Y4-G01; DEN-Y4-G02</x:v>
+        <x:v>DEN-Y4-T01; DEN-Y4-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>41</x:v>
@@ -42285,7 +42285,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e733e1496c743a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82baef5a16af414c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42570,7 +42570,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DPE-Y3-G09; DPE-Y3-G10; DPE-Y3-G11</x:v>
+        <x:v>DPE-Y3-T09; DPE-Y3-T10; DPE-Y3-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>72</x:v>
@@ -42611,7 +42611,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ARC-Y4-G09; ARC-Y4-G10</x:v>
+        <x:v>ARC-Y4-T09; ARC-Y4-T10</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>46</x:v>
@@ -42652,7 +42652,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>ARC-Y4-G01; ARC-Y4-G02; ARC-Y4-G03; ARC-Y4-G04; ARC-Y4-G05; ARC-Y4-G06; ARC-Y4-G07; ARC-Y4-G08</x:v>
+        <x:v>ARC-Y4-T01; ARC-Y4-T02; ARC-Y4-T03; ARC-Y4-T04; ARC-Y4-T05; ARC-Y4-T06; ARC-Y4-T07; ARC-Y4-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>189</x:v>
@@ -42693,7 +42693,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>DPE-Y3-G01; DPE-Y3-G02; DPE-Y3-G03; DPE-Y3-G04; DPE-Y3-G05; DPE-Y3-G06; DPE-Y3-G07; DPE-Y3-G08</x:v>
+        <x:v>DPE-Y3-T01; DPE-Y3-T02; DPE-Y3-T03; DPE-Y3-T04; DPE-Y3-T05; DPE-Y3-T06; DPE-Y3-T07; DPE-Y3-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>196</x:v>
@@ -42718,7 +42718,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1da1ce57b3644004"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ec18f0fe7a348c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43003,7 +43003,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>BIO-Y3-G01; BIO-Y3-G02; BIO-Y3-G03</x:v>
+        <x:v>BIO-Y3-T01; BIO-Y3-T02; BIO-Y3-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>55</x:v>
@@ -43044,7 +43044,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>BI-Y2-G01; BI-Y2-G02; BI-Y2-G03; BI-Y2-G04</x:v>
+        <x:v>BI-Y2-T01; BI-Y2-T02; BI-Y2-T03; BI-Y2-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>90</x:v>
@@ -43085,7 +43085,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CPH-Y1-G03; CPH-Y1-G04</x:v>
+        <x:v>CPH-Y1-T03; CPH-Y1-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>40</x:v>
@@ -43126,7 +43126,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>PHR-Y1-G01; PHR-Y1-G02; PHR-Y1-G03; PHR-Y1-G04; BIO-Y1-G01; BIO-Y1-G02; BIO-Y1-G03; CPH-Y1-G01; CPH-Y1-G02</x:v>
+        <x:v>PHR-Y1-T01; PHR-Y1-T02; PHR-Y1-T03; PHR-Y1-T04; BIO-Y1-T01; BIO-Y1-T02; BIO-Y1-T03; CPH-Y1-T01; CPH-Y1-T02</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>195</x:v>
@@ -43151,7 +43151,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R342c29e3237a43c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ef39806fff04204"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43432,7 +43432,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MAT-Y2-G09; MAT-Y2-G10; MAT-Y2-G11; MAT-Y2-G12</x:v>
+        <x:v>MAT-Y2-T09; MAT-Y2-T10; MAT-Y2-T11; MAT-Y2-T12</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>92</x:v>
@@ -43473,7 +43473,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MAT-Y2-G01; MAT-Y2-G02; MAT-Y2-G03; MAT-Y2-G04; MAT-Y2-G05; MAT-Y2-G06; MAT-Y2-G07; MAT-Y2-G08</x:v>
+        <x:v>MAT-Y2-T01; MAT-Y2-T02; MAT-Y2-T03; MAT-Y2-T04; MAT-Y2-T05; MAT-Y2-T06; MAT-Y2-T07; MAT-Y2-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>184</x:v>
@@ -43514,7 +43514,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>TBM-Y4-G01; TBM-Y4-G02; TBM-Y4-G03; TBM-Y4-G04</x:v>
+        <x:v>TBM-Y4-T01; TBM-Y4-T02; TBM-Y4-T03; TBM-Y4-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>84</x:v>
@@ -43539,7 +43539,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb54c3fe2315d479d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07db4dd50d804def"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43812,7 +43812,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CPH-Y2-G01; CPH-Y2-G02; CPH-Y2-G03; CPH-Y2-G04</x:v>
+        <x:v>CPH-Y2-T01; CPH-Y2-T02; CPH-Y2-T03; CPH-Y2-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>76</x:v>
@@ -43837,7 +43837,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9474fb34f5c408e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e775a0b9a674807"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44114,7 +44114,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PGD-Y4-G01; PGD-Y4-G02; PGD-Y4-G03</x:v>
+        <x:v>PGD-Y4-T01; PGD-Y4-T02; PGD-Y4-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>53</x:v>
@@ -44155,7 +44155,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MD-Y4-G01; MD-Y4-G02; MD-Y4-G03; MD-Y4-G04</x:v>
+        <x:v>MD-Y4-T01; MD-Y4-T02; MD-Y4-T03; MD-Y4-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>89</x:v>
@@ -44180,7 +44180,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97a5605ff39f4e06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3cf8c1d5bfc4367"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44481,7 +44481,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PHR-Y1-G01; PHR-Y1-G02; PHR-Y1-G03; PHR-Y1-G04</x:v>
+        <x:v>PHR-Y1-T01; PHR-Y1-T02; PHR-Y1-T03; PHR-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>93</x:v>
@@ -44522,7 +44522,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ARC-Y3-G01; ARC-Y3-G02; ARC-Y3-G03; ARC-Y3-G04; ARC-Y3-G05; ARC-Y3-G06; ARC-Y3-G07; ARC-Y3-G08</x:v>
+        <x:v>ARC-Y3-T01; ARC-Y3-T02; ARC-Y3-T03; ARC-Y3-T04; ARC-Y3-T05; ARC-Y3-T06; ARC-Y3-T07; ARC-Y3-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>198</x:v>
@@ -44563,7 +44563,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DPE-Y4-G01; DPE-Y4-G02; DPE-Y4-G03; DPE-Y4-G04; DPE-Y4-G05; DPE-Y4-G06; DPE-Y4-G07; DPE-Y4-G08</x:v>
+        <x:v>DPE-Y4-T01; DPE-Y4-T02; DPE-Y4-T03; DPE-Y4-T04; DPE-Y4-T05; DPE-Y4-T06; DPE-Y4-T07; DPE-Y4-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>186</x:v>
@@ -44604,7 +44604,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>ELX-Y4-G01; ELX-Y4-G02; ELX-Y4-G03; ELX-Y4-G04; ELX-Y4-G05; ELX-Y4-G06; ELX-Y4-G07; ELX-Y4-G08</x:v>
+        <x:v>ELX-Y4-T01; ELX-Y4-T02; ELX-Y4-T03; ELX-Y4-T04; ELX-Y4-T05; ELX-Y4-T06; ELX-Y4-T07; ELX-Y4-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>191</x:v>
@@ -44645,7 +44645,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>ARC-Y3-G09; ARC-Y3-G10</x:v>
+        <x:v>ARC-Y3-T09; ARC-Y3-T10</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>48</x:v>
@@ -44686,7 +44686,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>PD-Y5-G01; PD-Y5-G02; PD-Y5-G03; PD-Y5-G04</x:v>
+        <x:v>PD-Y5-T01; PD-Y5-T02; PD-Y5-T03; PD-Y5-T04</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>87</x:v>
@@ -44727,7 +44727,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>ELX-Y4-G09; ELX-Y4-G10</x:v>
+        <x:v>ELX-Y4-T09; ELX-Y4-T10</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>46</x:v>
@@ -44768,7 +44768,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>DPE-Y4-G09; DPE-Y4-G10; DPE-Y4-G11</x:v>
+        <x:v>DPE-Y4-T09; DPE-Y4-T10; DPE-Y4-T11</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>69</x:v>
@@ -44793,7 +44793,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R199ca08fd99f4de2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R611897569ce74de3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45070,7 +45070,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MCT-Y3-G01; MCT-Y3-G02; MCT-Y3-G03; MCT-Y3-G04; MCT-Y3-G05; MCT-Y3-G06; MCT-Y3-G07; MCT-Y3-G08</x:v>
+        <x:v>MCT-Y3-T01; MCT-Y3-T02; MCT-Y3-T03; MCT-Y3-T04; MCT-Y3-T05; MCT-Y3-T06; MCT-Y3-T07; MCT-Y3-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>192</x:v>
@@ -45111,7 +45111,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MCT-Y3-G09; MCT-Y3-G10; MCT-Y3-G11</x:v>
+        <x:v>MCT-Y3-T09; MCT-Y3-T10; MCT-Y3-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>71</x:v>
@@ -45136,7 +45136,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91b9a11ba6634a80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bde4a95444440a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45433,7 +45433,7 @@
         <x:v>L06</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>ARC-Y5-G01; ARC-Y5-G02; ARC-Y5-G03; ARC-Y5-G04; ARC-Y5-G05; ARC-Y5-G06; ARC-Y5-G07; ARC-Y5-G08</x:v>
+        <x:v>ARC-Y5-T01; ARC-Y5-T02; ARC-Y5-T03; ARC-Y5-T04; ARC-Y5-T05; ARC-Y5-T06; ARC-Y5-T07; ARC-Y5-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>199</x:v>
@@ -45474,7 +45474,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MAT-Y5-G09; MAT-Y5-G10; DPE-Y5-G01; DPE-Y5-G02; DPE-Y5-G03; DPE-Y5-G04; DPE-Y5-G05; DPE-Y5-G06</x:v>
+        <x:v>MAT-Y5-T09; MAT-Y5-T10; DPE-Y5-T01; DPE-Y5-T02; DPE-Y5-T03; DPE-Y5-T04; DPE-Y5-T05; DPE-Y5-T06</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>192</x:v>
@@ -45515,7 +45515,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DPE-Y5-G07; DPE-Y5-G08; DPE-Y5-G09; DPE-Y5-G10; MCT-Y5-G01; MCT-Y5-G02; MCT-Y5-G03; MCT-Y5-G04</x:v>
+        <x:v>DPE-Y5-T07; DPE-Y5-T08; DPE-Y5-T09; DPE-Y5-T10; MCT-Y5-T01; MCT-Y5-T02; MCT-Y5-T03; MCT-Y5-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>192</x:v>
@@ -45556,7 +45556,7 @@
         <x:v>L07</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>ARC-Y5-G09</x:v>
+        <x:v>ARC-Y5-T09</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>24</x:v>
@@ -45597,7 +45597,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>MCT-Y5-G05; MCT-Y5-G06; MCT-Y5-G07; MCT-Y5-G08; MCT-Y5-G09; MCT-Y5-G10; CIV-Y5-G01; CIV-Y5-G02</x:v>
+        <x:v>MCT-Y5-T05; MCT-Y5-T06; MCT-Y5-T07; MCT-Y5-T08; MCT-Y5-T09; MCT-Y5-T10; CIV-Y5-T01; CIV-Y5-T02</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>190</x:v>
@@ -45638,7 +45638,7 @@
         <x:v>L05</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>CIV-Y5-G03; CIV-Y5-G04; CIV-Y5-G05; CIV-Y5-G06; CIV-Y5-G07; CIV-Y5-G08; CIV-Y5-G09; CIV-Y5-G10</x:v>
+        <x:v>CIV-Y5-T03; CIV-Y5-T04; CIV-Y5-T05; CIV-Y5-T06; CIV-Y5-T07; CIV-Y5-T08; CIV-Y5-T09; CIV-Y5-T10</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>192</x:v>
@@ -45679,7 +45679,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>MAT-Y5-G01; MAT-Y5-G02; MAT-Y5-G03; MAT-Y5-G04; MAT-Y5-G05; MAT-Y5-G06; MAT-Y5-G07; MAT-Y5-G08</x:v>
+        <x:v>MAT-Y5-T01; MAT-Y5-T02; MAT-Y5-T03; MAT-Y5-T04; MAT-Y5-T05; MAT-Y5-T06; MAT-Y5-T07; MAT-Y5-T08</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>191</x:v>
@@ -45704,7 +45704,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4eaf0df4d2074310"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07e01c3691b44168"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45977,7 +45977,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>LLS-Y1-G01; LLS-Y1-G02; LLS-Y1-G03</x:v>
+        <x:v>LLS-Y1-T01; LLS-Y1-T02; LLS-Y1-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>69</x:v>
@@ -46002,7 +46002,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0531368eeb304025"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0026109308614fcf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46275,7 +46275,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MSC-Y3-G01; MSC-Y3-G02</x:v>
+        <x:v>MSC-Y3-T01; MSC-Y3-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>48</x:v>
@@ -46300,7 +46300,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R937fe00c62664822"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39d1a86457ec4bb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46577,7 +46577,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MCT-Y1-G09; MCT-Y1-G10; MCT-Y1-G11; MCT-Y1-G12</x:v>
+        <x:v>MCT-Y1-T09; MCT-Y1-T10; MCT-Y1-T11; MCT-Y1-T12</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>96</x:v>
@@ -46618,7 +46618,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MCT-Y1-G01; MCT-Y1-G02; MCT-Y1-G03; MCT-Y1-G04; MCT-Y1-G05; MCT-Y1-G06; MCT-Y1-G07; MCT-Y1-G08</x:v>
+        <x:v>MCT-Y1-T01; MCT-Y1-T02; MCT-Y1-T03; MCT-Y1-T04; MCT-Y1-T05; MCT-Y1-T06; MCT-Y1-T07; MCT-Y1-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>192</x:v>
@@ -46643,7 +46643,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bbae0ad2f434650"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57ed3c8aa63448b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46920,7 +46920,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CPH-Y4-G01; CPH-Y4-G02; CPH-Y4-G03</x:v>
+        <x:v>CPH-Y4-T01; CPH-Y4-T02; CPH-Y4-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>70</x:v>
@@ -46961,7 +46961,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>PHR-Y3-G01; PHR-Y3-G02; PHR-Y3-G03; PHR-Y3-G04</x:v>
+        <x:v>PHR-Y3-T01; PHR-Y3-T02; PHR-Y3-T03; PHR-Y3-T04</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>84</x:v>
@@ -46986,7 +46986,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9444b9444ba04e10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65a6ae26577a4742"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47279,7 +47279,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MAT-Y3-G09; MAT-Y3-G10; MAT-Y3-G11</x:v>
+        <x:v>MAT-Y3-T09; MAT-Y3-T10; MAT-Y3-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>72</x:v>
@@ -47320,7 +47320,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MAT-Y3-G01; MAT-Y3-G02; MAT-Y3-G03; MAT-Y3-G04; MAT-Y3-G05; MAT-Y3-G06; MAT-Y3-G07; MAT-Y3-G08</x:v>
+        <x:v>MAT-Y3-T01; MAT-Y3-T02; MAT-Y3-T03; MAT-Y3-T04; MAT-Y3-T05; MAT-Y3-T06; MAT-Y3-T07; MAT-Y3-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>192</x:v>
@@ -47361,7 +47361,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DEN-Y2-G01; DEN-Y2-G02</x:v>
+        <x:v>DEN-Y2-T01; DEN-Y2-T02</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>44</x:v>
@@ -47402,7 +47402,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>COM-Y1-G01; COM-Y1-G02; COM-Y1-G03; COM-Y1-G04; COM-Y1-G05; COM-Y1-G06; COM-Y1-G07; COM-Y1-G08</x:v>
+        <x:v>COM-Y1-T01; COM-Y1-T02; COM-Y1-T03; COM-Y1-T04; COM-Y1-T05; COM-Y1-T06; COM-Y1-T07; COM-Y1-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>197</x:v>
@@ -47443,7 +47443,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>COM-Y1-G09; COM-Y1-G10; COM-Y1-G11</x:v>
+        <x:v>COM-Y1-T09; COM-Y1-T10; COM-Y1-T11</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>72</x:v>
@@ -47484,7 +47484,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>PHD-Y1-G01; PHD-Y1-G02; PHD-Y1-G03; PHD-Y1-G04</x:v>
+        <x:v>PHD-Y1-T01; PHD-Y1-T02; PHD-Y1-T03; PHD-Y1-T04</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>100</x:v>
@@ -47509,7 +47509,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R569b0fe4be6a4d54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78c49fa4e8524eee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47782,7 +47782,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>BI-Y1-G01; BI-Y1-G02; BI-Y1-G03; BI-Y1-G04</x:v>
+        <x:v>BI-Y1-T01; BI-Y1-T02; BI-Y1-T03; BI-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>94</x:v>
@@ -47807,7 +47807,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b206975fc2f460c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53cc045d0a4a482b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48088,7 +48088,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>COM-Y3-G01; COM-Y3-G02; COM-Y3-G03; COM-Y3-G04; COM-Y3-G05; COM-Y3-G06; COM-Y3-G07; COM-Y3-G08</x:v>
+        <x:v>COM-Y3-T01; COM-Y3-T02; COM-Y3-T03; COM-Y3-T04; COM-Y3-T05; COM-Y3-T06; COM-Y3-T07; COM-Y3-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>197</x:v>
@@ -48129,7 +48129,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>COM-Y3-G09; COM-Y3-G10</x:v>
+        <x:v>COM-Y3-T09; COM-Y3-T10</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>48</x:v>
@@ -48170,7 +48170,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>GM-Y4-G01; GM-Y4-G02</x:v>
+        <x:v>GM-Y4-T01; GM-Y4-T02</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>39</x:v>
@@ -48195,7 +48195,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bb03cb46edf496b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re28b7385e7624d17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48476,7 +48476,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PHR-Y5-G01; PHR-Y5-G02; PHR-Y5-G03; PHR-Y5-G04</x:v>
+        <x:v>PHR-Y5-T01; PHR-Y5-T02; PHR-Y5-T03; PHR-Y5-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>76</x:v>
@@ -48517,7 +48517,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>BIO-Y4-G01; BIO-Y4-G02; BIO-Y4-G03</x:v>
+        <x:v>BIO-Y4-T01; BIO-Y4-T02; BIO-Y4-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>52</x:v>
@@ -48558,7 +48558,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>BI-Y5-G01; BI-Y5-G02; BI-Y5-G03; BI-Y5-G04</x:v>
+        <x:v>BI-Y5-T01; BI-Y5-T02; BI-Y5-T03; BI-Y5-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>76</x:v>
@@ -48583,7 +48583,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2797f6c114204c01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73f1f910f0584cee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48868,7 +48868,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MCT-Y2-G01; MCT-Y2-G02; MCT-Y2-G03; MCT-Y2-G04; MCT-Y2-G05; MCT-Y2-G06; MCT-Y2-G07; MCT-Y2-G08</x:v>
+        <x:v>MCT-Y2-T01; MCT-Y2-T02; MCT-Y2-T03; MCT-Y2-T04; MCT-Y2-T05; MCT-Y2-T06; MCT-Y2-T07; MCT-Y2-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>200</x:v>
@@ -48909,7 +48909,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MCT-Y2-G09; MCT-Y2-G10; MCT-Y2-G11</x:v>
+        <x:v>MCT-Y2-T09; MCT-Y2-T10; MCT-Y2-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>75</x:v>
@@ -48950,7 +48950,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DMET-Y3-G09; DMET-Y3-G10</x:v>
+        <x:v>DMET-Y3-T09; DMET-Y3-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>50</x:v>
@@ -48991,7 +48991,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>DMET-Y3-G01; DMET-Y3-G02; DMET-Y3-G03; DMET-Y3-G04; DMET-Y3-G05; DMET-Y3-G06; DMET-Y3-G07; DMET-Y3-G08</x:v>
+        <x:v>DMET-Y3-T01; DMET-Y3-T02; DMET-Y3-T03; DMET-Y3-T04; DMET-Y3-T05; DMET-Y3-T06; DMET-Y3-T07; DMET-Y3-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>200</x:v>
@@ -49016,7 +49016,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra54a9b2eede343ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3c436e60d5f4535"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49301,7 +49301,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DMET-Y2-G06; DMET-Y2-G07; DMET-Y2-G08; DMET-Y2-G09; DMET-Y2-G10; DMET-Y2-G11</x:v>
+        <x:v>DMET-Y2-T06; DMET-Y2-T07; DMET-Y2-T08; DMET-Y2-T09; DMET-Y2-T10; DMET-Y2-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>143</x:v>
@@ -49342,7 +49342,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>LLS-Y4-G01; LLS-Y4-G02; LLS-Y4-G03</x:v>
+        <x:v>LLS-Y4-T01; LLS-Y4-T02; LLS-Y4-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>59</x:v>
@@ -49383,7 +49383,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CSE-Y2-G01; CSE-Y2-G02; CSE-Y2-G03; CSE-Y2-G04; CSE-Y2-G05; CSE-Y2-G06; CSE-Y2-G07; CSE-Y2-G08</x:v>
+        <x:v>CSE-Y2-T01; CSE-Y2-T02; CSE-Y2-T03; CSE-Y2-T04; CSE-Y2-T05; CSE-Y2-T06; CSE-Y2-T07; CSE-Y2-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>196</x:v>
@@ -49424,7 +49424,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>CSE-Y2-G09; CSE-Y2-G10; CSE-Y2-G11; DMET-Y2-G01; DMET-Y2-G02; DMET-Y2-G03; DMET-Y2-G04; DMET-Y2-G05</x:v>
+        <x:v>CSE-Y2-T09; CSE-Y2-T10; CSE-Y2-T11; DMET-Y2-T01; DMET-Y2-T02; DMET-Y2-T03; DMET-Y2-T04; DMET-Y2-T05</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>192</x:v>
@@ -49449,7 +49449,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R867c6a5d3cf04b75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72b243b2a04c4ca7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49734,7 +49734,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PGD-Y1-G01; PGD-Y1-G02; PGD-Y1-G03</x:v>
+        <x:v>PGD-Y1-T01; PGD-Y1-T02; PGD-Y1-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>63</x:v>
@@ -49775,7 +49775,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MAT-Y1-G01; MAT-Y1-G02; MAT-Y1-G03; MAT-Y1-G04; MAT-Y1-G05; MAT-Y1-G06; MAT-Y1-G07; MAT-Y1-G08</x:v>
+        <x:v>MAT-Y1-T01; MAT-Y1-T02; MAT-Y1-T03; MAT-Y1-T04; MAT-Y1-T05; MAT-Y1-T06; MAT-Y1-T07; MAT-Y1-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>193</x:v>
@@ -49816,7 +49816,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MAT-Y1-G09; MAT-Y1-G10; MAT-Y1-G11; MAT-Y1-G12</x:v>
+        <x:v>MAT-Y1-T09; MAT-Y1-T10; MAT-Y1-T11; MAT-Y1-T12</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>96</x:v>
@@ -49857,7 +49857,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>PHD-Y3-G01; PHD-Y3-G02; PHD-Y3-G03; PHD-Y3-G04</x:v>
+        <x:v>PHD-Y3-T01; PHD-Y3-T02; PHD-Y3-T03; PHD-Y3-T04</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>92</x:v>
@@ -49882,7 +49882,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1eb8421e2cd04557"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1ec8e8aa38b4376"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50203,7 +50203,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PD-Y2-G01; PD-Y2-G02; PD-Y2-G03; PD-Y2-G04; PD-Y2-G05</x:v>
+        <x:v>PD-Y2-T01; PD-Y2-T02; PD-Y2-T03; PD-Y2-T04; PD-Y2-T05</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>101</x:v>
@@ -50244,7 +50244,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>MCT-Y2-G01; MCT-Y2-G02; MCT-Y2-G03; MCT-Y2-G04; MCT-Y2-G05; MCT-Y2-G06; MCT-Y2-G07; MCT-Y2-G08</x:v>
+        <x:v>MCT-Y2-T01; MCT-Y2-T02; MCT-Y2-T03; MCT-Y2-T04; MCT-Y2-T05; MCT-Y2-T06; MCT-Y2-T07; MCT-Y2-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>200</x:v>
@@ -50285,7 +50285,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DMET-Y3-G06; DMET-Y3-G07; DMET-Y3-G08; DMET-Y3-G09; DMET-Y3-G10</x:v>
+        <x:v>DMET-Y3-T06; DMET-Y3-T07; DMET-Y3-T08; DMET-Y3-T09; DMET-Y3-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>125</x:v>
@@ -50326,7 +50326,7 @@
         <x:v>L08</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>ARC-Y2-G10; ARC-Y2-G11</x:v>
+        <x:v>ARC-Y2-T10; ARC-Y2-T11</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>46</x:v>
@@ -50367,7 +50367,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>DPE-Y2-G05; DPE-Y2-G06; DPE-Y2-G07; DPE-Y2-G08; DPE-Y2-G09; DPE-Y2-G10; DPE-Y2-G11; DPE-Y2-G12</x:v>
+        <x:v>DPE-Y2-T05; DPE-Y2-T06; DPE-Y2-T07; DPE-Y2-T08; DPE-Y2-T09; DPE-Y2-T10; DPE-Y2-T11; DPE-Y2-T12</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>186</x:v>
@@ -50408,7 +50408,7 @@
         <x:v>L07</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>ARC-Y2-G02; ARC-Y2-G03; ARC-Y2-G04; ARC-Y2-G05; ARC-Y2-G06; ARC-Y2-G07; ARC-Y2-G08; ARC-Y2-G09</x:v>
+        <x:v>ARC-Y2-T02; ARC-Y2-T03; ARC-Y2-T04; ARC-Y2-T05; ARC-Y2-T06; ARC-Y2-T07; ARC-Y2-T08; ARC-Y2-T09</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>189</x:v>
@@ -50449,7 +50449,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K22" s="51" t="str">
-        <x:v>CSE-Y3-G09; CSE-Y3-G10; CSE-Y3-G11; DMET-Y3-G01; DMET-Y3-G02; DMET-Y3-G03; DMET-Y3-G04; DMET-Y3-G05</x:v>
+        <x:v>CSE-Y3-T09; CSE-Y3-T10; CSE-Y3-T11; DMET-Y3-T01; DMET-Y3-T02; DMET-Y3-T03; DMET-Y3-T04; DMET-Y3-T05</x:v>
       </x:c>
       <x:c r="L22" s="51" t="n">
         <x:v>194</x:v>
@@ -50490,7 +50490,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K23" s="51" t="str">
-        <x:v>GD-Y4-G01; GD-Y4-G02</x:v>
+        <x:v>GD-Y4-T01; GD-Y4-T02</x:v>
       </x:c>
       <x:c r="L23" s="51" t="n">
         <x:v>43</x:v>
@@ -50531,7 +50531,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K24" s="51" t="str">
-        <x:v>CSE-Y3-G01; CSE-Y3-G02; CSE-Y3-G03; CSE-Y3-G04; CSE-Y3-G05; CSE-Y3-G06; CSE-Y3-G07; CSE-Y3-G08</x:v>
+        <x:v>CSE-Y3-T01; CSE-Y3-T02; CSE-Y3-T03; CSE-Y3-T04; CSE-Y3-T05; CSE-Y3-T06; CSE-Y3-T07; CSE-Y3-T08</x:v>
       </x:c>
       <x:c r="L24" s="51" t="n">
         <x:v>186</x:v>
@@ -50572,7 +50572,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K25" s="51" t="str">
-        <x:v>MAT-Y2-G09; MAT-Y2-G10; MAT-Y2-G11; MAT-Y2-G12; DPE-Y2-G01; DPE-Y2-G02; DPE-Y2-G03; DPE-Y2-G04</x:v>
+        <x:v>MAT-Y2-T09; MAT-Y2-T10; MAT-Y2-T11; MAT-Y2-T12; DPE-Y2-T01; DPE-Y2-T02; DPE-Y2-T03; DPE-Y2-T04</x:v>
       </x:c>
       <x:c r="L25" s="51" t="n">
         <x:v>188</x:v>
@@ -50613,7 +50613,7 @@
         <x:v>L06</x:v>
       </x:c>
       <x:c r="K26" s="51" t="str">
-        <x:v>CIV-Y2-G06; CIV-Y2-G07; CIV-Y2-G08; CIV-Y2-G09; CIV-Y2-G10; CIV-Y2-G11; CIV-Y2-G12; ARC-Y2-G01</x:v>
+        <x:v>CIV-Y2-T06; CIV-Y2-T07; CIV-Y2-T08; CIV-Y2-T09; CIV-Y2-T10; CIV-Y2-T11; CIV-Y2-T12; ARC-Y2-T01</x:v>
       </x:c>
       <x:c r="L26" s="51" t="n">
         <x:v>186</x:v>
@@ -50654,7 +50654,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K27" s="51" t="str">
-        <x:v>MAT-Y2-G01; MAT-Y2-G02; MAT-Y2-G03; MAT-Y2-G04; MAT-Y2-G05; MAT-Y2-G06; MAT-Y2-G07; MAT-Y2-G08</x:v>
+        <x:v>MAT-Y2-T01; MAT-Y2-T02; MAT-Y2-T03; MAT-Y2-T04; MAT-Y2-T05; MAT-Y2-T06; MAT-Y2-T07; MAT-Y2-T08</x:v>
       </x:c>
       <x:c r="L27" s="51" t="n">
         <x:v>184</x:v>
@@ -50695,7 +50695,7 @@
         <x:v>L05</x:v>
       </x:c>
       <x:c r="K28" s="51" t="str">
-        <x:v>MCT-Y2-G09; MCT-Y2-G10; MCT-Y2-G11; CIV-Y2-G01; CIV-Y2-G02; CIV-Y2-G03; CIV-Y2-G04; CIV-Y2-G05</x:v>
+        <x:v>MCT-Y2-T09; MCT-Y2-T10; MCT-Y2-T11; CIV-Y2-T01; CIV-Y2-T02; CIV-Y2-T03; CIV-Y2-T04; CIV-Y2-T05</x:v>
       </x:c>
       <x:c r="L28" s="51" t="n">
         <x:v>195</x:v>
@@ -50720,7 +50720,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82004c1918e24473"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb1eff47d344907"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51001,7 +51001,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>COM-Y2-G09; COM-Y2-G10; COM-Y2-G11</x:v>
+        <x:v>COM-Y2-T09; COM-Y2-T10; COM-Y2-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>69</x:v>
@@ -51042,7 +51042,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>COM-Y2-G01; COM-Y2-G02; COM-Y2-G03; COM-Y2-G04; COM-Y2-G05; COM-Y2-G06; COM-Y2-G07; COM-Y2-G08</x:v>
+        <x:v>COM-Y2-T01; COM-Y2-T02; COM-Y2-T03; COM-Y2-T04; COM-Y2-T05; COM-Y2-T06; COM-Y2-T07; COM-Y2-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>188</x:v>
@@ -51083,7 +51083,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>LLS-Y3-G01; LLS-Y3-G02; LLS-Y3-G03</x:v>
+        <x:v>LLS-Y3-T01; LLS-Y3-T02; LLS-Y3-T03</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>62</x:v>
@@ -51108,7 +51108,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6229141f59494f5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08b3ed8ed96347c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51393,7 +51393,7 @@
         <x:v>L04</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>ELX-Y3-G04; ELX-Y3-G05; ELX-Y3-G06; ELX-Y3-G07; ELX-Y3-G08; ELX-Y3-G09; ELX-Y3-G10</x:v>
+        <x:v>ELX-Y3-T04; ELX-Y3-T05; ELX-Y3-T06; ELX-Y3-T07; ELX-Y3-T08; ELX-Y3-T09; ELX-Y3-T10</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>175</x:v>
@@ -51434,7 +51434,7 @@
         <x:v>L03</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>COM-Y3-G06; COM-Y3-G07; COM-Y3-G08; COM-Y3-G09; COM-Y3-G10; ELX-Y3-G01; ELX-Y3-G02; ELX-Y3-G03</x:v>
+        <x:v>COM-Y3-T06; COM-Y3-T07; COM-Y3-T08; COM-Y3-T09; COM-Y3-T10; ELX-Y3-T01; ELX-Y3-T02; ELX-Y3-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>195</x:v>
@@ -51475,7 +51475,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>NET-Y3-G09; NET-Y3-G10; NET-Y3-G11; COM-Y3-G01; COM-Y3-G02; COM-Y3-G03; COM-Y3-G04; COM-Y3-G05</x:v>
+        <x:v>NET-Y3-T09; NET-Y3-T10; NET-Y3-T11; COM-Y3-T01; COM-Y3-T02; COM-Y3-T03; COM-Y3-T04; COM-Y3-T05</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>194</x:v>
@@ -51516,7 +51516,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>NET-Y3-G01; NET-Y3-G02; NET-Y3-G03; NET-Y3-G04; NET-Y3-G05; NET-Y3-G06; NET-Y3-G07; NET-Y3-G08</x:v>
+        <x:v>NET-Y3-T01; NET-Y3-T02; NET-Y3-T03; NET-Y3-T04; NET-Y3-T05; NET-Y3-T06; NET-Y3-T07; NET-Y3-T08</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>190</x:v>
@@ -51541,7 +51541,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4882f9ae496048d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe98073e5968465f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51822,7 +51822,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CSE-Y2-G01; CSE-Y2-G02; CSE-Y2-G03; CSE-Y2-G04; CSE-Y2-G05; CSE-Y2-G06; CSE-Y2-G07; CSE-Y2-G08</x:v>
+        <x:v>CSE-Y2-T01; CSE-Y2-T02; CSE-Y2-T03; CSE-Y2-T04; CSE-Y2-T05; CSE-Y2-T06; CSE-Y2-T07; CSE-Y2-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>196</x:v>
@@ -51863,7 +51863,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CSE-Y2-G09; CSE-Y2-G10; CSE-Y2-G11</x:v>
+        <x:v>CSE-Y2-T09; CSE-Y2-T10; CSE-Y2-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>72</x:v>
@@ -51904,7 +51904,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>GD-Y3-G01; GD-Y3-G02</x:v>
+        <x:v>GD-Y3-T01; GD-Y3-T02</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>45</x:v>
@@ -51929,7 +51929,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b0cca811136447a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc862be1437421a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52210,7 +52210,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PGD-Y2-G01; PGD-Y2-G02; PGD-Y2-G03</x:v>
+        <x:v>PGD-Y2-T01; PGD-Y2-T02; PGD-Y2-T03</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>60</x:v>
@@ -52251,7 +52251,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>GD-Y5-G01; GD-Y5-G02</x:v>
+        <x:v>GD-Y5-T01; GD-Y5-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>40</x:v>
@@ -52292,7 +52292,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MD-Y2-G01; MD-Y2-G02; MD-Y2-G03; MD-Y2-G04</x:v>
+        <x:v>MD-Y2-T01; MD-Y2-T02; MD-Y2-T03; MD-Y2-T04</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>99</x:v>
@@ -52317,7 +52317,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18b09302fadf4e94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re252502fd6b14d4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52590,7 +52590,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>TBM-Y1-G01; TBM-Y1-G02; TBM-Y1-G03; TBM-Y1-G04</x:v>
+        <x:v>TBM-Y1-T01; TBM-Y1-T02; TBM-Y1-T03; TBM-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>96</x:v>
@@ -52615,7 +52615,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa9ed503f1c140b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2385224afe054879"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52904,7 +52904,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MAT-Y3-G01; MAT-Y3-G02; MAT-Y3-G03; MAT-Y3-G04; MAT-Y3-G05; MAT-Y3-G06; MAT-Y3-G07; MAT-Y3-G08</x:v>
+        <x:v>MAT-Y3-T01; MAT-Y3-T02; MAT-Y3-T03; MAT-Y3-T04; MAT-Y3-T05; MAT-Y3-T06; MAT-Y3-T07; MAT-Y3-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>192</x:v>
@@ -52945,7 +52945,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>COM-Y1-G09; COM-Y1-G10; COM-Y1-G11</x:v>
+        <x:v>COM-Y1-T09; COM-Y1-T10; COM-Y1-T11</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>72</x:v>
@@ -52986,7 +52986,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>MAT-Y3-G09; MAT-Y3-G10; MAT-Y3-G11</x:v>
+        <x:v>MAT-Y3-T09; MAT-Y3-T10; MAT-Y3-T11</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>72</x:v>
@@ -53027,7 +53027,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>PHD-Y1-G01; PHD-Y1-G02; PHD-Y1-G03; PHD-Y1-G04</x:v>
+        <x:v>PHD-Y1-T01; PHD-Y1-T02; PHD-Y1-T03; PHD-Y1-T04</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>100</x:v>
@@ -53068,7 +53068,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>COM-Y1-G01; COM-Y1-G02; COM-Y1-G03; COM-Y1-G04; COM-Y1-G05; COM-Y1-G06; COM-Y1-G07; COM-Y1-G08</x:v>
+        <x:v>COM-Y1-T01; COM-Y1-T02; COM-Y1-T03; COM-Y1-T04; COM-Y1-T05; COM-Y1-T06; COM-Y1-T07; COM-Y1-T08</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>197</x:v>
@@ -53093,7 +53093,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85bc51c7be634a68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3af3cf809e514d5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53366,7 +53366,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DEN-Y4-G01; DEN-Y4-G02</x:v>
+        <x:v>DEN-Y4-T01; DEN-Y4-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>41</x:v>
@@ -53391,7 +53391,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb50685f948a4eb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R909ead148bd54061"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53664,7 +53664,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>BI-Y1-G01; BI-Y1-G02; BI-Y1-G03; BI-Y1-G04</x:v>
+        <x:v>BI-Y1-T01; BI-Y1-T02; BI-Y1-T03; BI-Y1-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>94</x:v>
@@ -53689,7 +53689,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re608732e887e4c47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3a591d3f54f4364"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53970,7 +53970,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>GM-Y4-G01; GM-Y4-G02</x:v>
+        <x:v>GM-Y4-T01; GM-Y4-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>39</x:v>
@@ -54011,7 +54011,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>COM-Y3-G01; COM-Y3-G02; COM-Y3-G03; COM-Y3-G04; COM-Y3-G05; COM-Y3-G06; COM-Y3-G07; COM-Y3-G08</x:v>
+        <x:v>COM-Y3-T01; COM-Y3-T02; COM-Y3-T03; COM-Y3-T04; COM-Y3-T05; COM-Y3-T06; COM-Y3-T07; COM-Y3-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>197</x:v>
@@ -54052,7 +54052,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>COM-Y3-G09; COM-Y3-G10</x:v>
+        <x:v>COM-Y3-T09; COM-Y3-T10</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>48</x:v>
@@ -54077,7 +54077,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb31d8540658744df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra35f9395b63449ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54354,7 +54354,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PHD-Y4-G01; PHD-Y4-G02; PHD-Y4-G03; PHD-Y4-G04</x:v>
+        <x:v>PHD-Y4-T01; PHD-Y4-T02; PHD-Y4-T03; PHD-Y4-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>88</x:v>
@@ -54395,7 +54395,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DEN-Y2-G01; DEN-Y2-G02</x:v>
+        <x:v>DEN-Y2-T01; DEN-Y2-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>44</x:v>
@@ -54420,7 +54420,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R976939f1a1dd499a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdcc6dfd1344404a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54697,7 +54697,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PD-Y2-G01; PD-Y2-G02; PD-Y2-G03; PD-Y2-G04; PD-Y2-G05</x:v>
+        <x:v>PD-Y2-T01; PD-Y2-T02; PD-Y2-T03; PD-Y2-T04; PD-Y2-T05</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>101</x:v>
@@ -54738,7 +54738,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>GD-Y4-G01; GD-Y4-G02</x:v>
+        <x:v>GD-Y4-T01; GD-Y4-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>43</x:v>
@@ -54763,7 +54763,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re150d477b73c441c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a6a6d5dbb984310"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55048,7 +55048,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DPE-Y5-G01; DPE-Y5-G02; DPE-Y5-G03; DPE-Y5-G04; DPE-Y5-G05; DPE-Y5-G06; DPE-Y5-G07; DPE-Y5-G08</x:v>
+        <x:v>DPE-Y5-T01; DPE-Y5-T02; DPE-Y5-T03; DPE-Y5-T04; DPE-Y5-T05; DPE-Y5-T06; DPE-Y5-T07; DPE-Y5-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>194</x:v>
@@ -55089,7 +55089,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>ELX-Y5-G09</x:v>
+        <x:v>ELX-Y5-T09</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>24</x:v>
@@ -55130,7 +55130,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>ELX-Y5-G01; ELX-Y5-G02; ELX-Y5-G03; ELX-Y5-G04; ELX-Y5-G05; ELX-Y5-G06; ELX-Y5-G07; ELX-Y5-G08</x:v>
+        <x:v>ELX-Y5-T01; ELX-Y5-T02; ELX-Y5-T03; ELX-Y5-T04; ELX-Y5-T05; ELX-Y5-T06; ELX-Y5-T07; ELX-Y5-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>200</x:v>
@@ -55171,7 +55171,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>DPE-Y5-G09; DPE-Y5-G10</x:v>
+        <x:v>DPE-Y5-T09; DPE-Y5-T10</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>48</x:v>
@@ -55196,7 +55196,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5415299f8d1a4f75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R722072602b0c475e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55489,7 +55489,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>TBM-Y2-G03; TBM-Y2-G04</x:v>
+        <x:v>TBM-Y2-T03; TBM-Y2-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>46</x:v>
@@ -55530,7 +55530,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>GM-Y3-G01; GM-Y3-G02</x:v>
+        <x:v>GM-Y3-T01; GM-Y3-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>40</x:v>
@@ -55571,7 +55571,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>GM-Y2-G01; GM-Y2-G02; BI-Y2-G01; BI-Y2-G02; BI-Y2-G03; BI-Y2-G04; TBM-Y2-G01; TBM-Y2-G02</x:v>
+        <x:v>GM-Y2-T01; GM-Y2-T02; BI-Y2-T01; BI-Y2-T02; BI-Y2-T03; BI-Y2-T04; TBM-Y2-T01; TBM-Y2-T02</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>179</x:v>
@@ -55612,7 +55612,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>PD-Y2-G03; PD-Y2-G04; PD-Y2-G05</x:v>
+        <x:v>PD-Y2-T03; PD-Y2-T04; PD-Y2-T05</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>60</x:v>
@@ -55653,7 +55653,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K20" s="51" t="str">
-        <x:v>GD-Y2-G01; GD-Y2-G02; MD-Y2-G01; MD-Y2-G02; MD-Y2-G03; MD-Y2-G04; PD-Y2-G01; PD-Y2-G02</x:v>
+        <x:v>GD-Y2-T01; GD-Y2-T02; MD-Y2-T01; MD-Y2-T02; MD-Y2-T03; MD-Y2-T04; PD-Y2-T01; PD-Y2-T02</x:v>
       </x:c>
       <x:c r="L20" s="51" t="n">
         <x:v>186</x:v>
@@ -55694,7 +55694,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K21" s="51" t="str">
-        <x:v>LLS-Y5-G01; LLS-Y5-G02; LLS-Y5-G03</x:v>
+        <x:v>LLS-Y5-T01; LLS-Y5-T02; LLS-Y5-T03</x:v>
       </x:c>
       <x:c r="L21" s="51" t="n">
         <x:v>56</x:v>
@@ -55719,7 +55719,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c70270c113740d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfea2439da1b4438"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56000,7 +56000,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>COM-Y2-G09; COM-Y2-G10; COM-Y2-G11</x:v>
+        <x:v>COM-Y2-T09; COM-Y2-T10; COM-Y2-T11</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>69</x:v>
@@ -56041,7 +56041,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>LLS-Y3-G01; LLS-Y3-G02; LLS-Y3-G03</x:v>
+        <x:v>LLS-Y3-T01; LLS-Y3-T02; LLS-Y3-T03</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>62</x:v>
@@ -56082,7 +56082,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>COM-Y2-G01; COM-Y2-G02; COM-Y2-G03; COM-Y2-G04; COM-Y2-G05; COM-Y2-G06; COM-Y2-G07; COM-Y2-G08</x:v>
+        <x:v>COM-Y2-T01; COM-Y2-T02; COM-Y2-T03; COM-Y2-T04; COM-Y2-T05; COM-Y2-T06; COM-Y2-T07; COM-Y2-T08</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>188</x:v>
@@ -56107,7 +56107,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04ad5c81046e4e85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74173f588a1b4e3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56380,7 +56380,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>GM-Y3-G01; GM-Y3-G02</x:v>
+        <x:v>GM-Y3-T01; GM-Y3-T02</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>40</x:v>
@@ -56405,7 +56405,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7b9b6d6884b4805"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R749c6769e970491f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56686,7 +56686,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>MD-Y3-G01; MD-Y3-G02; MD-Y3-G03; MD-Y3-G04</x:v>
+        <x:v>MD-Y3-T01; MD-Y3-T02; MD-Y3-T03; MD-Y3-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>94</x:v>
@@ -56727,7 +56727,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>DEN-Y3-G01; DEN-Y3-G02</x:v>
+        <x:v>DEN-Y3-T01; DEN-Y3-T02</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>43</x:v>
@@ -56768,7 +56768,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>PGD-Y3-G01; PGD-Y3-G02; PGD-Y3-G03</x:v>
+        <x:v>PGD-Y3-T01; PGD-Y3-T02; PGD-Y3-T03</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>57</x:v>
@@ -56793,7 +56793,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f1a927e00a54d70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeff6fdec2254382"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57074,7 +57074,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>CSE-Y4-G09; CSE-Y4-G10</x:v>
+        <x:v>CSE-Y4-T09; CSE-Y4-T10</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>48</x:v>
@@ -57115,7 +57115,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CSE-Y4-G01; CSE-Y4-G02; CSE-Y4-G03; CSE-Y4-G04; CSE-Y4-G05; CSE-Y4-G06; CSE-Y4-G07; CSE-Y4-G08</x:v>
+        <x:v>CSE-Y4-T01; CSE-Y4-T02; CSE-Y4-T03; CSE-Y4-T04; CSE-Y4-T05; CSE-Y4-T06; CSE-Y4-T07; CSE-Y4-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>195</x:v>
@@ -57156,7 +57156,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CPH-Y5-G01; CPH-Y5-G02; CPH-Y5-G03</x:v>
+        <x:v>CPH-Y5-T01; CPH-Y5-T02; CPH-Y5-T03</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>66</x:v>
@@ -57181,7 +57181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb9a98cca9864ba9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b21dba3bd04051"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57466,7 +57466,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>TBM-Y3-G01; TBM-Y3-G02; TBM-Y3-G03; TBM-Y3-G04</x:v>
+        <x:v>TBM-Y3-T01; TBM-Y3-T02; TBM-Y3-T03; TBM-Y3-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>87</x:v>
@@ -57507,7 +57507,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CIV-Y4-G01; CIV-Y4-G02; CIV-Y4-G03; CIV-Y4-G04; CIV-Y4-G05; CIV-Y4-G06; CIV-Y4-G07; CIV-Y4-G08</x:v>
+        <x:v>CIV-Y4-T01; CIV-Y4-T02; CIV-Y4-T03; CIV-Y4-T04; CIV-Y4-T05; CIV-Y4-T06; CIV-Y4-T07; CIV-Y4-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>187</x:v>
@@ -57548,7 +57548,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>CIV-Y4-G09; CIV-Y4-G10; CIV-Y4-G11</x:v>
+        <x:v>CIV-Y4-T09; CIV-Y4-T10; CIV-Y4-T11</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>69</x:v>
@@ -57589,7 +57589,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>MSC-Y2-G01; MSC-Y2-G02</x:v>
+        <x:v>MSC-Y2-T01; MSC-Y2-T02</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>50</x:v>
@@ -57614,7 +57614,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc27d97efa7a1414c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56cee589530d4d21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57887,7 +57887,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>PGD-Y5-G01; PGD-Y5-G02; PGD-Y5-G03; MSC-Y5-G01; MSC-Y5-G02; PHD-Y5-G01; PHD-Y5-G02; PHD-Y5-G03; PHD-Y5-G04</x:v>
+        <x:v>PGD-Y5-T01; PGD-Y5-T02; PGD-Y5-T03; MSC-Y5-T01; MSC-Y5-T02; PHD-Y5-T01; PHD-Y5-T02; PHD-Y5-T03; PHD-Y5-T04</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>177</x:v>
@@ -57912,7 +57912,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20e6f953c9854098"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58c7eb63a9d449d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -58197,7 +58197,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K16" s="51" t="str">
-        <x:v>DMET-Y2-G01; DMET-Y2-G02; DMET-Y2-G03; DMET-Y2-G04; DMET-Y2-G05; DMET-Y2-G06; DMET-Y2-G07; DMET-Y2-G08</x:v>
+        <x:v>DMET-Y2-T01; DMET-Y2-T02; DMET-Y2-T03; DMET-Y2-T04; DMET-Y2-T05; DMET-Y2-T06; DMET-Y2-T07; DMET-Y2-T08</x:v>
       </x:c>
       <x:c r="L16" s="51" t="n">
         <x:v>192</x:v>
@@ -58238,7 +58238,7 @@
         <x:v>L01</x:v>
       </x:c>
       <x:c r="K17" s="51" t="str">
-        <x:v>CIV-Y5-G01; CIV-Y5-G02; CIV-Y5-G03; CIV-Y5-G04; CIV-Y5-G05; CIV-Y5-G06; CIV-Y5-G07; CIV-Y5-G08</x:v>
+        <x:v>CIV-Y5-T01; CIV-Y5-T02; CIV-Y5-T03; CIV-Y5-T04; CIV-Y5-T05; CIV-Y5-T06; CIV-Y5-T07; CIV-Y5-T08</x:v>
       </x:c>
       <x:c r="L17" s="51" t="n">
         <x:v>194</x:v>
@@ -58279,7 +58279,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K18" s="51" t="str">
-        <x:v>DMET-Y2-G09; DMET-Y2-G10; DMET-Y2-G11</x:v>
+        <x:v>DMET-Y2-T09; DMET-Y2-T10; DMET-Y2-T11</x:v>
       </x:c>
       <x:c r="L18" s="51" t="n">
         <x:v>71</x:v>
@@ -58320,7 +58320,7 @@
         <x:v>L02</x:v>
       </x:c>
       <x:c r="K19" s="51" t="str">
-        <x:v>CIV-Y5-G09; CIV-Y5-G10</x:v>
+        <x:v>CIV-Y5-T09; CIV-Y5-T10</x:v>
       </x:c>
       <x:c r="L19" s="51" t="n">
         <x:v>48</x:v>
@@ -58345,7 +58345,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cee5621383f4058"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R121775c9758e4619"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/fake data/Doctor Schedule Calendar.xlsx
+++ b/fake data/Doctor Schedule Calendar.xlsx
@@ -2,129 +2,129 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doctor Directory" sheetId="1" r:id="R5ec392f1ffcf40d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D001" sheetId="2" r:id="R3fb23f85761c45f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D002" sheetId="3" r:id="R683cad98308043a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D003" sheetId="4" r:id="Rd16c3e707ab1488a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D004" sheetId="5" r:id="R1120713ef47d4181"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D005" sheetId="6" r:id="Rcf24e805ebb9487a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D006" sheetId="7" r:id="R4278363331794219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D007" sheetId="8" r:id="Rac0220519f1846b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D008" sheetId="9" r:id="R2bf7c08a6cdc427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D009" sheetId="10" r:id="R37e5a3028be64b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D010" sheetId="11" r:id="R881deccf7a824f43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D011" sheetId="12" r:id="Rca73fb7749344f8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D012" sheetId="13" r:id="R9718b23cdbf444f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D013" sheetId="14" r:id="R294ef4e477f44151"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D014" sheetId="15" r:id="Reb598a1ee9b54798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D015" sheetId="16" r:id="R45e766e368584b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D016" sheetId="17" r:id="Re0f95e7c85dc4b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D017" sheetId="18" r:id="R81a25eda691e447f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D018" sheetId="19" r:id="R3c765f2297494768"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D019" sheetId="20" r:id="R14316e8a277a4ce9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D020" sheetId="21" r:id="R6c2a0066a0a649ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D021" sheetId="22" r:id="R844ff0d273b84648"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D022" sheetId="23" r:id="R56412824841f4762"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D023" sheetId="24" r:id="R3e63715eae484a47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D024" sheetId="25" r:id="Rfac8ac1213544be9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D025" sheetId="26" r:id="R37132d90559c4600"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D026" sheetId="27" r:id="Ra8ca2e98cdf84c11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D027" sheetId="28" r:id="R9bcd3883553548e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D028" sheetId="29" r:id="R8dbc3b341f434d62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D029" sheetId="30" r:id="R37752431c958477e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D030" sheetId="31" r:id="R1113346bf67f46b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D031" sheetId="32" r:id="Re9bba3596dab4618"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D032" sheetId="33" r:id="R8422300ffc04410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D033" sheetId="34" r:id="Red4543e740584a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D034" sheetId="35" r:id="Ra9536ef674f34b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D035" sheetId="36" r:id="R6deac1449fdc460f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D036" sheetId="37" r:id="R48c31de770ff45f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D037" sheetId="38" r:id="R71c2c664acf64716"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D038" sheetId="39" r:id="R1a8b0bbbf00b4e7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D039" sheetId="40" r:id="Re7d73a0fc0b14ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D040" sheetId="41" r:id="R664b7fa9cffb4dca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D041" sheetId="42" r:id="R4fe2a8adf5bf44f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D042" sheetId="43" r:id="R930041c2542c47ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D043" sheetId="44" r:id="R8c453cca56a44e05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D044" sheetId="45" r:id="R838801d7ced44e7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D045" sheetId="46" r:id="R375a13db08e54529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D046" sheetId="47" r:id="R7c8888fc93514522"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D047" sheetId="48" r:id="R6efc43eb5f9c4f92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D048" sheetId="49" r:id="Rd1a241edca9f44c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D049" sheetId="50" r:id="Rbe8595059ac54348"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D050" sheetId="51" r:id="R8c254c632cb24773"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D051" sheetId="52" r:id="Rc4d5804118b14541"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D052" sheetId="53" r:id="R4d8276f041ee42a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D053" sheetId="54" r:id="Rb519933e9b1042c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D054" sheetId="55" r:id="R90a4a525081b4f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D055" sheetId="56" r:id="R4f34c371c5924718"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D056" sheetId="57" r:id="R1efd4c76de10412c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D057" sheetId="58" r:id="Rad4bbef5afe743eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D058" sheetId="59" r:id="R43d3125093ab45f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D059" sheetId="60" r:id="Rafcb25455aaf4ea7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D060" sheetId="61" r:id="R2e5f8025c1df4457"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D061" sheetId="62" r:id="R6c02a8bfbd7e4408"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D062" sheetId="63" r:id="R2be3fa3b8b9840c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D063" sheetId="64" r:id="R080f0bf3849f49ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D064" sheetId="65" r:id="R3392ba9fb4064c6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D065" sheetId="66" r:id="R6807d1c88e0044b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D066" sheetId="67" r:id="R6cb301630cae47d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D067" sheetId="68" r:id="Rf154cc8cdd5f49f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D068" sheetId="69" r:id="R03d92d6daaa04b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D069" sheetId="70" r:id="Rce0207ecda714e4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D070" sheetId="71" r:id="R2dc385c1463f4105"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D071" sheetId="72" r:id="R705b32e16db9496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D072" sheetId="73" r:id="Rf9ae9f323fef4d9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D073" sheetId="74" r:id="Re35e7a64aa784bd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D074" sheetId="75" r:id="Rcdd2a534f4bd48ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D075" sheetId="76" r:id="Ra816fa3f0e07457c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D076" sheetId="77" r:id="R85612db9f94c4ad4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D077" sheetId="78" r:id="R83d5a8bbf9ae4a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D078" sheetId="79" r:id="R3e190b93e7ec4d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D079" sheetId="80" r:id="R25c48d5e837b4d1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D080" sheetId="81" r:id="Rbe821520af464bad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D081" sheetId="82" r:id="R1f6cb9e8c26b4474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D082" sheetId="83" r:id="Rebd9d1b1f20e445d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D083" sheetId="84" r:id="R46cdee44271945c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D084" sheetId="85" r:id="Rdb256a5402d54e15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D085" sheetId="86" r:id="Rce372b5e95974152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D086" sheetId="87" r:id="Ra6b1a551c76841b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D087" sheetId="88" r:id="R607d85aa08b842a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D088" sheetId="89" r:id="R9f9c154a343e444b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D089" sheetId="90" r:id="R6e3c092831a24df5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D090" sheetId="91" r:id="Re14a9ad779304f31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D091" sheetId="92" r:id="Rd5ee5ee68e6041b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D092" sheetId="93" r:id="R43046adbbac541ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D093" sheetId="94" r:id="Rd86ed4551d6342fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D094" sheetId="95" r:id="R883c2c4e7f6d423b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D095" sheetId="96" r:id="Rd7144d4145394337"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D096" sheetId="97" r:id="R7dc3f08adce64c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D097" sheetId="98" r:id="R712578a26d7942dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D098" sheetId="99" r:id="R0205915349b34abd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D099" sheetId="100" r:id="Rc007210648824bdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D100" sheetId="101" r:id="R91c6299e294f44c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D101" sheetId="102" r:id="R7e4f929a90b14e85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D102" sheetId="103" r:id="Ra3545d29b10a4458"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D103" sheetId="104" r:id="Rafb65c5f6ed74583"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D104" sheetId="105" r:id="R2c3249aae32849cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D105" sheetId="106" r:id="R72c52a56988b44fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D106" sheetId="107" r:id="R28a8d746b7b54e24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D107" sheetId="108" r:id="R3c4f7706fde9478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D108" sheetId="109" r:id="R975fb9d251314c53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D109" sheetId="110" r:id="R03244d343d814cb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D110" sheetId="111" r:id="Re97603e82e5d45d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D111" sheetId="112" r:id="R4d0e9982ac814d12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D112" sheetId="113" r:id="R7cd6c11335eb49da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D113" sheetId="114" r:id="R0c9a8966e59345da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D114" sheetId="115" r:id="Ra90c6abc798f4deb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D115" sheetId="116" r:id="R0eded2b6c6e44f87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D116" sheetId="117" r:id="Ra0edc109b6e545f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D117" sheetId="118" r:id="R363d2605117e4986"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D118" sheetId="119" r:id="R9e6b0b3e0567413b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D119" sheetId="120" r:id="Rfc0a5059911d425e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D120" sheetId="121" r:id="R74deb71e522b493c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D121" sheetId="122" r:id="R91ca88de4ece4967"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D122" sheetId="123" r:id="R02cdeb6b24de4b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doctor Directory" sheetId="1" r:id="Rc61c5b1f25e44f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D001" sheetId="2" r:id="R9ab76a7ede124483"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D002" sheetId="3" r:id="R3d26224365404a9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D003" sheetId="4" r:id="Rd9fe44469f944bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D004" sheetId="5" r:id="R77b0dd2213514530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D005" sheetId="6" r:id="R497cb4d570b1404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D006" sheetId="7" r:id="R4a6236b936f14a20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D007" sheetId="8" r:id="R666d0ab800224238"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D008" sheetId="9" r:id="R7d5ea2b599a648b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D009" sheetId="10" r:id="R796bd23365d94bf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D010" sheetId="11" r:id="R44191db22b4f43f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D011" sheetId="12" r:id="R15981bf01edd433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D012" sheetId="13" r:id="R7e528fd382ff42b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D013" sheetId="14" r:id="Rbbd86f01b6a549e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D014" sheetId="15" r:id="R24155c9b42da4df6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D015" sheetId="16" r:id="R2f16e216f3ab4313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D016" sheetId="17" r:id="R2852ab79dedf4864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D017" sheetId="18" r:id="R157259ff52e340a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D018" sheetId="19" r:id="R63c1661615154623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D019" sheetId="20" r:id="Rdc193b6756d4459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D020" sheetId="21" r:id="Re5acc2073b964259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D021" sheetId="22" r:id="R7ecda4eec5db4218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D022" sheetId="23" r:id="Rba01d8adfc494284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D023" sheetId="24" r:id="R10d6f69a2c1a4746"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D024" sheetId="25" r:id="R42f28cc595664d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D025" sheetId="26" r:id="R5b83856105d14c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D026" sheetId="27" r:id="R26aac3961cc84886"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D027" sheetId="28" r:id="Rb46f6eca791e47b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D028" sheetId="29" r:id="R37255e18e1da4f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D029" sheetId="30" r:id="Ra749fca1018a400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D030" sheetId="31" r:id="R06002ba2ec164347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D031" sheetId="32" r:id="R3227acd3955943e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D032" sheetId="33" r:id="R495715da4cf74c1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D033" sheetId="34" r:id="R647e2aecb4f14030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D034" sheetId="35" r:id="Rc90b7eaf52c74552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D035" sheetId="36" r:id="R78bfdb6f6bba4524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D036" sheetId="37" r:id="R2529b4e8de5742e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D037" sheetId="38" r:id="R9db79aed8afd460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D038" sheetId="39" r:id="Rc525eed724d640b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D039" sheetId="40" r:id="Rf600506e189a4d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D040" sheetId="41" r:id="Ree249d097b4448a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D041" sheetId="42" r:id="R63e012071173428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D042" sheetId="43" r:id="R12b519e8fc164374"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D043" sheetId="44" r:id="R718e045c108d4e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D044" sheetId="45" r:id="R14fe8955ea594ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D045" sheetId="46" r:id="R6746fc2731984c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D046" sheetId="47" r:id="Rdb812c60a4ba44a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D047" sheetId="48" r:id="R8e391f2a61a74f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D048" sheetId="49" r:id="Rdb2a70aab1b94670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D049" sheetId="50" r:id="Rf86fee236b8241b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D050" sheetId="51" r:id="R48f7233c5f3049ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D051" sheetId="52" r:id="R721c5d8523544464"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D052" sheetId="53" r:id="Rc00e686246534674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D053" sheetId="54" r:id="R388e7914df404c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D054" sheetId="55" r:id="R4e426a2875274c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D055" sheetId="56" r:id="Rb14fa2a42ba542b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D056" sheetId="57" r:id="Re63f5e92714b4ed0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D057" sheetId="58" r:id="R0414c9ed2c944a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D058" sheetId="59" r:id="Rbc96c84e19744790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D059" sheetId="60" r:id="R2b15a134f9824037"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D060" sheetId="61" r:id="Rda31def6ca394f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D061" sheetId="62" r:id="R901c82eeddd94dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D062" sheetId="63" r:id="R41145f228a51442c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D063" sheetId="64" r:id="R5b7db3f9247241af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D064" sheetId="65" r:id="R07be8f1be4884c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D065" sheetId="66" r:id="R0100ea70aa58499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D066" sheetId="67" r:id="R5d7275b5b8f54abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D067" sheetId="68" r:id="Rac2ddb600fd24986"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D068" sheetId="69" r:id="R6746f42db4a24fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D069" sheetId="70" r:id="Ra86a408b6d6a44c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D070" sheetId="71" r:id="R87d69375b0334486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D071" sheetId="72" r:id="R2d1cba9293514eba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D072" sheetId="73" r:id="Re5e903343e694d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D073" sheetId="74" r:id="R8b6daee9fb5a4c76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D074" sheetId="75" r:id="Rb699b3fb609841fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D075" sheetId="76" r:id="Ree85ff0798614e47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D076" sheetId="77" r:id="Rcd8e419064f2489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D077" sheetId="78" r:id="Raea699b5a9ad44c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D078" sheetId="79" r:id="R074cc09c03a94ba4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D079" sheetId="80" r:id="R62c062cfd85d481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D080" sheetId="81" r:id="R7a554776f9224ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D081" sheetId="82" r:id="Rf93091e83bd748a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D082" sheetId="83" r:id="R48a9171503c64b2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D083" sheetId="84" r:id="R2edc1f7e08924c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D084" sheetId="85" r:id="R10165f929f594cd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D085" sheetId="86" r:id="R4cf84ea6c184469b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D086" sheetId="87" r:id="Rb0b3d247c7d4492b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D087" sheetId="88" r:id="R185a9ba1fbd440f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D088" sheetId="89" r:id="R836b1a6dbcfa4340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D089" sheetId="90" r:id="Ra8d235aa33bd4b8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D090" sheetId="91" r:id="Rb7fb41a086b24701"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D091" sheetId="92" r:id="Rb14db50bdefd4e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D092" sheetId="93" r:id="Re348bfe9402f4a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D093" sheetId="94" r:id="R5ce619d8b96d40e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D094" sheetId="95" r:id="R3f8bc1479f6e42fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D095" sheetId="96" r:id="R556e85b5d449427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D096" sheetId="97" r:id="Rba0f439d61d54a49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D097" sheetId="98" r:id="R04a113c8a9ad4604"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D098" sheetId="99" r:id="Rb7de09401e444067"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D099" sheetId="100" r:id="Ra9c56cbca0874883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D100" sheetId="101" r:id="R9b100e860abc4869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D101" sheetId="102" r:id="Rd495793bdad8409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D102" sheetId="103" r:id="Rdef61874e9d140d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D103" sheetId="104" r:id="R9d93081e1b0e4a4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D104" sheetId="105" r:id="R3d1912b23a8947a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D105" sheetId="106" r:id="R561ad3b226e4411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D106" sheetId="107" r:id="R8261743048594d34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D107" sheetId="108" r:id="R9726705380174bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D108" sheetId="109" r:id="R070f2a5af0534a0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D109" sheetId="110" r:id="R378d59aae6ff44fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D110" sheetId="111" r:id="R55b246e027174261"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D111" sheetId="112" r:id="Rc9361a0a167d453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D112" sheetId="113" r:id="R974b0e1c64634a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D113" sheetId="114" r:id="R151bbc5282e64b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D114" sheetId="115" r:id="R608e0006e8aa4be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D115" sheetId="116" r:id="R9b4ed41fe6b54224"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D116" sheetId="117" r:id="Rba7d45c722884da9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D117" sheetId="118" r:id="R41c8d99a9bef4387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D118" sheetId="119" r:id="R3e839197a1c542e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D119" sheetId="120" r:id="R323951f1b05546f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D120" sheetId="121" r:id="R126ab5deed5f4b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D121" sheetId="122" r:id="Rf75735fc079a43c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D122" sheetId="123" r:id="Rd76d786a7d5b4c7d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -693,7 +693,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2b6eaeca064047b4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R59f7592bce604ead"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6822,9 +6822,9 @@
     <x:mergeCell ref="A2:P2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85cb08e230504ea6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8caa76ac84484b9e"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb831abebc6524758"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c6913567f3b4aa1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7122,7 +7122,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1732290716b64eba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f3c7cfd29b54cd3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7465,7 +7465,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R172314ef3479467d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a1319891cf643a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7808,7 +7808,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60d4235e47814f43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R356293c5abf44a5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8151,7 +8151,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00eb62f7ff7f4b02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e8186e15b4499e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8539,7 +8539,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R698270383c04435a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf26a2cae0bc643c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8882,7 +8882,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d2aa278147401b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c1955c82f6a457f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9270,7 +9270,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b46ab14ae4d46d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R677840a808ed4cda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9703,7 +9703,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42afcc11824d4786"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R536dee62103240dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10001,7 +10001,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R043a2de97dd34c18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00ec476747734f9b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10389,7 +10389,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56aeb6faba2c4326"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R247dbd9d36d648ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10957,7 +10957,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1ba9bbf353c452b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70a494e9bae5472c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11300,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf4bdda12b054d60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9307f280b3514d0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11598,7 +11598,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66f4829be07e4125"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1534585821b4e2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12076,7 +12076,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0113d3f5f1aa427e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbff4acf54bd24ae8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12374,7 +12374,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9d4f4db54da43a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc568cac1f0fb4127"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12852,7 +12852,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46fd8041e2ae42b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd24ae5941f9148a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13150,7 +13150,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1984690fcdc64167"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra86fc428dfca4639"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13718,7 +13718,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd764ce7676f48a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9145e6c44c42431a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14331,7 +14331,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R160c18dd65de45b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5607fa8b0787440d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14899,7 +14899,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40cad56e1df646d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27dc7c1241264db5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15557,7 +15557,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R013a25ca85514a9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46ad30ece9f54440"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15855,7 +15855,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10b3730704d648b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f1c67eb43824986"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16243,7 +16243,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4589a4e690f74e84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51afcb7ba7514b80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16676,7 +16676,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6060abf4e1d04ac8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaefd84e8e3041e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17064,7 +17064,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19e45fe99d944f3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11b1d83cc6ef4c36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17452,7 +17452,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fe593ff2cfb4d0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa0d737129f64372"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17795,7 +17795,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R691846fa15374b3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b70066a53b24ff5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18363,7 +18363,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28f75034922f4f42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R504c79ae4387404a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18931,7 +18931,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb4c853ab96b48b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13f7139b6ba5403a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19589,7 +19589,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31fc621472ac4d27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31cd93385bee4dbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19887,7 +19887,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3417eeefdd344980"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R596efe7c6e82458a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20320,7 +20320,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0746d0fac70b4ca7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red4ee44bff5a4397"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20663,7 +20663,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1547484ab24a4239"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R426ef55340a243be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21006,7 +21006,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a42784b79c2480c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree723a4be33f4df6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21439,7 +21439,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc32067495e7a4143"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a7518767aa14b9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21872,7 +21872,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd776377fd6a44425"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b5aa514baac48a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22260,7 +22260,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd81b728d05254df5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71a9109c4c0d49d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22648,7 +22648,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb334b3456e94737"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27e754b8124f46bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23216,7 +23216,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba7305c89d8f4e0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf43cb58fa804be5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23514,7 +23514,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0bc501f2c5b4a3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c8feb3bb8624d6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23947,7 +23947,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca19d60623054758"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21abe96378ec4335"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24245,7 +24245,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R908b26e0b69541a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b7a1da967ee460c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24678,7 +24678,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f440626a34d48a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19265f56545e423b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25156,7 +25156,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra716569f552b4d18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45cdaf00e2194e46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25499,7 +25499,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb275d1e0e8c4aec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47427d24b5684624"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25932,7 +25932,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebae08a910eb4139"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0e9223308c431d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26320,7 +26320,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf187b4980184907"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R997a7dc4c2f7421d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26753,7 +26753,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02b76b32b1624093"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2959eeb0be844bdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27141,7 +27141,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a73a6c836de426f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R277a539fd87b4a3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27529,7 +27529,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R882286db21ab4eb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5db2ac42ad7644cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28007,7 +28007,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd59a898484446d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cf036e784c84172"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28800,7 +28800,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47fab535fc7a47de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c4330e6daaa4950"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29143,7 +29143,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde175c1b010b41d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c1ae0a991874799"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29576,7 +29576,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34f3edcdf1f54dd8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ebead36fbc4616"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29874,7 +29874,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2343bf3da4c42f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f2adfda747b45e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30172,7 +30172,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a8742b41794bb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9a95c66f80d4b2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30560,7 +30560,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc375ca1edaec473f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cc12665ed2b4006"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30993,7 +30993,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bea11fe02eb41d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R350c5d7664e44578"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31471,7 +31471,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1324d7c555c94802"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a47f88f6d3641fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31949,7 +31949,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd896c4fb32c54237"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fad4f0d4c0842a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32337,7 +32337,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18c42caedcfa48fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4753b9d5f304de5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32770,7 +32770,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcaea04f78454c13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R605fc9806cb34aa3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33563,7 +33563,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7e8c2149b934ded"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25ff764a96484ed0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33951,7 +33951,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1902a961e0014fd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca761c6a080e440c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34429,7 +34429,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad31a7b30c3e4799"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06ba47f9c31642f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34727,7 +34727,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14531110f1db4791"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb94a81e22190485b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35250,7 +35250,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7535701f098346e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R623e8b0a5a90451a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35683,7 +35683,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R548d3ecfc7714d3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdce50e7319d49ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36206,7 +36206,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf14c7838d0cc46c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb15849395a84476"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36729,7 +36729,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a013dfd9729429d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cdeed5dd12b434d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37117,7 +37117,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51db348d8bb94fb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49be458f6c7f446d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37505,7 +37505,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf5d965953974e6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a7c565cc2474f7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37803,7 +37803,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ced38c1fcab4374"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff85181bf2724b58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38281,7 +38281,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c31b980a52b41c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d635a09e275428e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38714,7 +38714,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f78b40677c040e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra03a631951f64dea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39327,7 +39327,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R062f35999d934e88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32299c7cbeae4b4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39985,7 +39985,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dc83b033e3a4a69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8eaa33e6dc234839"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40643,7 +40643,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91fcadfb249042d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R602b69661a2a409d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40986,7 +40986,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28045f296bc340d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca13dff5307c486d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41599,7 +41599,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e88dd8692f2406d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdff66125f2f74b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41987,7 +41987,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bb1d68e32e24167"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0be4025ab50646a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42285,7 +42285,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82baef5a16af414c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89745b15e7d84378"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42718,7 +42718,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ec18f0fe7a348c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cf9020cb964414d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43151,7 +43151,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ef39806fff04204"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4f291511c174efb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43539,7 +43539,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07db4dd50d804def"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dc90aa40c1a4c45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43837,7 +43837,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e775a0b9a674807"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77624baa56c6452f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44180,7 +44180,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3cf8c1d5bfc4367"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66642ca1a14542a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44793,7 +44793,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R611897569ce74de3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R926ffecd8a52462e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45136,7 +45136,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bde4a95444440a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2cd43a866d84827"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45704,7 +45704,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07e01c3691b44168"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf77f50c6b5644021"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46002,7 +46002,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0026109308614fcf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f5b8343cb0542ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46300,7 +46300,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39d1a86457ec4bb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a30cd1d376d4712"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46643,7 +46643,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57ed3c8aa63448b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra21fd6de216243ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46986,7 +46986,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65a6ae26577a4742"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re51468cde0de471d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47509,7 +47509,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78c49fa4e8524eee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3037283358e4dc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47807,7 +47807,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53cc045d0a4a482b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79c807e034a54e5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48195,7 +48195,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re28b7385e7624d17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9352cf1860dc4382"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48583,7 +48583,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73f1f910f0584cee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbce128a597c84f53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49016,7 +49016,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3c436e60d5f4535"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346f9aaa69c1419e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49449,7 +49449,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72b243b2a04c4ca7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f8e1a7dfda4f3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49882,7 +49882,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1ec8e8aa38b4376"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde572eda5c05482f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50720,7 +50720,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb1eff47d344907"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bfc9e93e04f4cc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51108,7 +51108,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08b3ed8ed96347c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbe1439414a84e1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51541,7 +51541,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe98073e5968465f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d284375d1604fab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51929,7 +51929,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc862be1437421a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4ef269f48f349fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52317,7 +52317,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re252502fd6b14d4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04206c7fb80e4db3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52615,7 +52615,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2385224afe054879"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7009255a5ae642ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53093,7 +53093,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3af3cf809e514d5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff47418c27ae468c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53391,7 +53391,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R909ead148bd54061"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdae09f8547484599"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53689,7 +53689,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3a591d3f54f4364"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re62142e36cba4c59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54077,7 +54077,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra35f9395b63449ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R160b591bd7c94700"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54420,7 +54420,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdcc6dfd1344404a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R654ad04d28cd4d64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54763,7 +54763,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a6a6d5dbb984310"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf3b0e1c88e64042"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55196,7 +55196,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R722072602b0c475e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R116094444d8642be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55719,7 +55719,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfea2439da1b4438"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc968e40b39274778"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56107,7 +56107,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74173f588a1b4e3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b27916a07ad4d90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56405,7 +56405,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R749c6769e970491f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea5d437c3339440f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56793,7 +56793,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeff6fdec2254382"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf139debcb944a66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57181,7 +57181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b21dba3bd04051"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0223d14e69844402"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57614,7 +57614,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56cee589530d4d21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a2e18410e074e3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57912,7 +57912,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58c7eb63a9d449d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb7f2f49b247442b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -58345,7 +58345,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R121775c9758e4619"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R626358c69bec4d17"/>
   </x:tableParts>
 </x:worksheet>
 </file>